--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_F8DA8372CA39024E5FA14DBE1E299F2EE45F39C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82DB4FB0-0AF3-B44C-B8F4-8B5AD2B18401}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_C351045F9CC953CE308179B7844FEE98296F08CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0178E20F-49CC-A44D-BCF6-DA7348D56571}"/>
   <bookViews>
-    <workbookView xWindow="-2600" yWindow="2240" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="800" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="548">
   <si>
     <t>ID</t>
   </si>
@@ -990,6 +990,41 @@
     <t>Synopsis, fiches techniques, distributions et analyses explicitement séparées des sections « Notes ».</t>
   </si>
   <si>
+    <t>Chinesisches Roulette</t>
+  </si>
+  <si>
+    <t>Ila von Hasperg</t>
+  </si>
+  <si>
+    <t>Michael Fengler ; Barbet Schroeder</t>
+  </si>
+  <si>
+    <t>Anna Karina : Irene Cartis
+Margit Carstensen : Ariane Christ
+Brigitte Mira : Kast
+Ulli Lommel : Kolbe
+Alexander Allerson : Gerhard Christ
+Volker Spengler : Gabriel Kast
+Andrea Schober : Angela Christ
+Macha Méril : Traunitz, la gouvernante muette
+Armin Meier : le pompiste
+Roland Henschke : le mendiant</t>
+  </si>
+  <si>
+    <t>Format : couleurs, 1,66:1, mono
+Genre : drame, thriller
+Sortie : 1976</t>
+  </si>
+  <si>
+    <t>Un riche industriel et sa femme partent séparément passer le week-end avec leurs amants dans leur château de campagne, chacun croyant l’autre absent. La rencontre imprévue des deux couples est bientôt aggravée par l’arrivée de leur fille Angela, handicapée, et de sa gouvernante. Angela organise une « roulette chinoise » qui transforme le jeu mondain en règlement de comptes familial.</t>
+  </si>
+  <si>
+    <t>Le château devient un huis clos où vitrines, miroirs, meubles transparents, surcadrages et travellings circulaires enferment les personnages dans un réseau de regards et recomposent sans cesse les alliances. Angela utilise le jeu pour rendre visibles les mensonges, la haine familiale et la violence exercée sur l’enfant handicapée. Les allusions au IIIe Reich font affleurer, sous la respectabilité bourgeoise, une mémoire refoulée dont la violence éclate sans produire de résolution.</t>
+  </si>
+  <si>
+    <t>famille|adultère|huis clos|jeu|cruauté|handicap|nazisme|mémoire|miroirs|surcadrage</t>
+  </si>
+  <si>
     <t>Saisir une personne par ligne au format Nom canonique : rôle.</t>
   </si>
   <si>
@@ -1782,7 +1817,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">film inspiré par le </t>
+      <t xml:space="preserve">Le film dénonce la violence exercée par une société étriquée contre les étrnagers, violence que le personnage principal, d'origine grecque, reconduit avec des individus encore plus dominés que lui. Film à l'esthétique avant-gardiste, brechtienne par son caractère anti-illustionniste. Il est constitué d'une suite de brefs tableaux, d'images figées, de plans fontaux. Les mouvements de caméra sont rares : des travellings latéraux, sans profondeur d'images, conservent une forme de théâtralité à l'image. Comme d'autres films  de RWF de la période, </t>
     </r>
     <r>
       <rPr>
@@ -1790,72 +1825,15 @@
         <sz val="11"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>Week-end</t>
+      <t xml:space="preserve">Le bouc </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t xml:space="preserve"> de Godard (1967) : même sutrcutre de voyage picarestque à la campagne qui s'achève dans la violence. La succession de tableaux puise aussi au film </t>
+      <t xml:space="preserve">vise un public qui n'est ni restreint et cinéphile, ni populaire.  </t>
     </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>Antonio dans Mortes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> de Glauber Rocha (1969)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Dans un endroit perdu, une équipe de cinéma est traversée par des tensions alors qu'elle attend l'arrivée du réalisateur et l'argent de la paie. </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">L'œuvre est souvent décrite comme une relecture du tournage chaotique de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>Whity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> tourné la même année en Espagne. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Film initailiement produit par la WDR (télévision) qui se retire d'un projet dont le sujet est jugé trop sensible. Le sénat de Berlin, qui soutient les films tournés dans l'ancienne capitale, fait de même. Fassbinder, averti au moment du tournage finance le film sur ses propres deniers, aidé par un accord de coproduction avec la société munichoise Filmverlag der Autoren.
-Le film est une charge satirique violente contre les collectifs politiques, qui marque la fin d'une époque où ceux-ci ont été très présents sur la scène politique allemande et internationale. 
-La réalité parallèle dans laquelle semble évoluer le groupe d'activistes invite à établir des liens avec </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>Le monde sur un fil</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Un groupe d'activistes urbains forment une cellule clandestine. Croyant avoir été dénocnés, ils décident de passer à l'action, alors qu'ils sont en réalité manipulés par une multinationale qui vend des systèmes de surveillance. 
-Le mot de passe des terroristes est la formule de Schopenhauer "le monde comme volonté de représentation". </t>
   </si>
 </sst>
 </file>
@@ -2440,7 +2418,9 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
+      <c r="S3" s="4" t="s">
+        <v>547</v>
+      </c>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
@@ -2664,9 +2644,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="4" t="s">
-        <v>539</v>
-      </c>
+      <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
@@ -2776,13 +2754,9 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4" t="s">
-        <v>540</v>
-      </c>
+      <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="4" t="s">
-        <v>541</v>
-      </c>
+      <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
@@ -3959,38 +3933,60 @@
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="30">
+    <row r="27" spans="1:30" ht="150">
       <c r="A27" s="4" t="s">
         <v>194</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="D27" s="5">
         <v>1976</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5">
+        <v>96</v>
+      </c>
       <c r="G27" s="4" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+      <c r="I27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>278</v>
+      </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
+      <c r="M27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>282</v>
+      </c>
       <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
+      <c r="S27" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
@@ -3998,24 +3994,28 @@
       <c r="X27" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="Y27" s="4"/>
-      <c r="Z27" s="4"/>
+      <c r="Y27" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z27" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="AA27" s="4" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="AB27" s="1" t="s">
         <v>196</v>
       </c>
       <c r="AC27" s="9" t="str">
         <f>IF(O27="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O27)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O27)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O27)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O27)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O27)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O27)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O27)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O27)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O27)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O27)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O27)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O27)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O27)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O27)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O27)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O27)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O27)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O27)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O27)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O27)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O27)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O27)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O27)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-volker-spengler</v>
       </c>
       <c r="AD27" s="9" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H27:N27,P27),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:30" ht="60">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="45">
       <c r="A28" s="4" t="s">
         <v>197</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="45">
+    <row r="29" spans="1:30" ht="30">
       <c r="A29" s="4" t="s">
         <v>200</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="195">
+    <row r="35" spans="1:30" ht="45">
       <c r="A35" s="4" t="s">
         <v>223</v>
       </c>
@@ -4438,13 +4438,9 @@
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
-      <c r="Q35" s="4" t="s">
-        <v>543</v>
-      </c>
+      <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
-      <c r="S35" s="4" t="s">
-        <v>542</v>
-      </c>
+      <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
@@ -4641,7 +4637,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="45">
+    <row r="39" spans="1:30" ht="30">
       <c r="A39" s="4" t="s">
         <v>238</v>
       </c>
@@ -4697,7 +4693,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="45">
+    <row r="40" spans="1:30" ht="30">
       <c r="A40" s="4" t="s">
         <v>241</v>
       </c>
@@ -4857,7 +4853,7 @@
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>250</v>
       </c>
@@ -4985,7 +4981,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="74.75" customHeight="1">
@@ -4993,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="74.75" customHeight="1">
@@ -5020,7 +5016,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15">
+    <row r="13" spans="1:2" ht="16">
       <c r="A13" s="6" t="s">
         <v>273</v>
       </c>
@@ -5028,7 +5024,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15">
+    <row r="14" spans="1:2" ht="16">
       <c r="A14" s="6" t="s">
         <v>275</v>
       </c>
@@ -5038,18 +5034,18 @@
     </row>
     <row r="15" spans="1:2" ht="40" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="40" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="61.25" customHeight="1">
@@ -5057,7 +5053,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="61.25" customHeight="1">
@@ -5065,15 +5061,15 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="42.75" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5098,731 +5094,731 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="150">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="135">
       <c r="A2" s="8" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="180">
       <c r="A3" s="8" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="75">
       <c r="A4" s="8" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="45">
       <c r="A5" s="8" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="90">
       <c r="A6" s="8" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="180">
       <c r="A7" s="8" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="90">
       <c r="A8" s="8" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="195">
       <c r="A9" s="8" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="135">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="120">
       <c r="A10" s="8" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="150">
       <c r="A11" s="8" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="105">
       <c r="A12" s="8" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="105">
       <c r="A13" s="8" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="105">
       <c r="A14" s="8" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="90">
       <c r="A15" s="8" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="90">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="75">
       <c r="A16" s="8" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="240">
       <c r="A17" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>124</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="45">
       <c r="A18" s="8" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>151</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="30">
       <c r="A19" s="8" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>179</v>
@@ -5832,206 +5828,206 @@
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="180">
       <c r="A20" s="8" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="60">
       <c r="A21" s="8" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="45">
       <c r="A22" s="8" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="75">
       <c r="A23" s="8" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="120">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="105">
       <c r="A24" s="8" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_C351045F9CC953CE308179B7844FEE98296F08CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0178E20F-49CC-A44D-BCF6-DA7348D56571}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_C351045F9CC953CE308179B7844FEE98296F08CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4DAC3B-4980-7744-8CC1-EA0579CBFEAF}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="800" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="574">
   <si>
     <t>ID</t>
   </si>
@@ -1834,6 +1834,84 @@
       </rPr>
       <t xml:space="preserve">vise un public qui n'est ni restreint et cinéphile, ni populaire.  </t>
     </r>
+  </si>
+  <si>
+    <t>L_Amour_est_plus_froid_que_la_mort.jpg</t>
+  </si>
+  <si>
+    <t>Le_Bouc.jpg</t>
+  </si>
+  <si>
+    <t>Les_Dieux_de_la_peste.jpg</t>
+  </si>
+  <si>
+    <t>Le_Soldat_americain.jpg</t>
+  </si>
+  <si>
+    <t>Prenez_garde_a_la_sainte_putain.jpg</t>
+  </si>
+  <si>
+    <t>Le_Marchand_des_quatre_saisons.jpg</t>
+  </si>
+  <si>
+    <t>Les_Larmes_ameres_de_Petra_von_Kant.jpg</t>
+  </si>
+  <si>
+    <t>Le_Monde_sur_un_fil.jpg</t>
+  </si>
+  <si>
+    <t>Tous_les_autres_s_appellent_Ali.jpg</t>
+  </si>
+  <si>
+    <t>Effi_Briest.jpg</t>
+  </si>
+  <si>
+    <t>Le_Droit_du_plus_fort.jpg</t>
+  </si>
+  <si>
+    <t>Maman_Kusters_s_en_va_au_ciel.jpg</t>
+  </si>
+  <si>
+    <t>L_Ombre_des_anges.jpg</t>
+  </si>
+  <si>
+    <t>Le_Roti_de_Satan.jpg</t>
+  </si>
+  <si>
+    <t>Roulette_chinoise.jpg</t>
+  </si>
+  <si>
+    <t>Je_veux_seulement_que_vous_m_aimiez.jpg</t>
+  </si>
+  <si>
+    <t>L_Allemagne_en_automne.jpg</t>
+  </si>
+  <si>
+    <t>Despair.jpg</t>
+  </si>
+  <si>
+    <t>L_Annee_des_treize_lunes.jpg</t>
+  </si>
+  <si>
+    <t>Le_Mariage_de_Maria_Braun.jpg</t>
+  </si>
+  <si>
+    <t>La_Troisieme_generation.jpg</t>
+  </si>
+  <si>
+    <t>Berlin_Alexanderplatz.jpg</t>
+  </si>
+  <si>
+    <t>Lili_Marleen.jpg</t>
+  </si>
+  <si>
+    <t>Lola_une_femme_allemande.jpg</t>
+  </si>
+  <si>
+    <t>Le_Secret_de_Veronika_Voss.jpg</t>
+  </si>
+  <si>
+    <t>Querelle.jpg</t>
   </si>
 </sst>
 </file>
@@ -1977,7 +2055,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1996,6 +2077,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2021,7 +2106,7 @@
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="0"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie"/>
@@ -2362,7 +2447,9 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="U2" s="4" t="s">
+        <v>548</v>
+      </c>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
       <c r="X2" s="4" t="s">
@@ -2422,7 +2509,9 @@
         <v>547</v>
       </c>
       <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="U3" s="4" t="s">
+        <v>549</v>
+      </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4" t="s">
@@ -2478,7 +2567,9 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="U4" s="4" t="s">
+        <v>550</v>
+      </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4" t="s">
@@ -2590,7 +2681,9 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
+      <c r="U6" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
       <c r="X6" s="4" t="s">
@@ -2758,7 +2851,9 @@
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="U9" s="4" t="s">
+        <v>552</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4" t="s">
@@ -2872,7 +2967,9 @@
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
+      <c r="U11" s="4" t="s">
+        <v>553</v>
+      </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4" t="s">
@@ -2930,7 +3027,9 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
+      <c r="U12" s="4" t="s">
+        <v>554</v>
+      </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
       <c r="X12" s="4" t="s">
@@ -3192,7 +3291,9 @@
       <c r="T16" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="U16" s="4"/>
+      <c r="U16" s="4" t="s">
+        <v>555</v>
+      </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
       <c r="X16" s="4" t="s">
@@ -3264,7 +3365,9 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
+      <c r="U17" s="4" t="s">
+        <v>556</v>
+      </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
       <c r="X17" s="4" t="s">
@@ -3346,7 +3449,9 @@
       <c r="T18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="U18" s="4"/>
+      <c r="U18" s="4" t="s">
+        <v>557</v>
+      </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
       <c r="X18" s="4" t="s">
@@ -3568,7 +3673,9 @@
         <v>156</v>
       </c>
       <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
+      <c r="U21" s="4" t="s">
+        <v>558</v>
+      </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
       <c r="X21" s="4" t="s">
@@ -3654,7 +3761,9 @@
       <c r="T22" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="U22" s="4"/>
+      <c r="U22" s="4" t="s">
+        <v>559</v>
+      </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
       <c r="X22" s="4" t="s">
@@ -3826,7 +3935,9 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
+      <c r="U25" s="4" t="s">
+        <v>560</v>
+      </c>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
       <c r="X25" s="4" t="s">
@@ -3906,7 +4017,9 @@
       <c r="T26" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="U26" s="4"/>
+      <c r="U26" s="4" t="s">
+        <v>561</v>
+      </c>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
       <c r="X26" s="4" t="s">
@@ -3988,7 +4101,9 @@
         <v>283</v>
       </c>
       <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
+      <c r="U27" s="4" t="s">
+        <v>562</v>
+      </c>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
       <c r="X27" s="4" t="s">
@@ -4048,7 +4163,9 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
+      <c r="U28" s="4" t="s">
+        <v>563</v>
+      </c>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
       <c r="X28" s="4" t="s">
@@ -4216,7 +4333,9 @@
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
+      <c r="U31" s="4" t="s">
+        <v>564</v>
+      </c>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
       <c r="X31" s="4" t="s">
@@ -4272,7 +4391,9 @@
       <c r="R32" s="4"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
+      <c r="U32" s="4" t="s">
+        <v>565</v>
+      </c>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
       <c r="X32" s="4" t="s">
@@ -4328,7 +4449,9 @@
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
+      <c r="U33" s="4" t="s">
+        <v>566</v>
+      </c>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
       <c r="X33" s="4" t="s">
@@ -4386,7 +4509,9 @@
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
+      <c r="U34" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
       <c r="X34" s="4" t="s">
@@ -4442,7 +4567,9 @@
       <c r="R35" s="4"/>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
+      <c r="U35" s="4" t="s">
+        <v>568</v>
+      </c>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
       <c r="X35" s="4" t="s">
@@ -4500,7 +4627,9 @@
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
+      <c r="U36" s="4" t="s">
+        <v>569</v>
+      </c>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
       <c r="X36" s="4" t="s">
@@ -4558,7 +4687,9 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
+      <c r="U37" s="4" t="s">
+        <v>570</v>
+      </c>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
       <c r="X37" s="4" t="s">
@@ -4670,7 +4801,9 @@
       <c r="R39" s="4"/>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
+      <c r="U39" s="4" t="s">
+        <v>571</v>
+      </c>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
       <c r="X39" s="4" t="s">
@@ -4728,7 +4861,9 @@
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
+      <c r="U40" s="4" t="s">
+        <v>572</v>
+      </c>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
       <c r="X40" s="4" t="s">
@@ -4786,7 +4921,9 @@
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
+      <c r="U41" s="4" t="s">
+        <v>573</v>
+      </c>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
       <c r="X41" s="4" t="s">
@@ -4810,8 +4947,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AA18">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="A2:T18 V2:AA18">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_C351045F9CC953CE308179B7844FEE98296F08CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4DAC3B-4980-7744-8CC1-EA0579CBFEAF}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_C351045F9CC953CE308179B7844FEE98296F08CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2F20A16-34C6-1B44-B4BF-14019B3BF6B6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1836,82 +1836,82 @@
     </r>
   </si>
   <si>
-    <t>L_Amour_est_plus_froid_que_la_mort.jpg</t>
-  </si>
-  <si>
-    <t>Le_Bouc.jpg</t>
-  </si>
-  <si>
-    <t>Les_Dieux_de_la_peste.jpg</t>
-  </si>
-  <si>
-    <t>Le_Soldat_americain.jpg</t>
-  </si>
-  <si>
-    <t>Prenez_garde_a_la_sainte_putain.jpg</t>
-  </si>
-  <si>
-    <t>Le_Marchand_des_quatre_saisons.jpg</t>
-  </si>
-  <si>
-    <t>Les_Larmes_ameres_de_Petra_von_Kant.jpg</t>
-  </si>
-  <si>
-    <t>Le_Monde_sur_un_fil.jpg</t>
-  </si>
-  <si>
-    <t>Tous_les_autres_s_appellent_Ali.jpg</t>
-  </si>
-  <si>
-    <t>Effi_Briest.jpg</t>
-  </si>
-  <si>
-    <t>Le_Droit_du_plus_fort.jpg</t>
-  </si>
-  <si>
-    <t>Maman_Kusters_s_en_va_au_ciel.jpg</t>
-  </si>
-  <si>
-    <t>L_Ombre_des_anges.jpg</t>
-  </si>
-  <si>
-    <t>Le_Roti_de_Satan.jpg</t>
-  </si>
-  <si>
-    <t>Roulette_chinoise.jpg</t>
-  </si>
-  <si>
-    <t>Je_veux_seulement_que_vous_m_aimiez.jpg</t>
-  </si>
-  <si>
-    <t>L_Allemagne_en_automne.jpg</t>
-  </si>
-  <si>
-    <t>Despair.jpg</t>
-  </si>
-  <si>
-    <t>L_Annee_des_treize_lunes.jpg</t>
-  </si>
-  <si>
-    <t>Le_Mariage_de_Maria_Braun.jpg</t>
-  </si>
-  <si>
-    <t>La_Troisieme_generation.jpg</t>
-  </si>
-  <si>
-    <t>Berlin_Alexanderplatz.jpg</t>
-  </si>
-  <si>
-    <t>Lili_Marleen.jpg</t>
-  </si>
-  <si>
-    <t>Lola_une_femme_allemande.jpg</t>
-  </si>
-  <si>
-    <t>Le_Secret_de_Veronika_Voss.jpg</t>
-  </si>
-  <si>
-    <t>Querelle.jpg</t>
+    <t>Films_images/L_Amour_est_plus_froid_que_la_mort.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Bouc.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Les_Dieux_de_la_peste.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Soldat_americain.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Prenez_garde_a_la_sainte_putain.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Marchand_des_quatre_saisons.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Les_Larmes_ameres_de_Petra_von_Kant.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Monde_sur_un_fil.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Tous_les_autres_s_appellent_Ali.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Effi_Briest.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Droit_du_plus_fort.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Maman_Kusters_s_en_va_au_ciel.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/L_Ombre_des_anges.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Roti_de_Satan.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Roulette_chinoise.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Je_veux_seulement_que_vous_m_aimiez.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/L_Allemagne_en_automne.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Despair.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/L_Annee_des_treize_lunes.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Mariage_de_Maria_Braun.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/La_Troisieme_generation.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Berlin_Alexanderplatz.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Lili_Marleen.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Lola_une_femme_allemande.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Secret_de_Veronika_Voss.jpg</t>
+  </si>
+  <si>
+    <t>Films_images/Querelle.jpg</t>
   </si>
 </sst>
 </file>
@@ -2057,14 +2057,14 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFF3F6F8"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2106,7 +2106,7 @@
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="0"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="1"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie"/>
@@ -4948,7 +4948,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:T18 V2:AA18">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederiquehammerli/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_C351045F9CC953CE308179B7844FEE98296F08CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2F20A16-34C6-1B44-B4BF-14019B3BF6B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="592">
   <si>
     <t>ID</t>
   </si>
@@ -146,6 +146,9 @@
     <t>Rainer Werner Fassbinder</t>
   </si>
   <si>
+    <t>Films_images/L_Amour_est_plus_froid_que_la_mort.jpg</t>
+  </si>
+  <si>
     <t>1969</t>
   </si>
   <si>
@@ -164,6 +167,9 @@
     <t>Katzelmacher</t>
   </si>
   <si>
+    <t>Films_images/Le_Bouc.jpg</t>
+  </si>
+  <si>
     <t>film-1969-le-bouc</t>
   </si>
   <si>
@@ -173,6 +179,9 @@
     <t>Les Dieux de la peste</t>
   </si>
   <si>
+    <t>Films_images/Les_Dieux_de_la_peste.jpg</t>
+  </si>
+  <si>
     <t>1970</t>
   </si>
   <si>
@@ -194,6 +203,9 @@
     <t>Le Soldat américain</t>
   </si>
   <si>
+    <t>Films_images/Le_Soldat_americain.jpg</t>
+  </si>
+  <si>
     <t>film-1970-le-soldat-americain</t>
   </si>
   <si>
@@ -227,6 +239,9 @@
     <t>Prenez garde à la sainte putain</t>
   </si>
   <si>
+    <t>Films_images/Prenez_garde_a_la_sainte_putain.jpg</t>
+  </si>
+  <si>
     <t>film-1971-prenez-garde-a-la-sainte-putain</t>
   </si>
   <si>
@@ -248,6 +263,9 @@
     <t>Händler der vier Jahreszeiten</t>
   </si>
   <si>
+    <t>Films_images/Le_Marchand_des_quatre_saisons.jpg</t>
+  </si>
+  <si>
     <t>1972</t>
   </si>
   <si>
@@ -263,6 +281,9 @@
     <t>Die bitteren Tränen der Petra von Kant</t>
   </si>
   <si>
+    <t>Films_images/Les_Larmes_ameres_de_Petra_von_Kant.jpg</t>
+  </si>
+  <si>
     <t>film-1972-les-larmes-ameres-de-petra-von-kant</t>
   </si>
   <si>
@@ -291,6 +312,9 @@
   </si>
   <si>
     <t>Marie Anne Gerhardt</t>
+  </si>
+  <si>
+    <t>Kurt Raab</t>
   </si>
   <si>
     <t>WDR</t>
@@ -379,6 +403,9 @@
     <t>Daniel F. Galouye, Simulacron 3</t>
   </si>
   <si>
+    <t>Films_images/Le_Monde_sur_un_fil.jpg</t>
+  </si>
+  <si>
     <t>science-fiction|simulation|réalité virtuelle|identité|cybernétique|télévision</t>
   </si>
   <si>
@@ -421,6 +448,9 @@
     <t>Dans l’Allemagne de l’Ouest des années 1970, Emmi, veuve âgée, et Ali, travailleur immigré marocain, tombent amoureux puis se marient. Leur couple affronte le racisme, les préjugés et l’hostilité de l’entourage. Lorsque cette hostilité s’atténue par intérêt, de nouvelles tensions apparaissent au sein du couple.</t>
   </si>
   <si>
+    <t>Films_images/Tous_les_autres_s_appellent_Ali.jpg</t>
+  </si>
+  <si>
     <t>1974</t>
   </si>
   <si>
@@ -446,9 +476,6 @@
   </si>
   <si>
     <t>Thea Eymèsz</t>
-  </si>
-  <si>
-    <t>Kurt Raab</t>
   </si>
   <si>
     <t>Hanna Schygulla : Effi Briest
@@ -480,6 +507,9 @@
     <t>Theodor Fontane, Effi Briest</t>
   </si>
   <si>
+    <t>Films_images/Effi_Briest.jpg</t>
+  </si>
+  <si>
     <t>adaptation littéraire|mariage|conventions sociales|patriarcat|Theodor Fontane|noir et blanc</t>
   </si>
   <si>
@@ -592,6 +622,9 @@
     <t>Le film articule mélodrame, lutte des classes et exploitation affective. Le gain à la loterie ouvre un cycle provisoire de bonheur qui se referme sur la dépossession et la mort de Fox. La relation amoureuse ne supprime pas les rapports de domination : le capital culturel et les codes bourgeois transforment l’intimité en mécanisme d’exploitation.</t>
   </si>
   <si>
+    <t>Films_images/Le_Droit_du_plus_fort.jpg</t>
+  </si>
+  <si>
     <t>1975</t>
   </si>
   <si>
@@ -652,6 +685,9 @@
     <t>Mutter Krausens Fahrt ins Glück (1929), film-source mentionné</t>
   </si>
   <si>
+    <t>Films_images/Maman_Kusters_s_en_va_au_ciel.jpg</t>
+  </si>
+  <si>
     <t>presse|classe ouvrière|communisme|anarchisme|distanciation|Brecht|RFA</t>
   </si>
   <si>
@@ -680,6 +716,9 @@
   </si>
   <si>
     <t>L’Ombre des anges</t>
+  </si>
+  <si>
+    <t>Films_images/L_Ombre_des_anges.jpg</t>
   </si>
   <si>
     <t>1976</t>
@@ -735,6 +774,9 @@
 Thomas Elsaesser, analyses sur Fassbinder et Despair</t>
   </si>
   <si>
+    <t>Films_images/Le_Roti_de_Satan.jpg</t>
+  </si>
+  <si>
     <t>artiste|folie|grotesque|Antonin Artaud|Stefan George|création|comédie noire</t>
   </si>
   <si>
@@ -747,250 +789,10 @@
     <t>Roulette chinoise</t>
   </si>
   <si>
-    <t>film-1976-roulette-chinoise</t>
-  </si>
-  <si>
-    <t>rwf-1976-je-veux-seulement-que-vous-maimiez</t>
-  </si>
-  <si>
-    <t>Je veux seulement que vous m’aimiez</t>
-  </si>
-  <si>
-    <t>film-1976-je-veux-seulement-que-vous-m-aimiez</t>
-  </si>
-  <si>
-    <t>rwf-1977-femmes-a-new-york</t>
-  </si>
-  <si>
-    <t>Femmes à New York</t>
-  </si>
-  <si>
-    <t>1977</t>
-  </si>
-  <si>
-    <t>film-1977-femmes-a-new-york</t>
-  </si>
-  <si>
-    <t>rwf-1977-la-femme-du-chef-de-gare</t>
-  </si>
-  <si>
-    <t>La Femme du chef de gare</t>
-  </si>
-  <si>
-    <t>film-1977-la-femme-du-chef-de-gare</t>
-  </si>
-  <si>
-    <t>rwf-1978-lallemagne-en-automne</t>
-  </si>
-  <si>
-    <t>L’Allemagne en automne</t>
-  </si>
-  <si>
-    <t>Film collectif</t>
-  </si>
-  <si>
-    <t>1978</t>
-  </si>
-  <si>
-    <t>film-1978-l-allemagne-en-automne</t>
-  </si>
-  <si>
-    <t>rwf-1978-despair</t>
-  </si>
-  <si>
-    <t>Despair</t>
-  </si>
-  <si>
-    <t>film-1978-despair</t>
-  </si>
-  <si>
-    <t>rwf-1978-lannee-des-treize-lunes</t>
-  </si>
-  <si>
-    <t>L’Année des treize lunes</t>
-  </si>
-  <si>
-    <t>film-1978-l-annee-des-treize-lunes</t>
-  </si>
-  <si>
-    <t>rwf-1978-maria-braun</t>
-  </si>
-  <si>
-    <t>Le Mariage de Maria Braun</t>
-  </si>
-  <si>
-    <t>Die Ehe der Maria Braun</t>
-  </si>
-  <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>film-1979-le-mariage-de-maria-braun</t>
-  </si>
-  <si>
-    <t>rwf-1979-la-troisieme-generation</t>
-  </si>
-  <si>
-    <t>La Troisième génération</t>
-  </si>
-  <si>
-    <t>film-1979-la-troisieme-generation</t>
-  </si>
-  <si>
-    <t>rwf-1980-berlin-alexanderplatz</t>
-  </si>
-  <si>
-    <t>Berlin Alexanderplatz</t>
-  </si>
-  <si>
-    <t>1980</t>
-  </si>
-  <si>
-    <t>film-1980-berlin-alexanderplatz</t>
-  </si>
-  <si>
-    <t>rwf-1981-lili-marleen</t>
-  </si>
-  <si>
-    <t>Lili Marleen</t>
-  </si>
-  <si>
-    <t>1981</t>
-  </si>
-  <si>
-    <t>film-1981-lili-marleen</t>
-  </si>
-  <si>
-    <t>rwf-1981-theatre-en-transe</t>
-  </si>
-  <si>
-    <t>Théâtre en transe</t>
-  </si>
-  <si>
-    <t>Documentaire</t>
-  </si>
-  <si>
-    <t>film-1981-theatre-en-transe</t>
-  </si>
-  <si>
-    <t>rwf-1981-lola-une-femme-allemande</t>
-  </si>
-  <si>
-    <t>Lola, une femme allemande</t>
-  </si>
-  <si>
-    <t>film-1981-lola-une-femme-allemande</t>
-  </si>
-  <si>
-    <t>rwf-1982-veronika-voss</t>
-  </si>
-  <si>
-    <t>Le Secret de Veronika Voss</t>
-  </si>
-  <si>
-    <t>Die Sehnsucht der Veronika Voss</t>
-  </si>
-  <si>
-    <t>film-1981-le-secret-de-veronika-voss</t>
-  </si>
-  <si>
-    <t>rwf-1982-querelle</t>
-  </si>
-  <si>
-    <t>Querelle</t>
+    <t>Chinesisches Roulette</t>
   </si>
   <si>
     <t>RFA / France</t>
-  </si>
-  <si>
-    <t>1982</t>
-  </si>
-  <si>
-    <t>film-1982-querelle</t>
-  </si>
-  <si>
-    <t>Types</t>
-  </si>
-  <si>
-    <t>Statuts</t>
-  </si>
-  <si>
-    <t>Court métrage</t>
-  </si>
-  <si>
-    <t>En cours</t>
-  </si>
-  <si>
-    <t>Relu</t>
-  </si>
-  <si>
-    <t>Publié</t>
-  </si>
-  <si>
-    <t>Épisode télévisé</t>
-  </si>
-  <si>
-    <t>Pièce filmée</t>
-  </si>
-  <si>
-    <t>Autre</t>
-  </si>
-  <si>
-    <t>RWF_Films.xlsx — mode d’emploi</t>
-  </si>
-  <si>
-    <t>Principe</t>
-  </si>
-  <si>
-    <t>Une ligne correspond à un film, téléfilm, série ou autre œuvre audiovisuelle.</t>
-  </si>
-  <si>
-    <t>Nom du fichier</t>
-  </si>
-  <si>
-    <t>Conserver exactement le nom RWF_Films.xlsx et placer le fichier à la racine du dépôt GitHub.</t>
-  </si>
-  <si>
-    <t>Affiches</t>
-  </si>
-  <si>
-    <t>Placer les images dans le dossier Films_images. Dans la colonne Affiche, saisir seulement le nom du fichier, par exemple maria_braun.jpg. Une URL complète reste possible.</t>
-  </si>
-  <si>
-    <t>Saisir une URL complète ou un nom de fichier présent dans Frise_extraits. Plusieurs extraits peuvent être séparés par |.</t>
-  </si>
-  <si>
-    <t>Champs multiples</t>
-  </si>
-  <si>
-    <t>Séparer plusieurs noms, références ou années par le caractère |. Les retours à la ligne sont également acceptés.</t>
-  </si>
-  <si>
-    <t>Indiquer les identifiants d’années de la frise, par exemple 1978|1979. Un bouton permettra d’ouvrir directement l’année correspondante.</t>
-  </si>
-  <si>
-    <t>Une référence par ligne ou séparée par |. Ajouter une URL dans la colonne Sources lorsqu’elle existe.</t>
-  </si>
-  <si>
-    <t>Identifiant stable, unique et sans espaces. Ne pas le modifier une fois les liens créés.</t>
-  </si>
-  <si>
-    <t>À compléter, En cours, Relu ou Publié. Ce champ sert au suivi éditorial et n’est pas affiché dans la fiche publique.</t>
-  </si>
-  <si>
-    <t>Source de l’enrichissement</t>
-  </si>
-  <si>
-    <t>RWF_Notes sur les films.docx. Les sections intitulées « Notes » n’ont pas été reprises.</t>
-  </si>
-  <si>
-    <t>Contenu importé</t>
-  </si>
-  <si>
-    <t>Synopsis, fiches techniques, distributions et analyses explicitement séparées des sections « Notes ».</t>
-  </si>
-  <si>
-    <t>Chinesisches Roulette</t>
   </si>
   <si>
     <t>Ila von Hasperg</t>
@@ -1022,13 +824,289 @@
     <t>Le château devient un huis clos où vitrines, miroirs, meubles transparents, surcadrages et travellings circulaires enferment les personnages dans un réseau de regards et recomposent sans cesse les alliances. Angela utilise le jeu pour rendre visibles les mensonges, la haine familiale et la violence exercée sur l’enfant handicapée. Les allusions au IIIe Reich font affleurer, sous la respectabilité bourgeoise, une mémoire refoulée dont la violence éclate sans produire de résolution.</t>
   </si>
   <si>
+    <t>Films_images/Roulette_chinoise.jpg</t>
+  </si>
+  <si>
     <t>famille|adultère|huis clos|jeu|cruauté|handicap|nazisme|mémoire|miroirs|surcadrage</t>
   </si>
   <si>
+    <t>film-1976-roulette-chinoise</t>
+  </si>
+  <si>
+    <t>rwf-1976-je-veux-seulement-que-vous-maimiez</t>
+  </si>
+  <si>
+    <t>Je veux seulement que vous m’aimiez</t>
+  </si>
+  <si>
+    <t>Films_images/Je_veux_seulement_que_vous_m_aimiez.jpg</t>
+  </si>
+  <si>
+    <t>film-1976-je-veux-seulement-que-vous-m-aimiez</t>
+  </si>
+  <si>
+    <t>rwf-1977-femmes-a-new-york</t>
+  </si>
+  <si>
+    <t>Femmes à New York</t>
+  </si>
+  <si>
+    <t>1977</t>
+  </si>
+  <si>
+    <t>film-1977-femmes-a-new-york</t>
+  </si>
+  <si>
+    <t>rwf-1977-la-femme-du-chef-de-gare</t>
+  </si>
+  <si>
+    <t>La Femme du chef de gare</t>
+  </si>
+  <si>
+    <t>film-1977-la-femme-du-chef-de-gare</t>
+  </si>
+  <si>
+    <t>rwf-1978-lallemagne-en-automne</t>
+  </si>
+  <si>
+    <t>L’Allemagne en automne</t>
+  </si>
+  <si>
+    <t>Film collectif</t>
+  </si>
+  <si>
+    <t>Films_images/L_Allemagne_en_automne.jpg</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>film-1978-l-allemagne-en-automne</t>
+  </si>
+  <si>
+    <t>rwf-1978-despair</t>
+  </si>
+  <si>
+    <t>Despair</t>
+  </si>
+  <si>
+    <t>Films_images/Despair.jpg</t>
+  </si>
+  <si>
+    <t>film-1978-despair</t>
+  </si>
+  <si>
+    <t>rwf-1978-lannee-des-treize-lunes</t>
+  </si>
+  <si>
+    <t>L’Année des treize lunes</t>
+  </si>
+  <si>
+    <t>Films_images/L_Annee_des_treize_lunes.jpg</t>
+  </si>
+  <si>
+    <t>film-1978-l-annee-des-treize-lunes</t>
+  </si>
+  <si>
+    <t>rwf-1978-maria-braun</t>
+  </si>
+  <si>
+    <t>Le Mariage de Maria Braun</t>
+  </si>
+  <si>
+    <t>Die Ehe der Maria Braun</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Mariage_de_Maria_Braun.jpg</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>film-1979-le-mariage-de-maria-braun</t>
+  </si>
+  <si>
+    <t>rwf-1979-la-troisieme-generation</t>
+  </si>
+  <si>
+    <t>La Troisième génération</t>
+  </si>
+  <si>
+    <t>Films_images/La_Troisieme_generation.jpg</t>
+  </si>
+  <si>
+    <t>film-1979-la-troisieme-generation</t>
+  </si>
+  <si>
+    <t>rwf-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>Films_images/Berlin_Alexanderplatz.jpg</t>
+  </si>
+  <si>
+    <t>1980</t>
+  </si>
+  <si>
+    <t>film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>rwf-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>Lili Marleen</t>
+  </si>
+  <si>
+    <t>Films_images/Lili_Marleen.jpg</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>rwf-1981-theatre-en-transe</t>
+  </si>
+  <si>
+    <t>Théâtre en transe</t>
+  </si>
+  <si>
+    <t>Documentaire</t>
+  </si>
+  <si>
+    <t>film-1981-theatre-en-transe</t>
+  </si>
+  <si>
+    <t>rwf-1981-lola-une-femme-allemande</t>
+  </si>
+  <si>
+    <t>Lola, une femme allemande</t>
+  </si>
+  <si>
+    <t>Films_images/Lola_une_femme_allemande.jpg</t>
+  </si>
+  <si>
+    <t>film-1981-lola-une-femme-allemande</t>
+  </si>
+  <si>
+    <t>rwf-1982-veronika-voss</t>
+  </si>
+  <si>
+    <t>Le Secret de Veronika Voss</t>
+  </si>
+  <si>
+    <t>Die Sehnsucht der Veronika Voss</t>
+  </si>
+  <si>
+    <t>Films_images/Le_Secret_de_Veronika_Voss.jpg</t>
+  </si>
+  <si>
+    <t>film-1981-le-secret-de-veronika-voss</t>
+  </si>
+  <si>
+    <t>rwf-1982-querelle</t>
+  </si>
+  <si>
+    <t>Querelle</t>
+  </si>
+  <si>
+    <t>Films_images/Querelle.jpg</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>film-1982-querelle</t>
+  </si>
+  <si>
+    <t>Types</t>
+  </si>
+  <si>
+    <t>Statuts</t>
+  </si>
+  <si>
+    <t>Court métrage</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>Relu</t>
+  </si>
+  <si>
+    <t>Publié</t>
+  </si>
+  <si>
+    <t>Épisode télévisé</t>
+  </si>
+  <si>
+    <t>Pièce filmée</t>
+  </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>RWF_Films.xlsx — mode d’emploi</t>
+  </si>
+  <si>
+    <t>Principe</t>
+  </si>
+  <si>
+    <t>Une ligne correspond à un film, téléfilm, série ou autre œuvre audiovisuelle.</t>
+  </si>
+  <si>
+    <t>Nom du fichier</t>
+  </si>
+  <si>
+    <t>Conserver exactement le nom RWF_Films.xlsx et placer le fichier à la racine du dépôt GitHub.</t>
+  </si>
+  <si>
+    <t>Affiches</t>
+  </si>
+  <si>
+    <t>Placer les images dans le dossier Films_images. Dans la colonne Affiche, saisir seulement le nom du fichier, par exemple maria_braun.jpg. Une URL complète reste possible.</t>
+  </si>
+  <si>
+    <t>Saisir une URL complète ou un nom de fichier présent dans Frise_extraits. Plusieurs extraits peuvent être séparés par |.</t>
+  </si>
+  <si>
+    <t>Champs multiples</t>
+  </si>
+  <si>
+    <t>Séparer plusieurs noms, références ou années par le caractère |. Les retours à la ligne sont également acceptés.</t>
+  </si>
+  <si>
+    <t>Indiquer les identifiants d’années de la frise, par exemple 1978|1979. Un bouton permettra d’ouvrir directement l’année correspondante.</t>
+  </si>
+  <si>
     <t>Saisir une personne par ligne au format Nom canonique : rôle.</t>
   </si>
   <si>
     <t>Pour les fonctions non couvertes par une colonne spécialisée, saisir Fonction : noms, avec une fonction par ligne.</t>
+  </si>
+  <si>
+    <t>Une référence par ligne ou séparée par |. Ajouter une URL dans la colonne Sources lorsqu’elle existe.</t>
+  </si>
+  <si>
+    <t>Identifiant stable, unique et sans espaces. Ne pas le modifier une fois les liens créés.</t>
+  </si>
+  <si>
+    <t>À compléter, En cours, Relu ou Publié. Ce champ sert au suivi éditorial et n’est pas affiché dans la fiche publique.</t>
+  </si>
+  <si>
+    <t>Source de l’enrichissement</t>
+  </si>
+  <si>
+    <t>RWF_Notes sur les films.docx. Les sections intitulées « Notes » n’ont pas été reprises.</t>
+  </si>
+  <si>
+    <t>Contenu importé</t>
+  </si>
+  <si>
+    <t>Synopsis, fiches techniques, distributions et analyses explicitement séparées des sections « Notes ».</t>
   </si>
   <si>
     <t>Liaison automatique</t>
@@ -1816,13 +1894,121 @@
     <t>Volker.jpg</t>
   </si>
   <si>
+    <t>Ich will doch nur, daß ihr mich liebt</t>
+  </si>
+  <si>
+    <t>Bavaria Atelier GmbH pour la WDR</t>
+  </si>
+  <si>
+    <t>Vitus Zeplichal : Peter
+Elke Aberle : Erika
+Alexander Allerson : le père
+Erni Mangold : la mère
+Johanna Hofer : la grand-mère
+Katharina Buchhammer : Ulla
+Wolfgang Hess : le chef de chantier
+Armin Meier : le contremaître
+Erika Runge : la psychologue
+Ulrich Radke : le père d’Erika
+Annemarie Wendl : la mère d’Erika
+Janos Gönczöl : le tenancier
+Edith Volkmann : la tenancière
+Robert Naegele : l’huissier
+Axel Ganz : le concierge
+Inge Schulz : Mme Emmerich
+Heinz H. Bernstein : le vendeur de meubles
+Helga Bender : la vendeuse dans la boutique
+Adi Gruber : l’employé des postes
+Ingrid Caven : la vendeuse de machines à tricoter
+Sonja Neudorres : la bijoutière
+Reinhard Brex : l’entrepreneur
+Lilo Pempeit : la dame à la poste</t>
+  </si>
+  <si>
+    <t>Adaptation : d’après une histoire tirée de Lebenslänglich — Protokolle aus der Haft de Klaus Antes et Christiane Ehrhardt
+Assistants à la réalisation : Renate Leiffer ; Christian Hohoff
+Production exécutive : Peter Märthesheimer
+Son : Karsten Ullrich
+Format : 16 mm, couleur
+Genre : drame
+Tournage : 25 jours, novembre-décembre 1975, Munich et environs
+Diffusion : 23 mars 1976 (ARD)</t>
+  </si>
+  <si>
+    <t>Peter Trepper, condamné à dix ans de prison pour homicide, raconte son histoire à une psychologue. Privé d’affection par ses parents, il cherche à gagner l’amour de son épouse Erika par son travail, les cadeaux et une consommation à crédit qui l’endette toujours davantage. Épuisé par le surtravail et incapable de demander de l’aide, il finit par tuer un cafetier qui maltraite un jeune homme.</t>
+  </si>
+  <si>
+    <t>Peter tente d’acheter par son travail et ses cadeaux une affection dont il a été privé : chez Fassbinder, l’argent, les objets et les sentiments sont incommensurables. L’engrenage du crédit et du surtravail inscrit sa détresse dans le « miracle économique » ouest-allemand, construit au prix des relations humaines. Les retours en arrière, les brefs aperçus anticipés, les fleurs et les miroirs empruntent au mélodrame tout en révélant les origines quotidiennes de la violence et de la folie.</t>
+  </si>
+  <si>
+    <t>amour|famille|travail|argent|crédit|consommation|surtravail|violence|folie|mélodrame|fleurs|miroirs</t>
+  </si>
+  <si>
+    <t>Film collectif : Alf Brustellin ; Bernhard Sinkel ; Rainer Werner Fassbinder ; Alexander Kluge ; Maximiliane Mainka ; Edgar Reitz ; Beate Mainka-Jellinghaus ; Peter Schubert ; Hans Peter Cloos ; Katja Rupé ; Volker Schlöndorff
+Format : 1,66:1, mono
+Genre : drame, documentaire
+Sortie : mars 1978</t>
+  </si>
+  <si>
+    <t>Premier film consacré à la Fraction armée rouge, L’Allemagne en automne réunit plusieurs cinéastes du Nouveau cinéma allemand. Dans son segment autofictionnel, Fassbinder met en scène son travail, son couple et sa mère pour confronter l’artiste et la société allemande aux événements de l’automne 1977, à la question de l’engagement et au poids de la mémoire historique.</t>
+  </si>
+  <si>
+    <t>Fassbinder expose la contradiction entre son analyse politique et un comportement intime ambivalent, violent et irrationnel, notamment dans sa relation avec Armin Meier. Armin et la mère du cinéaste incarnent deux formes de « bon sens » allemand où la défense de la démocratie coexiste avec l’acceptation de la violence policière et le désir d’autorité. Le huis clos obscur, les cadres serrés et les surcadrages composent ainsi l’autoportrait crépusculaire d’un artiste impuissant, où l’intime, le politique et la création demeurent indissociables.</t>
+  </si>
+  <si>
+    <t>Fraction armée rouge|terrorisme|autofiction|engagement|démocratie|autorité|mémoire|couple|autoportrait|intime|politique|huis clos</t>
+  </si>
+  <si>
+    <t>Despair – Eine Reise ins Licht</t>
+  </si>
+  <si>
+    <t>Tom Stoppard, d’après La Méprise de Vladimir Nabokov</t>
+  </si>
+  <si>
+    <t>Dirk Bogarde : Hermann Hermann
+Andréa Ferréol : Lydia
+Klaus Löwitsch : Felix Weber
+Volker Spengler : Ardalion
+Peter Kern : Müller
+Alexander Allerson : Mayer
+Gottfried John : Perebrodov
+Hark Bohm : le docteur
+Bernhard Wicki : Orlovius
+Isolde Barth
+Ingrid Caven : la réceptionniste de l’hôtel
+Adrian Hoven : l’inspecteur Schelling
+Roger Fritz : l’inspecteur Braun
+Voli Geiller : Madame
+Hans Zander : le frère de Müller</t>
+  </si>
+  <si>
+    <t>Langue : anglais
+Format : couleur
+Sortie : 19 mai 1978</t>
+  </si>
+  <si>
+    <t>Dans l’Allemagne des années 1930, Hermann Hermann, magnat du chocolat et émigré russe, s’enfonce lentement dans la folie.</t>
+  </si>
+  <si>
+    <t>En adaptant Nabokov, Fassbinder transforme le récit du double en crise de l’identification : vitres, miroirs, zooms et décalages spatiaux rendent la perception instable et empêchent Hermann de s’inscrire dans un espace classique. Le récit labyrinthique repose sur des répétitions, des échos et des identités flottantes, jusqu’à la rupture finale de la fiction face à la caméra. La folie du bourgeois, l’impuissance sexuelle et le rêve de fusion se nouent à l’ascension du nazisme et à une lecture du fascisme comme forme extrême du capitalisme de monopole.</t>
+  </si>
+  <si>
+    <t>double|folie|identité|perception|labyrinthe|miroirs|nazisme|capitalisme|homosexualité|adaptation|Nabokov|cinéma</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t xml:space="preserve">Le film dénonce la violence exercée par une société étriquée contre les étrnagers, violence que le personnage principal, d'origine grecque, reconduit avec des individus encore plus dominés que lui. Film à l'esthétique avant-gardiste, brechtienne par son caractère anti-illustionniste. Il est constitué d'une suite de brefs tableaux, d'images figées, de plans fontaux. Les mouvements de caméra sont rares : des travellings latéraux, sans profondeur d'images, conservent une forme de théâtralité à l'image. Comme d'autres films  de RWF de la période, </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Carlito"/>
       </rPr>
       <t xml:space="preserve">Le bouc </t>
@@ -1830,95 +2016,18 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Carlito"/>
       </rPr>
       <t xml:space="preserve">vise un public qui n'est ni restreint et cinéphile, ni populaire.  </t>
     </r>
-  </si>
-  <si>
-    <t>Films_images/L_Amour_est_plus_froid_que_la_mort.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Bouc.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Les_Dieux_de_la_peste.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Soldat_americain.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Prenez_garde_a_la_sainte_putain.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Marchand_des_quatre_saisons.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Les_Larmes_ameres_de_Petra_von_Kant.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Monde_sur_un_fil.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Tous_les_autres_s_appellent_Ali.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Effi_Briest.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Droit_du_plus_fort.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Maman_Kusters_s_en_va_au_ciel.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/L_Ombre_des_anges.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Roti_de_Satan.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Roulette_chinoise.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Je_veux_seulement_que_vous_m_aimiez.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/L_Allemagne_en_automne.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Despair.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/L_Annee_des_treize_lunes.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Mariage_de_Maria_Braun.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/La_Troisieme_generation.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Berlin_Alexanderplatz.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Lili_Marleen.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Lola_une_femme_allemande.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Le_Secret_de_Veronika_Voss.jpg</t>
-  </si>
-  <si>
-    <t>Films_images/Querelle.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1958,8 +2067,14 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -2027,12 +2142,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2051,20 +2160,383 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFF3F6F8"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2079,40 +2551,36 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA41" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="19"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="11"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="6"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="4"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2290,7 +2758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2320,86 +2788,86 @@
     <col min="31" max="31" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="60.25" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:30" ht="80.25" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -2412,2543 +2880,2599 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="128" customHeight="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="11">
         <v>1969</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4" t="s">
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="AB2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC2" s="9" t="str">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="7" t="str">
         <f>IF(O2="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O2)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O2)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O2)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O2)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O2)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O2)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O2)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O2)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O2)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O2)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O2)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O2)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O2)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O2)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O2)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O2)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O2)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O2)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O2)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O2)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O2)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O2)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O2)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD2" s="9" t="str">
+      <c r="AD2" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H2:N2,P2),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="128" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="5">
+      <c r="C3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="11">
         <v>1969</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="AB3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC3" s="9" t="str">
+        <v>44</v>
+      </c>
+      <c r="AC3" s="7" t="str">
         <f>IF(O3="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O3)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O3)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O3)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O3)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O3)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O3)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O3)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O3)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O3)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O3)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O3)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O3)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O3)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O3)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O3)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O3)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O3)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O3)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O3)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O3)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O3)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O3)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O3)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD3" s="9" t="str">
+      <c r="AD3" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H3:N3,P3),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="128" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5">
+    <row r="4" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11">
         <v>1970</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4" t="s">
-        <v>37</v>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC4" s="9" t="str">
+        <v>49</v>
+      </c>
+      <c r="AC4" s="7" t="str">
         <f>IF(O4="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O4)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O4)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O4)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O4)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O4)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O4)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O4)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O4)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O4)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O4)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O4)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O4)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O4)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O4)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O4)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O4)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O4)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O4)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O4)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O4)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O4)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O4)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O4)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD4" s="9" t="str">
+      <c r="AD4" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H4:N4,P4),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="128" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11">
+        <v>1970</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5">
-        <v>1970</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4" t="s">
-        <v>37</v>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC5" s="9" t="str">
+        <v>52</v>
+      </c>
+      <c r="AC5" s="7" t="str">
         <f>IF(O5="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O5)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O5)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O5)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O5)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O5)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O5)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O5)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O5)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O5)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O5)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O5)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O5)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O5)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O5)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O5)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O5)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O5)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O5)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O5)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O5)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O5)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O5)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O5)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD5" s="9" t="str">
+      <c r="AD5" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H5:N5,P5),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="128" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5">
+    <row r="6" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11">
         <v>1970</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4" t="s">
-        <v>37</v>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC6" s="9" t="str">
+        <v>56</v>
+      </c>
+      <c r="AC6" s="7" t="str">
         <f>IF(O6="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O6)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O6)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O6)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O6)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O6)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O6)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O6)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O6)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O6)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O6)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O6)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O6)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O6)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O6)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O6)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O6)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O6)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O6)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O6)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O6)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O6)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O6)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O6)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD6" s="9" t="str">
+      <c r="AD6" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H6:N6,P6),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="128" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5">
+    <row r="7" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11">
         <v>1970</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4" t="s">
-        <v>37</v>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC7" s="9" t="str">
+        <v>60</v>
+      </c>
+      <c r="AC7" s="7" t="str">
         <f>IF(O7="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O7)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O7)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O7)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O7)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O7)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O7)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O7)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O7)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O7)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O7)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O7)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O7)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O7)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O7)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O7)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O7)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O7)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O7)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O7)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O7)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O7)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O7)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O7)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD7" s="9" t="str">
+      <c r="AD7" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H7:N7,P7),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="128" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5">
+    <row r="8" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11">
         <v>1971</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="11"/>
+      <c r="G8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4" t="s">
-        <v>37</v>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC8" s="9" t="str">
+        <v>64</v>
+      </c>
+      <c r="AC8" s="7" t="str">
         <f>IF(O8="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O8)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O8)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O8)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O8)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O8)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O8)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O8)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O8)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O8)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O8)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O8)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O8)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O8)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O8)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O8)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O8)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O8)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O8)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O8)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O8)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O8)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O8)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O8)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD8" s="9" t="str">
+      <c r="AD8" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H8:N8,P8),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="128" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5">
+    <row r="9" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11">
         <v>1971</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4" t="s">
-        <v>37</v>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC9" s="9" t="str">
+        <v>68</v>
+      </c>
+      <c r="AC9" s="7" t="str">
         <f>IF(O9="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O9)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O9)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O9)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O9)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O9)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O9)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O9)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O9)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O9)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O9)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O9)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O9)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O9)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O9)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O9)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O9)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O9)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O9)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O9)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O9)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O9)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O9)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O9)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD9" s="9" t="str">
+      <c r="AD9" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H9:N9,P9),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="128" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5">
+    <row r="10" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11">
         <v>1971</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4" t="s">
+      <c r="E10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4" t="s">
-        <v>37</v>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC10" s="9" t="str">
+        <v>71</v>
+      </c>
+      <c r="AC10" s="7" t="str">
         <f>IF(O10="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O10)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O10)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O10)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O10)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O10)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O10)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O10)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O10)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O10)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O10)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O10)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O10)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O10)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O10)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O10)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O10)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O10)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O10)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O10)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O10)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O10)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O10)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O10)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD10" s="9" t="str">
+      <c r="AD10" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H10:N10,P10),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="128" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="5">
+    <row r="11" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="11">
         <v>1972</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4" t="s">
-        <v>37</v>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC11" s="9" t="str">
+        <v>77</v>
+      </c>
+      <c r="AC11" s="7" t="str">
         <f>IF(O11="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O11)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O11)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O11)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O11)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O11)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O11)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O11)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O11)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O11)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O11)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O11)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O11)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O11)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O11)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O11)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O11)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O11)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O11)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O11)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O11)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O11)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O11)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O11)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD11" s="9" t="str">
+      <c r="AD11" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H11:N11,P11),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="128" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="5">
+    <row r="12" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="11">
         <v>1972</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4" t="s">
-        <v>37</v>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC12" s="9" t="str">
+        <v>82</v>
+      </c>
+      <c r="AC12" s="7" t="str">
         <f>IF(O12="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O12)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O12)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O12)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O12)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O12)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O12)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O12)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O12)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O12)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O12)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O12)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O12)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O12)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O12)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O12)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O12)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O12)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O12)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O12)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O12)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O12)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O12)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O12)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD12" s="9" t="str">
+      <c r="AD12" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H12:N12,P12),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="128" customHeight="1">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11">
+        <v>1972</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5">
-        <v>1972</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4" t="s">
-        <v>37</v>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC13" s="9" t="str">
+        <v>85</v>
+      </c>
+      <c r="AC13" s="7" t="str">
         <f>IF(O13="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O13)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O13)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O13)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O13)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O13)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O13)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O13)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O13)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O13)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O13)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O13)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O13)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O13)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O13)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O13)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O13)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O13)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O13)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O13)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O13)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O13)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O13)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O13)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD13" s="9" t="str">
+      <c r="AD13" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H13:N13,P13),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="128" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="5">
+    <row r="14" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="11">
         <v>1972</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="E14" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="11">
         <v>467</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y14" s="4" t="s">
+      <c r="J14" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="Z14" s="4" t="s">
+      <c r="K14" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="AA14" s="4" t="s">
+      <c r="L14" s="10" t="s">
         <v>92</v>
       </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y14" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z14" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA14" s="10" t="s">
+        <v>100</v>
+      </c>
       <c r="AB14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC14" s="9" t="str">
+        <v>101</v>
+      </c>
+      <c r="AC14" s="7" t="str">
         <f>IF(O14="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O14)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O14)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O14)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O14)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O14)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O14)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O14)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O14)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O14)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O14)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O14)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O14)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O14)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O14)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O14)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O14)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O14)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O14)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O14)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O14)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O14)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O14)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O14)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-gottfried-john; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
-      <c r="AD14" s="9" t="str">
+      <c r="AD14" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H14:N14,P14),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="128" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5">
+    <row r="15" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A15" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11">
         <v>1973</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="4" t="s">
+      <c r="E15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4" t="s">
-        <v>37</v>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC15" s="9" t="str">
+        <v>105</v>
+      </c>
+      <c r="AC15" s="7" t="str">
         <f>IF(O15="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O15)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O15)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O15)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O15)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O15)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O15)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O15)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O15)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O15)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O15)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O15)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O15)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O15)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O15)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O15)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O15)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O15)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O15)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O15)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O15)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O15)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O15)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O15)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD15" s="9" t="str">
+      <c r="AD15" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H15:N15,P15),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="128" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="11">
+        <v>1973</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="11">
+        <v>212</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y16" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z16" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1973</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="5">
-        <v>212</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="U16" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y16" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z16" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA16" s="4" t="s">
-        <v>107</v>
+      <c r="AA16" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC16" s="9" t="str">
+        <v>117</v>
+      </c>
+      <c r="AC16" s="7" t="str">
         <f>IF(O16="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O16)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O16)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O16)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O16)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O16)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O16)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O16)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O16)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O16)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O16)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O16)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O16)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O16)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O16)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O16)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O16)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O16)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O16)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O16)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O16)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O16)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O16)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O16)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD16" s="9" t="str">
+      <c r="AD16" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H16:N16,P16),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="128" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="5">
+    <row r="17" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A17" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="11">
         <v>1974</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="11">
         <v>93</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA17" s="4" t="s">
-        <v>92</v>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y17" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z17" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA17" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC17" s="9" t="str">
+        <v>127</v>
+      </c>
+      <c r="AC17" s="7" t="str">
         <f>IF(O17="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O17)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O17)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O17)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O17)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O17)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O17)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O17)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O17)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O17)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O17)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O17)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O17)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O17)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O17)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O17)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O17)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O17)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O17)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O17)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O17)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O17)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O17)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O17)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira; pers-barbara-valentin</v>
       </c>
-      <c r="AD17" s="9" t="str">
+      <c r="AD17" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H17:N17,P17),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="128" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" s="5">
+    <row r="18" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="11">
         <v>1974</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="11">
         <v>140</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4" t="s">
+      <c r="I18" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P18" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q18" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="P18" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA18" s="4" t="s">
-        <v>92</v>
+      <c r="Y18" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA18" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC18" s="9" t="str">
+        <v>140</v>
+      </c>
+      <c r="AC18" s="7" t="str">
         <f>IF(O18="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O18)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O18)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O18)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O18)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O18)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O18)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O18)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O18)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O18)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O18)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O18)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O18)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O18)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O18)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O18)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O18)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O18)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O18)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O18)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O18)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O18)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O18)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O18)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-karlheinz-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz; pers-barbara-valentin</v>
       </c>
-      <c r="AD18" s="9" t="str">
+      <c r="AD18" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H18:N18,P18),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="30">
-      <c r="A19" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5">
+    <row r="19" spans="1:30" ht="32">
+      <c r="A19" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11">
         <v>1974</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="4" t="s">
+      <c r="E19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4" t="s">
-        <v>37</v>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC19" s="9" t="str">
+        <v>143</v>
+      </c>
+      <c r="AC19" s="7" t="str">
         <f>IF(O19="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O19)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O19)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O19)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O19)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O19)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O19)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O19)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O19)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O19)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O19)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O19)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O19)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O19)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O19)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O19)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O19)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O19)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O19)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O19)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O19)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O19)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O19)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O19)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD19" s="9" t="str">
+      <c r="AD19" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H19:N19,P19),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="150">
-      <c r="A20" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="5">
+    <row r="20" spans="1:30" ht="160">
+      <c r="A20" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="11">
         <v>1974</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="5">
+      <c r="E20" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="11">
         <v>116</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y20" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z20" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA20" s="4" t="s">
+      <c r="I20" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>92</v>
       </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="O20" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P20" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q20" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z20" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA20" s="10" t="s">
+        <v>100</v>
+      </c>
       <c r="AB20" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC20" s="9" t="str">
+        <v>156</v>
+      </c>
+      <c r="AC20" s="7" t="str">
         <f>IF(O20="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O20)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O20)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O20)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O20)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O20)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O20)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O20)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O20)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O20)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O20)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O20)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O20)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O20)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O20)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O20)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O20)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O20)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O20)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O20)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O20)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O20)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O20)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O20)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab; pers-barbara-valentin</v>
       </c>
-      <c r="AD20" s="9" t="str">
+      <c r="AD20" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H20:N20,P20),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="255">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:30" ht="272">
+      <c r="A21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1975</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="11">
+        <v>123</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="J21" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1975</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="5">
-        <v>123</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z21" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA21" s="4" t="s">
-        <v>92</v>
+      <c r="K21" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y21" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA21" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC21" s="9" t="str">
+        <v>170</v>
+      </c>
+      <c r="AC21" s="7" t="str">
         <f>IF(O21="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O21)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O21)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O21)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O21)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O21)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O21)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O21)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O21)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O21)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O21)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O21)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O21)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O21)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O21)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O21)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O21)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O21)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O21)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O21)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O21)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O21)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O21)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O21)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-harry-baer; pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab; pers-barbara-valentin</v>
       </c>
-      <c r="AD21" s="9" t="str">
+      <c r="AD21" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H21:N21,P21),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="240">
-      <c r="A22" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="4" t="s">
+    <row r="22" spans="1:30" ht="256">
+      <c r="A22" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1975</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="11">
+        <v>120</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="M22" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1975</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="5">
-        <v>120</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4" t="s">
+      <c r="N22" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P22" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q22" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="T22" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="U22" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="T22" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y22" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA22" s="4" t="s">
-        <v>92</v>
+      <c r="Y22" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z22" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA22" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AC22" s="9" t="str">
+        <v>183</v>
+      </c>
+      <c r="AC22" s="7" t="str">
         <f>IF(O22="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O22)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O22)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O22)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O22)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O22)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O22)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O22)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O22)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O22)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O22)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O22)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O22)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O22)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O22)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O22)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O22)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O22)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O22)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O22)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O22)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O22)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O22)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O22)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
       </c>
-      <c r="AD22" s="9" t="str">
+      <c r="AD22" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H22:N22,P22),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="30">
-      <c r="A23" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5">
+    <row r="23" spans="1:30" ht="48">
+      <c r="A23" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="11">
         <v>1975</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4" t="s">
+      <c r="E23" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4" t="s">
-        <v>37</v>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC23" s="9" t="str">
+        <v>186</v>
+      </c>
+      <c r="AC23" s="7" t="str">
         <f>IF(O23="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O23)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O23)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O23)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O23)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O23)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O23)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O23)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O23)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O23)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O23)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O23)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O23)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O23)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O23)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O23)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O23)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O23)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O23)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O23)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O23)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O23)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O23)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O23)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD23" s="9" t="str">
+      <c r="AD23" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H23:N23,P23),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="30">
-      <c r="A24" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5">
+    <row r="24" spans="1:30" ht="32">
+      <c r="A24" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11">
         <v>1975</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="4" t="s">
+      <c r="E24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4" t="s">
-        <v>37</v>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AA24" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC24" s="9" t="str">
+        <v>189</v>
+      </c>
+      <c r="AC24" s="7" t="str">
         <f>IF(O24="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O24)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O24)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O24)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O24)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O24)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O24)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O24)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O24)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O24)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O24)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O24)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O24)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O24)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O24)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O24)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O24)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O24)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O24)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O24)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O24)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O24)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O24)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O24)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD24" s="9" t="str">
+      <c r="AD24" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H24:N24,P24),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="30">
-      <c r="A25" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5">
+    <row r="25" spans="1:30" ht="32">
+      <c r="A25" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="11">
         <v>1976</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="11"/>
+      <c r="G25" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4" t="s">
-        <v>37</v>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+      <c r="AA25" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC25" s="9" t="str">
+        <v>194</v>
+      </c>
+      <c r="AC25" s="7" t="str">
         <f>IF(O25="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O25)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O25)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O25)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O25)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O25)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O25)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O25)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O25)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O25)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O25)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O25)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O25)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O25)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O25)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O25)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O25)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O25)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O25)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O25)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O25)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O25)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O25)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O25)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD25" s="9" t="str">
+      <c r="AD25" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H25:N25,P25),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="210">
-      <c r="A26" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="5">
+    <row r="26" spans="1:30" ht="224">
+      <c r="A26" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="11">
         <v>1976</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="11">
         <v>112</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="T26" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>92</v>
+      <c r="J26" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="T26" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="U26" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y26" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA26" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AC26" s="9" t="str">
+        <v>207</v>
+      </c>
+      <c r="AC26" s="7" t="str">
         <f>IF(O26="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O26)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O26)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O26)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O26)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O26)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O26)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O26)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O26)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O26)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O26)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O26)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O26)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O26)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O26)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O26)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O26)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O26)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O26)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O26)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O26)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O26)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O26)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O26)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
       </c>
-      <c r="AD26" s="9" t="str">
+      <c r="AD26" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H26:N26,P26),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="150">
-      <c r="A27" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D27" s="5">
+    <row r="27" spans="1:30" ht="160">
+      <c r="A27" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D27" s="11">
         <v>1976</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="11">
         <v>96</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="G27" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y27" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="Z27" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA27" s="4" t="s">
-        <v>92</v>
+      <c r="J27" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y27" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA27" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC27" s="9" t="str">
+        <v>220</v>
+      </c>
+      <c r="AC27" s="7" t="str">
         <f>IF(O27="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O27)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O27)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O27)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O27)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O27)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O27)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O27)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O27)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O27)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O27)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O27)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O27)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O27)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O27)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O27)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O27)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O27)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O27)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O27)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O27)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O27)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O27)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O27)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-volker-spengler</v>
       </c>
-      <c r="AD27" s="9" t="str">
+      <c r="AD27" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H27:N27,P27),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="45">
-      <c r="A28" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5">
+    <row r="28" spans="1:30" ht="380">
+      <c r="A28" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D28" s="11">
         <v>1976</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="4" t="s">
+      <c r="E28" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="11">
+        <v>104</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4" t="s">
-        <v>37</v>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q28" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y28" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="Z28" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA28" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AC28" s="9" t="str">
+        <v>224</v>
+      </c>
+      <c r="AC28" s="7" t="str">
         <f>IF(O28="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O28)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O28)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O28)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O28)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O28)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O28)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O28)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O28)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O28)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O28)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O28)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O28)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O28)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O28)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O28)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O28)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O28)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O28)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O28)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O28)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O28)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O28)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O28)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
-      </c>
-      <c r="AD28" s="9" t="str">
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-armin-meier</v>
+      </c>
+      <c r="AD28" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H28:N28,P28),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="30">
-      <c r="A29" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5">
+        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="32">
+      <c r="A29" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="11">
         <v>1977</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="4" t="s">
+      <c r="E29" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4" t="s">
-        <v>37</v>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+      <c r="AA29" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC29" s="9" t="str">
+        <v>228</v>
+      </c>
+      <c r="AC29" s="7" t="str">
         <f>IF(O29="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O29)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O29)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O29)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O29)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O29)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O29)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O29)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O29)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O29)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O29)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O29)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O29)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O29)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O29)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O29)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O29)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O29)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O29)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O29)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O29)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O29)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O29)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O29)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD29" s="9" t="str">
+      <c r="AD29" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H29:N29,P29),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="45">
-      <c r="A30" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5">
+    <row r="30" spans="1:30" ht="48">
+      <c r="A30" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="11">
         <v>1977</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="4" t="s">
+      <c r="E30" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="11"/>
+      <c r="G30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4" t="s">
-        <v>37</v>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AA30" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC30" s="9" t="str">
+        <v>231</v>
+      </c>
+      <c r="AC30" s="7" t="str">
         <f>IF(O30="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O30)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O30)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O30)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O30)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O30)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O30)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O30)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O30)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O30)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O30)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O30)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O30)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O30)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O30)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O30)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O30)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O30)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O30)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O30)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O30)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O30)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O30)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O30)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD30" s="9" t="str">
+      <c r="AD30" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H30:N30,P30),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="45">
-      <c r="A31" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5">
+    <row r="31" spans="1:30" ht="160">
+      <c r="A31" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="11">
         <v>1978</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="4" t="s">
+      <c r="E31" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31" s="11">
+        <v>119</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4" t="s">
-        <v>37</v>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q31" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y31" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="Z31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA31" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC31" s="9" t="str">
+        <v>237</v>
+      </c>
+      <c r="AC31" s="7" t="str">
         <f>IF(O31="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O31)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O31)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O31)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O31)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O31)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O31)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O31)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O31)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O31)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O31)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O31)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O31)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O31)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O31)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O31)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O31)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O31)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O31)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O31)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O31)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O31)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O31)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O31)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD31" s="9" t="str">
+      <c r="AD31" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H31:N31,P31),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="15">
-      <c r="A32" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5">
+    <row r="32" spans="1:30" ht="240">
+      <c r="A32" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="D32" s="11">
         <v>1978</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="4" t="s">
+      <c r="F32" s="11">
+        <v>119</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4" t="s">
-        <v>37</v>
+      <c r="I32" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q32" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="Z32" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA32" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="AC32" s="9" t="str">
+        <v>241</v>
+      </c>
+      <c r="AC32" s="7" t="str">
         <f>IF(O32="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O32)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O32)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O32)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O32)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O32)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O32)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O32)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O32)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O32)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O32)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O32)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O32)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O32)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O32)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O32)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O32)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O32)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O32)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O32)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O32)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O32)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O32)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O32)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
-      </c>
-      <c r="AD32" s="9" t="str">
+        <v>pers-ingrid-caven; pers-gottfried-john; pers-volker-spengler</v>
+      </c>
+      <c r="AD32" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H32:N32,P32),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="30">
-      <c r="A33" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5">
+    <row r="33" spans="1:30" ht="32">
+      <c r="A33" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="11">
         <v>1978</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="4" t="s">
+      <c r="F33" s="11"/>
+      <c r="G33" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4" t="s">
-        <v>37</v>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AC33" s="9" t="str">
+        <v>245</v>
+      </c>
+      <c r="AC33" s="7" t="str">
         <f>IF(O33="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O33)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O33)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O33)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O33)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O33)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O33)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O33)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O33)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O33)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O33)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O33)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O33)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O33)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O33)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O33)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O33)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O33)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O33)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O33)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O33)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O33)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O33)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O33)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD33" s="9" t="str">
+      <c r="AD33" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H33:N33,P33),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="45">
-      <c r="A34" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D34" s="5">
+    <row r="34" spans="1:30" ht="48">
+      <c r="A34" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="11">
         <v>1979</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="11"/>
+      <c r="G34" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4" t="s">
-        <v>37</v>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
+      <c r="AA34" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AC34" s="9" t="str">
+        <v>251</v>
+      </c>
+      <c r="AC34" s="7" t="str">
         <f>IF(O34="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O34)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O34)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O34)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O34)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O34)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O34)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O34)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O34)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O34)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O34)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O34)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O34)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O34)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O34)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O34)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O34)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O34)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O34)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O34)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O34)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O34)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O34)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O34)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD34" s="9" t="str">
+      <c r="AD34" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H34:N34,P34),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="45">
-      <c r="A35" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5">
+    <row r="35" spans="1:30" ht="48">
+      <c r="A35" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="11">
         <v>1979</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="4" t="s">
+      <c r="F35" s="11"/>
+      <c r="G35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4" t="s">
-        <v>37</v>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y35" s="10"/>
+      <c r="Z35" s="10"/>
+      <c r="AA35" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC35" s="9" t="str">
+        <v>255</v>
+      </c>
+      <c r="AC35" s="7" t="str">
         <f>IF(O35="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O35)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O35)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O35)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O35)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O35)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O35)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O35)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O35)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O35)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O35)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O35)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O35)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O35)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O35)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O35)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O35)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O35)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O35)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O35)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O35)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O35)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O35)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O35)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD35" s="9" t="str">
+      <c r="AD35" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H35:N35,P35),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="30">
-      <c r="A36" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D36" s="5">
+    <row r="36" spans="1:30" ht="32">
+      <c r="A36" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D36" s="11">
         <v>1980</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="4" t="s">
+      <c r="E36" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4" t="s">
-        <v>37</v>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
+      <c r="AA36" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="AC36" s="9" t="str">
+        <v>260</v>
+      </c>
+      <c r="AC36" s="7" t="str">
         <f>IF(O36="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O36)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O36)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O36)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O36)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O36)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O36)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O36)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O36)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O36)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O36)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O36)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O36)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O36)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O36)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O36)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O36)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O36)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O36)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O36)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O36)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O36)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O36)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O36)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD36" s="9" t="str">
+      <c r="AD36" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H36:N36,P36),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="30">
-      <c r="A37" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D37" s="5">
+    <row r="37" spans="1:30" ht="32">
+      <c r="A37" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D37" s="11">
         <v>1981</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="4" t="s">
+      <c r="F37" s="11"/>
+      <c r="G37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4" t="s">
-        <v>37</v>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
+      <c r="AA37" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="AC37" s="9" t="str">
+        <v>265</v>
+      </c>
+      <c r="AC37" s="7" t="str">
         <f>IF(O37="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O37)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O37)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O37)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O37)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O37)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O37)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O37)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O37)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O37)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O37)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O37)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O37)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O37)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O37)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O37)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O37)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O37)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O37)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O37)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O37)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O37)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O37)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O37)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD37" s="9" t="str">
+      <c r="AD37" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H37:N37,P37),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="30">
-      <c r="A38" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5">
+    <row r="38" spans="1:30" ht="32">
+      <c r="A38" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="11">
         <v>1981</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F38" s="5"/>
-      <c r="G38" s="4" t="s">
+      <c r="E38" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F38" s="11"/>
+      <c r="G38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4" t="s">
-        <v>37</v>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y38" s="10"/>
+      <c r="Z38" s="10"/>
+      <c r="AA38" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="AC38" s="9" t="str">
+        <v>269</v>
+      </c>
+      <c r="AC38" s="7" t="str">
         <f>IF(O38="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O38)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O38)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O38)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O38)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O38)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O38)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O38)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O38)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O38)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O38)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O38)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O38)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O38)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O38)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O38)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O38)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O38)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O38)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O38)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O38)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O38)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O38)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O38)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD38" s="9" t="str">
+      <c r="AD38" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H38:N38,P38),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="30">
-      <c r="A39" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5">
+    <row r="39" spans="1:30" ht="32">
+      <c r="A39" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="11">
         <v>1981</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="4" t="s">
+      <c r="F39" s="11"/>
+      <c r="G39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4" t="s">
-        <v>37</v>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y39" s="10"/>
+      <c r="Z39" s="10"/>
+      <c r="AA39" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AC39" s="9" t="str">
+        <v>273</v>
+      </c>
+      <c r="AC39" s="7" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD39" s="9" t="str">
+      <c r="AD39" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H39:N39,P39),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="30">
-      <c r="A40" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D40" s="5">
+    <row r="40" spans="1:30" ht="48">
+      <c r="A40" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="11">
         <v>1981</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="4" t="s">
+      <c r="F40" s="11"/>
+      <c r="G40" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4" t="s">
-        <v>37</v>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y40" s="10"/>
+      <c r="Z40" s="10"/>
+      <c r="AA40" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC40" s="9" t="str">
+        <v>278</v>
+      </c>
+      <c r="AC40" s="7" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD40" s="9" t="str">
+      <c r="AD40" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H40:N40,P40),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="15">
-      <c r="A41" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D41" s="5">
+    <row r="41" spans="1:30" ht="16">
+      <c r="A41" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D41" s="11">
         <v>1982</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H41" s="4" t="s">
+      <c r="F41" s="11"/>
+      <c r="G41" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4" t="s">
-        <v>37</v>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
+      <c r="X41" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y41" s="10"/>
+      <c r="Z41" s="10"/>
+      <c r="AA41" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="AC41" s="9" t="str">
+        <v>283</v>
+      </c>
+      <c r="AC41" s="7" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD41" s="9" t="str">
+      <c r="AD41" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H41:N41,P41),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:T18 V2:AA18">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4961,41 +5485,23 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>Listes!$A$2:$A$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E500</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
-          <x14:formula1>
-            <xm:f>Listes!$B$2:$B$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>AA2:AA500</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5003,46 +5509,46 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5053,160 +5559,160 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="60.25" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="11"/>
-    </row>
-    <row r="2" spans="1:2" ht="74.75" customHeight="1">
+    <row r="1" spans="1:2" ht="80.25" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:2" ht="99.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="74.75" customHeight="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="99.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="74.75" customHeight="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="99.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="74.75" customHeight="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="99.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="74.75" customHeight="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="99.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="74.75" customHeight="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="99.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="74.75" customHeight="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="99.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="74.75" customHeight="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="99.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="74.75" customHeight="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="99.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="74.75" customHeight="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="99.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="74.75" customHeight="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="99.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16">
-      <c r="A13" s="6" t="s">
-        <v>273</v>
+      <c r="A13" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="16">
-      <c r="A14" s="6" t="s">
-        <v>275</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="32">
+      <c r="A14" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="40" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>287</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="53.25" customHeight="1">
+      <c r="A15" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="40" customHeight="1">
-      <c r="A16" s="10" t="s">
-        <v>289</v>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="53.25" customHeight="1">
+      <c r="A16" s="8" t="s">
+        <v>315</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="61.25" customHeight="1">
-      <c r="A17" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="81.75" customHeight="1">
+      <c r="A17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="61.25" customHeight="1">
-      <c r="A18" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="81.75" customHeight="1">
+      <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="42.75" customHeight="1">
-      <c r="A19" s="10" t="s">
-        <v>293</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="57" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>319</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -5220,7 +5726,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -5229,942 +5735,942 @@
     <col min="7" max="14" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15">
+    <row r="1" spans="1:14" ht="16">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="135">
-      <c r="A2" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>310</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="160">
+      <c r="A2" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>336</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="180">
-      <c r="A3" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>137</v>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="192">
+      <c r="A3" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="75">
-      <c r="A4" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>333</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="80">
+      <c r="A4" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="45">
-      <c r="A5" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>345</v>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="48">
+      <c r="A5" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>371</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="90">
-      <c r="A6" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>356</v>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="96">
+      <c r="A6" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>382</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="180">
-      <c r="A7" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>368</v>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="192">
+      <c r="A7" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>394</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="90">
-      <c r="A8" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>379</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="96">
+      <c r="A8" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="195">
-      <c r="A9" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>390</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="208">
+      <c r="A9" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>416</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="120">
-      <c r="A10" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>401</v>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="144">
+      <c r="A10" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="150">
-      <c r="A11" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>410</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="160">
+      <c r="A11" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>436</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="105">
-      <c r="A12" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>420</v>
+        <v>444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="112">
+      <c r="A12" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>446</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="105">
-      <c r="A13" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>430</v>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="112">
+      <c r="A13" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>456</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="105">
-      <c r="A14" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>438</v>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="112">
+      <c r="A14" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>464</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="90">
-      <c r="A15" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>449</v>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="96">
+      <c r="A15" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>475</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="75">
-      <c r="A16" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>459</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="96">
+      <c r="A16" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="240">
-      <c r="A17" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>124</v>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="256">
+      <c r="A17" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="45">
-      <c r="A18" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>151</v>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="48">
+      <c r="A18" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="30">
-      <c r="A19" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>488</v>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="32">
+      <c r="A19" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>514</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="180">
-      <c r="A20" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>498</v>
+        <v>522</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="192">
+      <c r="A20" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>524</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="60">
-      <c r="A21" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>510</v>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="64">
+      <c r="A21" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>536</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="45">
-      <c r="A22" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>521</v>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="48">
+      <c r="A22" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>547</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="75">
-      <c r="A23" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>531</v>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="80">
+      <c r="A23" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>557</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="105">
-      <c r="A24" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>540</v>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="128">
+      <c r="A24" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederiquehammerli/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCF1F848-69A3-C840-8AE0-4081B9DB2FDC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="900" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="605">
   <si>
     <t>ID</t>
   </si>
@@ -2021,6 +2021,45 @@
       </rPr>
       <t xml:space="preserve">vise un public qui n'est ni restreint et cinéphile, ni populaire.  </t>
     </r>
+  </si>
+  <si>
+    <t>Collaboration ponctuelle et opportuniste</t>
+  </si>
+  <si>
+    <t>Petit chaos</t>
+  </si>
+  <si>
+    <t>Court-métrage</t>
+  </si>
+  <si>
+    <t>Le Clochard</t>
+  </si>
+  <si>
+    <t>rwf-1967-petit-chaos</t>
+  </si>
+  <si>
+    <t>rwf-1966-le-clochard</t>
+  </si>
+  <si>
+    <t>film-1966-le-clochard</t>
+  </si>
+  <si>
+    <t>film-1967-petit-chaos</t>
+  </si>
+  <si>
+    <t>rwf-1970-rio-das-mortes</t>
+  </si>
+  <si>
+    <t>Rio das mortes</t>
+  </si>
+  <si>
+    <t>Film</t>
+  </si>
+  <si>
+    <t>Rainer Werner Fassbinder et Michael Fengler</t>
+  </si>
+  <si>
+    <t>film-1970-rio-das-mortes</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2117,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2120,6 +2159,12 @@
         <fgColor rgb="FFEEF5FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2133,7 +2178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2157,6 +2202,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2170,7 +2227,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="32">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F6F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F6F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2531,13 +2602,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F6F8"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2551,36 +2615,40 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA41" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA44" headerRowDxfId="31" dataDxfId="30" totalsRowDxfId="29">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="19"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="6"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="4"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="18"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="7"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="6"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="5"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="4"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2757,8 +2825,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:AD44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2880,176 +2948,148 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:30" s="12" customFormat="1" ht="80.25" customHeight="1">
+      <c r="A2" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11">
+        <v>1966</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+    </row>
+    <row r="3" spans="1:30" s="12" customFormat="1" ht="80.25" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11">
+        <v>1967</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+    </row>
+    <row r="4" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D4" s="10">
         <v>1969</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="10" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10" t="s">
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10" t="s">
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10" t="s">
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="AC2" s="7" t="str">
-        <f>IF(O2="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O2)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O2)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O2)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O2)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O2)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O2)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O2)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O2)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O2)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O2)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O2)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O2)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O2)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O2)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O2)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O2)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O2)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O2)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O2)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O2)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O2)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O2)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O2)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
-      </c>
-      <c r="AD2" s="7" t="str">
-        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H2:N2,P2),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="11">
-        <v>1969</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC3" s="7" t="str">
-        <f>IF(O3="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O3)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O3)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O3)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O3)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O3)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O3)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O3)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O3)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O3)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O3)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O3)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O3)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O3)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O3)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O3)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O3)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O3)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O3)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O3)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O3)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O3)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O3)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O3)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
-      </c>
-      <c r="AD3" s="7" t="str">
-        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H3:N3,P3),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11">
-        <v>1970</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="AC4" s="7" t="str">
         <f>IF(O4="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O4)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O4)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O4)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O4)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O4)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O4)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O4)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O4)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O4)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O4)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O4)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O4)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O4)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O4)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O4)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O4)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O4)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O4)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O4)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O4)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O4)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O4)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O4)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3061,51 +3101,57 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A5" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11">
-        <v>1970</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="A5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1969</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10" t="s">
+      <c r="F5" s="10"/>
+      <c r="G5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AC5" s="7" t="str">
         <f>IF(O5="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O5)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O5)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O5)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O5)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O5)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O5)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O5)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O5)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O5)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O5)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O5)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O5)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O5)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O5)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O5)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O5)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O5)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O5)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O5)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O5)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O5)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O5)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O5)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3117,53 +3163,53 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A6" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11">
+      <c r="A6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10">
         <v>1970</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10" t="s">
+      <c r="F6" s="10"/>
+      <c r="G6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10" t="s">
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10" t="s">
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="AC6" s="7" t="str">
         <f>IF(O6="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O6)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O6)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O6)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O6)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O6)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O6)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O6)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O6)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O6)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O6)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O6)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O6)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O6)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O6)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O6)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O6)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O6)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O6)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O6)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O6)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O6)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O6)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O6)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3175,51 +3221,51 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A7" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11">
+      <c r="A7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10">
         <v>1970</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10" t="s">
+      <c r="E7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10" t="s">
+      <c r="H7" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10" t="s">
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AC7" s="7" t="str">
         <f>IF(O7="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O7)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O7)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O7)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O7)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O7)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O7)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O7)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O7)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O7)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O7)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O7)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O7)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O7)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O7)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O7)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O7)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O7)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O7)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O7)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O7)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O7)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O7)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O7)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3231,51 +3277,53 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A8" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11">
-        <v>1971</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="A8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10">
+        <v>1970</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10" t="s">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AC8" s="7" t="str">
         <f>IF(O8="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O8)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O8)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O8)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O8)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O8)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O8)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O8)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O8)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O8)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O8)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O8)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O8)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O8)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O8)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O8)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O8)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O8)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O8)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O8)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O8)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O8)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O8)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O8)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3287,53 +3335,51 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11">
-        <v>1971</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="10" t="s">
+      <c r="A9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10">
+        <v>1970</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10" t="s">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AC9" s="7" t="str">
         <f>IF(O9="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O9)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O9)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O9)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O9)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O9)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O9)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O9)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O9)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O9)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O9)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O9)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O9)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O9)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O9)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O9)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O9)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O9)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O9)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O9)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O9)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O9)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O9)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O9)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3345,111 +3391,99 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A10" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11">
+      <c r="A10" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15">
+        <v>1970</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>602</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14">
+        <v>1970</v>
+      </c>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+    </row>
+    <row r="11" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10">
         <v>1971</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="10" t="s">
+      <c r="E11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10" t="s">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10" t="s">
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AB10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC10" s="7" t="str">
-        <f>IF(O10="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O10)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O10)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O10)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O10)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O10)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O10)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O10)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O10)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O10)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O10)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O10)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O10)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O10)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O10)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O10)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O10)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O10)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O10)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O10)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O10)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O10)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O10)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O10)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
-      </c>
-      <c r="AD10" s="7" t="str">
-        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H10:N10,P10),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1972</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10" t="s">
-        <v>38</v>
-      </c>
       <c r="AB11" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="AC11" s="7" t="str">
         <f>IF(O11="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O11)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O11)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O11)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O11)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O11)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O11)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O11)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O11)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O11)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O11)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O11)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O11)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O11)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O11)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O11)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O11)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O11)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O11)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O11)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O11)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O11)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O11)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O11)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3461,55 +3495,53 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1972</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="A12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10">
+        <v>1971</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="10"/>
+      <c r="G12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10" t="s">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="AC12" s="7" t="str">
         <f>IF(O12="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O12)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O12)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O12)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O12)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O12)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O12)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O12)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O12)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O12)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O12)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O12)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O12)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O12)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O12)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O12)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O12)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O12)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O12)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O12)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O12)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O12)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O12)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O12)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3521,51 +3553,51 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11">
-        <v>1972</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="A13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10">
+        <v>1971</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="10"/>
+      <c r="G13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10" t="s">
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="AC13" s="7" t="str">
         <f>IF(O13="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O13)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O13)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O13)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O13)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O13)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O13)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O13)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O13)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O13)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O13)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O13)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O13)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O13)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O13)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O13)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O13)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O13)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O13)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O13)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O13)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O13)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O13)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O13)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3577,131 +3609,115 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A14" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="A14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="10">
         <v>1972</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="11">
-        <v>467</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="E14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q14" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y14" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z14" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA14" s="10" t="s">
-        <v>100</v>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AC14" s="7" t="str">
         <f>IF(O14="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O14)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O14)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O14)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O14)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O14)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O14)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O14)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O14)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O14)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O14)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O14)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O14)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O14)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O14)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O14)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O14)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O14)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O14)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O14)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O14)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O14)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O14)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O14)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-gottfried-john; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
+        <v/>
       </c>
       <c r="AD14" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H14:N14,P14),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11">
-        <v>1973</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="10" t="s">
+      <c r="A15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1972</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10" t="s">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AC15" s="7" t="str">
         <f>IF(O15="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O15)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O15)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O15)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O15)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O15)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O15)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O15)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O15)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O15)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O15)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O15)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O15)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O15)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O15)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O15)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O15)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O15)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O15)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O15)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O15)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O15)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O15)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O15)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3713,71 +3729,51 @@
       </c>
     </row>
     <row r="16" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A16" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="11">
-        <v>1973</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" s="11">
-        <v>212</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10">
+        <v>1972</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="U16" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y16" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z16" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA16" s="10" t="s">
-        <v>116</v>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="AC16" s="7" t="str">
         <f>IF(O16="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O16)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O16)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O16)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O16)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O16)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O16)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O16)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O16)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O16)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O16)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O16)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O16)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O16)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O16)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O16)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O16)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O16)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O16)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O16)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O16)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O16)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O16)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O16)),'Référentiel entourage'!$A$24,"")))</f>
@@ -3789,209 +3785,207 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="11">
-        <v>1974</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="11">
+      <c r="A17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1972</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="10">
+        <v>467</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q17" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y17" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z17" s="10" t="s">
+      <c r="O17" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z17" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AA17" s="10" t="s">
+      <c r="AA17" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="AC17" s="7" t="str">
         <f>IF(O17="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O17)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O17)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O17)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O17)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O17)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O17)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O17)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O17)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O17)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O17)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O17)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O17)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O17)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O17)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O17)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O17)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O17)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O17)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O17)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O17)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O17)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O17)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O17)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira; pers-barbara-valentin</v>
+        <v>pers-gottfried-john; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
       <c r="AD17" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H17:N17,P17),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
+        <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A18" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="11">
-        <v>1974</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="11">
-        <v>140</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="A18" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10">
+        <v>1973</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q18" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="U18" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y18" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z18" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA18" s="10" t="s">
-        <v>100</v>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="AC18" s="7" t="str">
         <f>IF(O18="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O18)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O18)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O18)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O18)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O18)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O18)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O18)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O18)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O18)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O18)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O18)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O18)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O18)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O18)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O18)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O18)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O18)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O18)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O18)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O18)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O18)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O18)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O18)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-karlheinz-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz; pers-barbara-valentin</v>
+        <v/>
       </c>
       <c r="AD18" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H18:N18,P18),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" ht="32">
-      <c r="A19" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="11">
-        <v>1974</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="10" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1973</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="10">
+        <v>212</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10" t="s">
-        <v>38</v>
+      <c r="I19" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="U19" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y19" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z19" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA19" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="AC19" s="7" t="str">
         <f>IF(O19="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O19)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O19)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O19)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O19)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O19)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O19)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O19)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O19)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O19)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O19)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O19)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O19)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O19)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O19)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O19)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O19)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O19)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O19)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O19)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O19)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O19)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O19)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O19)),'Référentiel entourage'!$A$24,"")))</f>
@@ -4002,992 +3996,1002 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="160">
-      <c r="A20" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="11">
+    <row r="20" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="10">
         <v>1974</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="11">
-        <v>116</v>
-      </c>
-      <c r="G20" s="10" t="s">
+      <c r="E20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="10">
+        <v>93</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="P20" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q20" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="T20" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10" t="s">
+      <c r="I20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="Y20" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z20" s="10" t="s">
+      <c r="Y20" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z20" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AA20" s="10" t="s">
+      <c r="AA20" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="AC20" s="7" t="str">
         <f>IF(O20="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O20)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O20)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O20)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O20)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O20)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O20)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O20)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O20)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O20)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O20)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O20)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O20)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O20)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O20)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O20)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O20)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O20)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O20)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O20)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O20)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O20)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O20)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O20)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab; pers-barbara-valentin</v>
+        <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira; pers-barbara-valentin</v>
       </c>
       <c r="AD20" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H20:N20,P20),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" ht="272">
-      <c r="A21" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="11">
-        <v>1975</v>
-      </c>
-      <c r="E21" s="10" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="170.75" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1974</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="11">
-        <v>123</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="10">
+        <v>140</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K21" s="10" t="s">
+      <c r="I21" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q21" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y21" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z21" s="10" t="s">
+      <c r="L21" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="U21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z21" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AA21" s="10" t="s">
+      <c r="AA21" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AC21" s="7" t="str">
         <f>IF(O21="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O21)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O21)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O21)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O21)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O21)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O21)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O21)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O21)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O21)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O21)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O21)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O21)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O21)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O21)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O21)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O21)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O21)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O21)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O21)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O21)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O21)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O21)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O21)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab; pers-barbara-valentin</v>
+        <v>pers-karlheinz-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz; pers-barbara-valentin</v>
       </c>
       <c r="AD21" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H21:N21,P21),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" ht="256">
-      <c r="A22" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="11">
-        <v>1975</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="11">
-        <v>120</v>
-      </c>
-      <c r="G22" s="10" t="s">
+        <v>pers-kurt-raab</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="30">
+      <c r="A22" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10">
+        <v>1974</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="O22" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="P22" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q22" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="T22" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="U22" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y22" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z22" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA22" s="10" t="s">
-        <v>100</v>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="AC22" s="7" t="str">
         <f>IF(O22="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O22)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O22)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O22)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O22)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O22)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O22)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O22)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O22)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O22)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O22)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O22)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O22)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O22)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O22)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O22)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O22)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O22)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O22)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O22)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O22)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O22)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O22)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O22)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
+        <v/>
       </c>
       <c r="AD22" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H22:N22,P22),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" ht="48">
-      <c r="A23" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11">
-        <v>1975</v>
-      </c>
-      <c r="E23" s="10" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="150">
+      <c r="A23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1974</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="10">
+        <v>116</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10"/>
-      <c r="X23" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10" t="s">
-        <v>38</v>
+      <c r="I23" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y23" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z23" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA23" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="AC23" s="7" t="str">
         <f>IF(O23="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O23)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O23)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O23)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O23)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O23)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O23)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O23)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O23)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O23)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O23)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O23)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O23)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O23)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O23)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O23)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O23)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O23)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O23)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O23)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O23)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O23)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O23)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O23)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab; pers-barbara-valentin</v>
       </c>
       <c r="AD23" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H23:N23,P23),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="32">
-      <c r="A24" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11">
+        <v>pers-michael-ballhaus; pers-kurt-raab</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="255">
+      <c r="A24" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="10">
         <v>1975</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="10" t="s">
+      <c r="E24" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="10">
+        <v>123</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10" t="s">
+      <c r="I24" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10" t="s">
-        <v>38</v>
+      <c r="Y24" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z24" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA24" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="AC24" s="7" t="str">
         <f>IF(O24="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O24)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O24)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O24)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O24)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O24)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O24)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O24)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O24)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O24)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O24)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O24)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O24)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O24)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O24)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O24)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O24)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O24)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O24)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O24)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O24)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O24)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O24)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O24)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-harry-baer; pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab; pers-barbara-valentin</v>
       </c>
       <c r="AD24" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H24:N24,P24),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:30" ht="32">
-      <c r="A25" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11">
-        <v>1976</v>
-      </c>
-      <c r="E25" s="10" t="s">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="240">
+      <c r="A25" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="10">
+        <v>1975</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="10" t="s">
+      <c r="F25" s="10">
+        <v>120</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10" t="s">
-        <v>38</v>
+      <c r="I25" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="U25" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y25" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z25" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA25" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AC25" s="7" t="str">
         <f>IF(O25="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O25)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O25)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O25)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O25)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O25)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O25)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O25)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O25)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O25)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O25)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O25)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O25)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O25)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O25)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O25)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O25)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O25)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O25)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O25)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O25)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O25)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O25)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O25)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
       </c>
       <c r="AD25" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H25:N25,P25),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:30" ht="224">
-      <c r="A26" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="11">
-        <v>1976</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" s="11">
-        <v>112</v>
-      </c>
-      <c r="G26" s="10" t="s">
+        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="30">
+      <c r="A26" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10">
+        <v>1975</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="O26" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="P26" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q26" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="T26" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="U26" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y26" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z26" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA26" s="10" t="s">
-        <v>100</v>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="AC26" s="7" t="str">
         <f>IF(O26="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O26)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O26)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O26)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O26)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O26)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O26)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O26)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O26)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O26)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O26)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O26)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O26)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O26)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O26)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O26)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O26)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O26)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O26)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O26)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O26)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O26)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O26)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O26)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
+        <v/>
       </c>
       <c r="AD26" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H26:N26,P26),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" ht="160">
-      <c r="A27" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="11">
-        <v>1976</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" s="11">
-        <v>96</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H27" s="10" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="30">
+      <c r="A27" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10">
+        <v>1975</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q27" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10"/>
-      <c r="X27" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y27" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z27" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA27" s="10" t="s">
-        <v>100</v>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="AC27" s="7" t="str">
         <f>IF(O27="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O27)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O27)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O27)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O27)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O27)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O27)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O27)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O27)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O27)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O27)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O27)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O27)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O27)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O27)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O27)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O27)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O27)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O27)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O27)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O27)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O27)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O27)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O27)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-volker-spengler</v>
+        <v/>
       </c>
       <c r="AD27" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H27:N27,P27),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" ht="380">
-      <c r="A28" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="D28" s="11">
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="30">
+      <c r="A28" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10">
         <v>1976</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="11">
-        <v>104</v>
-      </c>
-      <c r="G28" s="10" t="s">
+      <c r="E28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="P28" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q28" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="T28" s="10"/>
-      <c r="U28" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10"/>
-      <c r="X28" s="10" t="s">
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="Y28" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="Z28" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA28" s="10" t="s">
-        <v>100</v>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="AC28" s="7" t="str">
         <f>IF(O28="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O28)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O28)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O28)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O28)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O28)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O28)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O28)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O28)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O28)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O28)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O28)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O28)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O28)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O28)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O28)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O28)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O28)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O28)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O28)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O28)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O28)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O28)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O28)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-armin-meier</v>
+        <v/>
       </c>
       <c r="AD28" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H28:N28,P28),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="32">
-      <c r="A29" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="11">
-        <v>1977</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="10" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="210">
+      <c r="A29" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="10">
+        <v>1976</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="10">
+        <v>112</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y29" s="10"/>
-      <c r="Z29" s="10"/>
-      <c r="AA29" s="10" t="s">
-        <v>38</v>
+      <c r="I29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="U29" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y29" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z29" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA29" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="AC29" s="7" t="str">
         <f>IF(O29="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O29)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O29)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O29)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O29)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O29)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O29)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O29)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O29)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O29)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O29)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O29)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O29)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O29)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O29)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O29)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O29)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O29)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O29)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O29)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O29)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O29)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O29)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O29)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
       </c>
       <c r="AD29" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H29:N29,P29),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:30" ht="48">
-      <c r="A30" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11">
-        <v>1977</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H30" s="10" t="s">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="150">
+      <c r="A30" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1976</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="10">
+        <v>96</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10"/>
-      <c r="AA30" s="10" t="s">
-        <v>38</v>
+      <c r="I30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q30" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y30" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z30" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA30" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="AC30" s="7" t="str">
         <f>IF(O30="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O30)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O30)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O30)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O30)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O30)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O30)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O30)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O30)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O30)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O30)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O30)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O30)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O30)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O30)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O30)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O30)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O30)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O30)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O30)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O30)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O30)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O30)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O30)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-volker-spengler</v>
       </c>
       <c r="AD30" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H30:N30,P30),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:30" ht="160">
-      <c r="A31" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="11">
-        <v>1978</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F31" s="11">
-        <v>119</v>
-      </c>
-      <c r="G31" s="10" t="s">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" ht="342">
+      <c r="A31" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="D31" s="10">
+        <v>1976</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="10">
+        <v>104</v>
+      </c>
+      <c r="G31" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="Q31" s="10" t="s">
-        <v>581</v>
-      </c>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10" t="s">
-        <v>582</v>
-      </c>
-      <c r="T31" s="10"/>
-      <c r="U31" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="V31" s="10"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y31" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="Z31" s="10" t="s">
+      <c r="I31" s="9"/>
+      <c r="J31" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y31" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="Z31" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AA31" s="10" t="s">
+      <c r="AA31" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="AC31" s="7" t="str">
         <f>IF(O31="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O31)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O31)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O31)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O31)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O31)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O31)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O31)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O31)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O31)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O31)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O31)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O31)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O31)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O31)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O31)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O31)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O31)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O31)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O31)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O31)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O31)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O31)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O31)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-armin-meier</v>
       </c>
       <c r="AD31" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H31:N31,P31),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:30" ht="240">
-      <c r="A32" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="D32" s="11">
-        <v>1978</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" s="11">
-        <v>119</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H32" s="10" t="s">
+        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="30">
+      <c r="A32" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10">
+        <v>1977</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="P32" s="10" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q32" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="T32" s="10"/>
-      <c r="U32" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="Z32" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA32" s="10" t="s">
-        <v>100</v>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AC32" s="7" t="str">
         <f>IF(O32="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O32)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O32)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O32)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O32)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O32)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O32)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O32)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O32)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O32)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O32)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O32)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O32)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O32)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O32)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O32)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O32)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O32)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O32)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O32)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O32)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O32)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O32)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O32)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-gottfried-john; pers-volker-spengler</v>
+        <v/>
       </c>
       <c r="AD32" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H32:N32,P32),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="32">
-      <c r="A33" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="11">
-        <v>1978</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="10" t="s">
+    <row r="33" spans="1:30" ht="45">
+      <c r="A33" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10">
+        <v>1977</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-      <c r="X33" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y33" s="10"/>
-      <c r="Z33" s="10"/>
-      <c r="AA33" s="10" t="s">
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="AC33" s="7" t="str">
         <f>IF(O33="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O33)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O33)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O33)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O33)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O33)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O33)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O33)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O33)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O33)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O33)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O33)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O33)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O33)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O33)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O33)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O33)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O33)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O33)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O33)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O33)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O33)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O33)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O33)),'Référentiel entourage'!$A$24,"")))</f>
@@ -4998,56 +5002,66 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="48">
-      <c r="A34" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="11">
-        <v>1979</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="10" t="s">
+    <row r="34" spans="1:30" ht="150">
+      <c r="A34" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10">
+        <v>1978</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F34" s="10">
+        <v>119</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-      <c r="X34" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y34" s="10"/>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="10" t="s">
-        <v>38</v>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y34" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="Z34" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA34" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="AC34" s="7" t="str">
         <f>IF(O34="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O34)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O34)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O34)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O34)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O34)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O34)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O34)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O34)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O34)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O34)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O34)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O34)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O34)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O34)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O34)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O34)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O34)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O34)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O34)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O34)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O34)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O34)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O34)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5058,114 +5072,130 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="48">
-      <c r="A35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="11">
-        <v>1979</v>
-      </c>
-      <c r="E35" s="10" t="s">
+    <row r="35" spans="1:30" ht="225">
+      <c r="A35" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1978</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="10" t="s">
+      <c r="F35" s="10">
+        <v>119</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10"/>
-      <c r="X35" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y35" s="10"/>
-      <c r="Z35" s="10"/>
-      <c r="AA35" s="10" t="s">
-        <v>38</v>
+      <c r="I35" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y35" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="Z35" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA35" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="AC35" s="7" t="str">
         <f>IF(O35="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O35)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O35)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O35)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O35)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O35)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O35)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O35)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O35)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O35)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O35)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O35)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O35)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O35)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O35)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O35)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O35)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O35)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O35)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O35)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O35)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O35)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O35)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O35)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-ingrid-caven; pers-gottfried-john; pers-volker-spengler</v>
       </c>
       <c r="AD35" s="7" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H35:N35,P35),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="32">
-      <c r="A36" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="D36" s="11">
-        <v>1980</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="10" t="s">
+    <row r="36" spans="1:30" ht="30">
+      <c r="A36" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10">
+        <v>1978</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
-      <c r="AA36" s="10" t="s">
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="AC36" s="7" t="str">
         <f>IF(O36="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O36)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O36)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O36)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O36)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O36)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O36)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O36)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O36)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O36)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O36)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O36)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O36)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O36)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O36)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O36)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O36)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O36)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O36)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O36)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O36)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O36)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O36)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O36)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5176,56 +5206,56 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="32">
-      <c r="A37" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="D37" s="11">
-        <v>1981</v>
-      </c>
-      <c r="E37" s="10" t="s">
+    <row r="37" spans="1:30" ht="45">
+      <c r="A37" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="10">
+        <v>1979</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="10" t="s">
+      <c r="F37" s="10"/>
+      <c r="G37" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="10"/>
-      <c r="AA37" s="10" t="s">
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="AC37" s="7" t="str">
         <f>IF(O37="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O37)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O37)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O37)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O37)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O37)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O37)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O37)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O37)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O37)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O37)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O37)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O37)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O37)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O37)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O37)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O37)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O37)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O37)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O37)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O37)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O37)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O37)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O37)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5236,52 +5266,54 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="32">
-      <c r="A38" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="11">
-        <v>1981</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="10" t="s">
+    <row r="38" spans="1:30" ht="45">
+      <c r="A38" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10">
+        <v>1979</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
-      <c r="U38" s="10"/>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y38" s="10"/>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="10" t="s">
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AC38" s="7" t="str">
         <f>IF(O38="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O38)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O38)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O38)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O38)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O38)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O38)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O38)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O38)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O38)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O38)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O38)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O38)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O38)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O38)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O38)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O38)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O38)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O38)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O38)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O38)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O38)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O38)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O38)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5292,54 +5324,56 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="32">
-      <c r="A39" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="11">
-        <v>1981</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="10" t="s">
+    <row r="39" spans="1:30" ht="30">
+      <c r="A39" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" s="10">
+        <v>1980</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="V39" s="10"/>
-      <c r="W39" s="10"/>
-      <c r="X39" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y39" s="10"/>
-      <c r="Z39" s="10"/>
-      <c r="AA39" s="10" t="s">
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="AC39" s="7" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5350,56 +5384,56 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="48">
-      <c r="A40" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="D40" s="11">
+    <row r="40" spans="1:30" ht="30">
+      <c r="A40" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D40" s="10">
         <v>1981</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="10" t="s">
+      <c r="F40" s="10"/>
+      <c r="G40" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="10" t="s">
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="Y40" s="10"/>
-      <c r="Z40" s="10"/>
-      <c r="AA40" s="10" t="s">
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AC40" s="7" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5410,56 +5444,52 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="16">
-      <c r="A41" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="D41" s="11">
-        <v>1982</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H41" s="10" t="s">
+    <row r="41" spans="1:30" ht="30">
+      <c r="A41" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10">
+        <v>1981</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10"/>
-      <c r="X41" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="Y41" s="10"/>
-      <c r="Z41" s="10"/>
-      <c r="AA41" s="10" t="s">
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="9"/>
+      <c r="AA41" s="9" t="s">
         <v>38</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="AC41" s="7" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5470,14 +5500,197 @@
         <v/>
       </c>
     </row>
+    <row r="42" spans="1:30" ht="30">
+      <c r="A42" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10">
+        <v>1981</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="9"/>
+      <c r="AA42" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB42" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC42" s="7" t="str">
+        <f>IF(O42="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O42)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O42)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O42)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O42)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O42)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O42)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O42)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O42)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O42)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O42)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O42)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O42)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O42)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O42)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O42)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O42)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O42)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O42)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O42)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O42)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O42)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O42)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O42)),'Référentiel entourage'!$A$24,"")))</f>
+        <v/>
+      </c>
+      <c r="AD42" s="7" t="str">
+        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H42:N42,P42),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="30">
+      <c r="A43" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D43" s="10">
+        <v>1981</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="10"/>
+      <c r="G43" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
+      <c r="AA43" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB43" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC43" s="7" t="str">
+        <f>IF(O43="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O43)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O43)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O43)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O43)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O43)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O43)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O43)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O43)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O43)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O43)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O43)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O43)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O43)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O43)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O43)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O43)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O43)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O43)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O43)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O43)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O43)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O43)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O43)),'Référentiel entourage'!$A$24,"")))</f>
+        <v/>
+      </c>
+      <c r="AD43" s="7" t="str">
+        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H43:N43,P43),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="15">
+      <c r="A44" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D44" s="10">
+        <v>1982</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB44" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC44" s="7" t="str">
+        <f>IF(O44="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O44)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O44)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O44)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O44)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O44)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O44)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O44)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O44)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O44)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O44)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O44)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O44)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O44)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O44)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O44)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O44)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O44)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O44)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O44)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O44)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O44)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O44)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O44)),'Référentiel entourage'!$A$24,"")))</f>
+        <v/>
+      </c>
+      <c r="AD44" s="7" t="str">
+        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H44:N44,P44),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:T18 V2:AA18">
-    <cfRule type="expression" dxfId="30" priority="1">
+  <conditionalFormatting sqref="V4:AA21 A4:T21">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H3">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="AA2:AA18" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="AA4:AA21" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"À compléter,Partiellement documenté,Documenté,Validé"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5491,12 +5704,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>284</v>
       </c>
@@ -5559,17 +5772,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="80.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="99.75" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -5667,7 +5880,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="32">
+    <row r="14" spans="1:2" ht="16">
       <c r="A14" s="4" t="s">
         <v>311</v>
       </c>
@@ -5726,7 +5939,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -5735,7 +5948,7 @@
     <col min="7" max="14" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16">
+    <row r="1" spans="1:14" ht="15">
       <c r="A1" s="1" t="s">
         <v>321</v>
       </c>
@@ -5779,7 +5992,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="160">
+    <row r="2" spans="1:14" ht="135">
       <c r="A2" s="6" t="s">
         <v>335</v>
       </c>
@@ -5819,7 +6032,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="192">
+    <row r="3" spans="1:14" ht="180">
       <c r="A3" s="6" t="s">
         <v>347</v>
       </c>
@@ -5859,7 +6072,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="80">
+    <row r="4" spans="1:14" ht="75">
       <c r="A4" s="6" t="s">
         <v>358</v>
       </c>
@@ -5899,7 +6112,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="48">
+    <row r="5" spans="1:14" ht="45">
       <c r="A5" s="6" t="s">
         <v>370</v>
       </c>
@@ -5939,7 +6152,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="96">
+    <row r="6" spans="1:14" ht="90">
       <c r="A6" s="6" t="s">
         <v>381</v>
       </c>
@@ -5979,7 +6192,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="192">
+    <row r="7" spans="1:14" ht="180">
       <c r="A7" s="6" t="s">
         <v>393</v>
       </c>
@@ -6019,7 +6232,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="96">
+    <row r="8" spans="1:14" ht="90">
       <c r="A8" s="6" t="s">
         <v>404</v>
       </c>
@@ -6059,7 +6272,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="208">
+    <row r="9" spans="1:14" ht="195">
       <c r="A9" s="6" t="s">
         <v>415</v>
       </c>
@@ -6097,7 +6310,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="144">
+    <row r="10" spans="1:14" ht="120">
       <c r="A10" s="6" t="s">
         <v>426</v>
       </c>
@@ -6133,7 +6346,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="160">
+    <row r="11" spans="1:14" ht="150">
       <c r="A11" s="6" t="s">
         <v>435</v>
       </c>
@@ -6171,7 +6384,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="112">
+    <row r="12" spans="1:14" ht="105">
       <c r="A12" s="6" t="s">
         <v>445</v>
       </c>
@@ -6211,7 +6424,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="112">
+    <row r="13" spans="1:14" ht="105">
       <c r="A13" s="6" t="s">
         <v>455</v>
       </c>
@@ -6243,7 +6456,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="112">
+    <row r="14" spans="1:14" ht="105">
       <c r="A14" s="6" t="s">
         <v>463</v>
       </c>
@@ -6281,7 +6494,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="96">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="6" t="s">
         <v>474</v>
       </c>
@@ -6321,7 +6534,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="96">
+    <row r="16" spans="1:14" ht="75">
       <c r="A16" s="6" t="s">
         <v>484</v>
       </c>
@@ -6361,7 +6574,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="256">
+    <row r="17" spans="1:14" ht="240">
       <c r="A17" s="6" t="s">
         <v>495</v>
       </c>
@@ -6401,7 +6614,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="48">
+    <row r="18" spans="1:14" ht="45">
       <c r="A18" s="6" t="s">
         <v>505</v>
       </c>
@@ -6437,7 +6650,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="32">
+    <row r="19" spans="1:14" ht="30">
       <c r="A19" s="6" t="s">
         <v>513</v>
       </c>
@@ -6477,7 +6690,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="192">
+    <row r="20" spans="1:14" ht="180">
       <c r="A20" s="6" t="s">
         <v>523</v>
       </c>
@@ -6519,7 +6732,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="64">
+    <row r="21" spans="1:14" ht="60">
       <c r="A21" s="6" t="s">
         <v>535</v>
       </c>
@@ -6559,7 +6772,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="48">
+    <row r="22" spans="1:14" ht="45">
       <c r="A22" s="6" t="s">
         <v>546</v>
       </c>
@@ -6599,7 +6812,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="80">
+    <row r="23" spans="1:14" ht="75">
       <c r="A23" s="6" t="s">
         <v>556</v>
       </c>
@@ -6637,7 +6850,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="128">
+    <row r="24" spans="1:14" ht="105">
       <c r="A24" s="6" t="s">
         <v>565</v>
       </c>
@@ -6651,14 +6864,15 @@
         <v>568</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>592</v>
+      </c>
       <c r="G24" s="1" t="s">
         <v>374</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
         <v>569</v>
       </c>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise_Fassbinder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCF1F848-69A3-C840-8AE0-4081B9DB2FDC}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06045885-5F19-B949-8B75-9EB2C0614A73}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="900" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -866,9 +866,6 @@
     <t>film-1977-la-femme-du-chef-de-gare</t>
   </si>
   <si>
-    <t>rwf-1978-lallemagne-en-automne</t>
-  </si>
-  <si>
     <t>L’Allemagne en automne</t>
   </si>
   <si>
@@ -2060,6 +2057,9 @@
   </si>
   <si>
     <t>film-1970-rio-das-mortes</t>
+  </si>
+  <si>
+    <t>rwf-1978-l-allemagne-en-automne</t>
   </si>
 </sst>
 </file>
@@ -2178,7 +2178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2216,12 +2216,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2615,10 +2609,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA44" headerRowDxfId="31" dataDxfId="30" totalsRowDxfId="29">
   <tableColumns count="27">
@@ -2950,17 +2940,17 @@
     </row>
     <row r="2" spans="1:30" s="12" customFormat="1" ht="80.25" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11">
         <v>1966</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11" t="s">
@@ -2989,24 +2979,24 @@
       <c r="Z2" s="11"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AC2" s="11"/>
       <c r="AD2" s="11"/>
     </row>
     <row r="3" spans="1:30" s="12" customFormat="1" ht="80.25" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11">
         <v>1967</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11" t="s">
@@ -3035,7 +3025,7 @@
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AC3" s="11"/>
       <c r="AD3" s="11"/>
@@ -3134,7 +3124,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9" t="s">
@@ -3239,7 +3229,7 @@
         <v>34</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -3391,49 +3381,49 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="170.75" customHeight="1">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="10">
+        <v>1970</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15">
-        <v>1970</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>602</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14" t="s">
+      <c r="F10" s="10"/>
+      <c r="G10" s="9" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14">
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9">
         <v>1970</v>
       </c>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
       <c r="AB10" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
@@ -4814,7 +4804,7 @@
         <v>222</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D31" s="10">
         <v>1976</v>
@@ -4845,20 +4835,20 @@
         <v>161</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="P31" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="P31" s="9" t="s">
+      <c r="Q31" s="9" t="s">
         <v>576</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>577</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9" t="s">
@@ -4870,7 +4860,7 @@
         <v>193</v>
       </c>
       <c r="Y31" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Z31" s="9" t="s">
         <v>99</v>
@@ -5004,17 +4994,17 @@
     </row>
     <row r="34" spans="1:30" ht="150">
       <c r="A34" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="10">
         <v>1978</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F34" s="10">
         <v>119</v>
@@ -5033,26 +5023,26 @@
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q34" s="9" t="s">
         <v>580</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>581</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
       <c r="X34" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Y34" s="9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Z34" s="9" t="s">
         <v>99</v>
@@ -5061,7 +5051,7 @@
         <v>100</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AC34" s="7" t="str">
         <f>IF(O34="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O34)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O34)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O34)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O34)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O34)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O34)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O34)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O34)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O34)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O34)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O34)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O34)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O34)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O34)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O34)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O34)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O34)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O34)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O34)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O34)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O34)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O34)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O34)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5074,13 +5064,13 @@
     </row>
     <row r="35" spans="1:30" ht="225">
       <c r="A35" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>239</v>
-      </c>
       <c r="C35" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D35" s="10">
         <v>1978</v>
@@ -5098,7 +5088,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -5106,29 +5096,29 @@
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="Q35" s="9" t="s">
         <v>587</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>588</v>
       </c>
       <c r="R35" s="9"/>
       <c r="S35" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Y35" s="9" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Z35" s="9" t="s">
         <v>99</v>
@@ -5137,7 +5127,7 @@
         <v>100</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AC35" s="7" t="str">
         <f>IF(O35="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O35)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O35)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O35)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O35)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O35)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O35)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O35)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O35)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O35)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O35)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O35)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O35)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O35)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O35)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O35)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O35)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O35)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O35)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O35)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O35)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O35)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O35)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O35)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5150,10 +5140,10 @@
     </row>
     <row r="36" spans="1:30" ht="30">
       <c r="A36" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10">
@@ -5182,12 +5172,12 @@
       <c r="S36" s="9"/>
       <c r="T36" s="9"/>
       <c r="U36" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
       <c r="X36" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
@@ -5195,7 +5185,7 @@
         <v>38</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC36" s="7" t="str">
         <f>IF(O36="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O36)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O36)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O36)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O36)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O36)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O36)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O36)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O36)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O36)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O36)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O36)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O36)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O36)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O36)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O36)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O36)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O36)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O36)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O36)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O36)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O36)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O36)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O36)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5208,13 +5198,13 @@
     </row>
     <row r="37" spans="1:30" ht="45">
       <c r="A37" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="D37" s="10">
         <v>1979</v>
@@ -5242,12 +5232,12 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
       <c r="X37" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
@@ -5255,7 +5245,7 @@
         <v>38</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AC37" s="7" t="str">
         <f>IF(O37="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O37)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O37)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O37)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O37)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O37)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O37)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O37)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O37)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O37)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O37)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O37)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O37)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O37)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O37)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O37)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O37)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O37)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O37)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O37)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O37)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O37)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O37)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O37)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5268,10 +5258,10 @@
     </row>
     <row r="38" spans="1:30" ht="45">
       <c r="A38" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10">
@@ -5300,12 +5290,12 @@
       <c r="S38" s="9"/>
       <c r="T38" s="9"/>
       <c r="U38" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
       <c r="X38" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
@@ -5313,7 +5303,7 @@
         <v>38</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AC38" s="7" t="str">
         <f>IF(O38="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O38)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O38)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O38)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O38)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O38)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O38)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O38)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O38)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O38)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O38)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O38)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O38)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O38)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O38)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O38)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O38)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O38)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O38)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O38)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O38)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O38)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O38)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O38)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5326,13 +5316,13 @@
     </row>
     <row r="39" spans="1:30" ht="30">
       <c r="A39" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>257</v>
-      </c>
       <c r="C39" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D39" s="10">
         <v>1980</v>
@@ -5360,12 +5350,12 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
@@ -5373,7 +5363,7 @@
         <v>38</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AC39" s="7" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5386,13 +5376,13 @@
     </row>
     <row r="40" spans="1:30" ht="30">
       <c r="A40" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>262</v>
-      </c>
       <c r="C40" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D40" s="10">
         <v>1981</v>
@@ -5420,12 +5410,12 @@
       <c r="S40" s="9"/>
       <c r="T40" s="9"/>
       <c r="U40" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="V40" s="9"/>
       <c r="W40" s="9"/>
       <c r="X40" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
@@ -5433,7 +5423,7 @@
         <v>38</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AC40" s="7" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5446,17 +5436,17 @@
     </row>
     <row r="41" spans="1:30" ht="30">
       <c r="A41" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10">
         <v>1981</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="9" t="s">
@@ -5481,7 +5471,7 @@
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
@@ -5489,7 +5479,7 @@
         <v>38</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AC41" s="7" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5502,10 +5492,10 @@
     </row>
     <row r="42" spans="1:30" ht="30">
       <c r="A42" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>271</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10">
@@ -5534,12 +5524,12 @@
       <c r="S42" s="9"/>
       <c r="T42" s="9"/>
       <c r="U42" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
       <c r="X42" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
@@ -5547,7 +5537,7 @@
         <v>38</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AC42" s="7" t="str">
         <f>IF(O42="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O42)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O42)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O42)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O42)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O42)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O42)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O42)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O42)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O42)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O42)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O42)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O42)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O42)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O42)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O42)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O42)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O42)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O42)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O42)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O42)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O42)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O42)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O42)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5560,13 +5550,13 @@
     </row>
     <row r="43" spans="1:30" ht="30">
       <c r="A43" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="9" t="s">
         <v>275</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>276</v>
       </c>
       <c r="D43" s="10">
         <v>1981</v>
@@ -5594,12 +5584,12 @@
       <c r="S43" s="9"/>
       <c r="T43" s="9"/>
       <c r="U43" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
       <c r="X43" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
@@ -5607,7 +5597,7 @@
         <v>38</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AC43" s="7" t="str">
         <f>IF(O43="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O43)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O43)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O43)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O43)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O43)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O43)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O43)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O43)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O43)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O43)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O43)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O43)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O43)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O43)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O43)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O43)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O43)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O43)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O43)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O43)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O43)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O43)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O43)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5620,13 +5610,13 @@
     </row>
     <row r="44" spans="1:30" ht="15">
       <c r="A44" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>280</v>
-      </c>
       <c r="C44" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D44" s="10">
         <v>1982</v>
@@ -5654,12 +5644,12 @@
       <c r="S44" s="9"/>
       <c r="T44" s="9"/>
       <c r="U44" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="V44" s="9"/>
       <c r="W44" s="9"/>
       <c r="X44" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
@@ -5667,7 +5657,7 @@
         <v>38</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AC44" s="7" t="str">
         <f>IF(O44="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O44)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O44)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O44)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O44)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O44)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O44)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O44)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O44)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O44)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O44)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O44)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O44)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O44)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O44)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O44)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O44)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O44)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O44)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O44)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O44)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O44)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O44)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O44)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5679,7 +5669,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V4:AA21 A4:T21">
+  <conditionalFormatting sqref="A4:T21 V4:AA21">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -5711,10 +5701,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5727,10 +5717,10 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" t="s">
         <v>286</v>
-      </c>
-      <c r="B3" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5738,7 +5728,7 @@
         <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5746,22 +5736,22 @@
         <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -5780,32 +5770,32 @@
   <sheetData>
     <row r="1" spans="1:2" ht="80.25" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="99.75" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="99.75" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="99.75" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="99.75" customHeight="1">
@@ -5813,15 +5803,15 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="99.75" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="99.75" customHeight="1">
@@ -5829,7 +5819,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="99.75" customHeight="1">
@@ -5837,7 +5827,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="99.75" customHeight="1">
@@ -5845,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="99.75" customHeight="1">
@@ -5853,7 +5843,7 @@
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="99.75" customHeight="1">
@@ -5861,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="99.75" customHeight="1">
@@ -5869,39 +5859,39 @@
         <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16">
       <c r="A13" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16">
       <c r="A14" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="53.25" customHeight="1">
       <c r="A15" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="53.25" customHeight="1">
       <c r="A16" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="81.75" customHeight="1">
@@ -5909,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="81.75" customHeight="1">
@@ -5917,15 +5907,15 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="57" customHeight="1">
       <c r="A19" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -5950,731 +5940,731 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="135">
       <c r="A2" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="180">
       <c r="A3" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="75">
       <c r="A4" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="45">
       <c r="A5" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="90">
       <c r="A6" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="180">
       <c r="A7" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="90">
       <c r="A8" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="195">
       <c r="A9" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="120">
       <c r="A10" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="150">
       <c r="A11" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="105">
       <c r="A12" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="105">
       <c r="A13" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="105">
       <c r="A14" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="90">
       <c r="A15" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="75">
       <c r="A16" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="240">
       <c r="A17" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="45">
       <c r="A18" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>507</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="30">
       <c r="A19" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>191</v>
@@ -6684,207 +6674,207 @@
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="180">
       <c r="A20" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="60">
       <c r="A21" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>543</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="45">
       <c r="A22" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="H22" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="75">
       <c r="A23" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="105">
       <c r="A24" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>568</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06045885-5F19-B949-8B75-9EB2C0614A73}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{3A3DF4C9-37E7-F84B-A19A-8081989E315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49165CD8-5B26-E346-9A8F-2052F841B854}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="900" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,9 +893,6 @@
     <t>film-1978-despair</t>
   </si>
   <si>
-    <t>rwf-1978-lannee-des-treize-lunes</t>
-  </si>
-  <si>
     <t>L’Année des treize lunes</t>
   </si>
   <si>
@@ -918,9 +915,6 @@
   </si>
   <si>
     <t>1979</t>
-  </si>
-  <si>
-    <t>film-1979-le-mariage-de-maria-braun</t>
   </si>
   <si>
     <t>rwf-1979-la-troisieme-generation</t>
@@ -2060,6 +2054,12 @@
   </si>
   <si>
     <t>rwf-1978-l-allemagne-en-automne</t>
+  </si>
+  <si>
+    <t>rwf-1978-l-annee-des-treize-lunes</t>
+  </si>
+  <si>
+    <t>film-1978-le-mariage-de-maria-braun</t>
   </si>
 </sst>
 </file>
@@ -2609,6 +2609,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA44" headerRowDxfId="31" dataDxfId="30" totalsRowDxfId="29">
   <tableColumns count="27">
@@ -2940,17 +2944,17 @@
     </row>
     <row r="2" spans="1:30" s="12" customFormat="1" ht="80.25" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11">
         <v>1966</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11" t="s">
@@ -2979,24 +2983,24 @@
       <c r="Z2" s="11"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AC2" s="11"/>
       <c r="AD2" s="11"/>
     </row>
     <row r="3" spans="1:30" s="12" customFormat="1" ht="80.25" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11">
         <v>1967</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11" t="s">
@@ -3025,7 +3029,7 @@
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AC3" s="11"/>
       <c r="AD3" s="11"/>
@@ -3124,7 +3128,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9" t="s">
@@ -3229,7 +3233,7 @@
         <v>34</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -3382,17 +3386,17 @@
     </row>
     <row r="10" spans="1:30" ht="170.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10">
         <v>1970</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="9" t="s">
@@ -3423,7 +3427,7 @@
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
       <c r="AB10" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
@@ -4804,7 +4808,7 @@
         <v>222</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D31" s="10">
         <v>1976</v>
@@ -4835,20 +4839,20 @@
         <v>161</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="P31" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="Q31" s="9" t="s">
         <v>574</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>576</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9" t="s">
@@ -4860,7 +4864,7 @@
         <v>193</v>
       </c>
       <c r="Y31" s="9" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Z31" s="9" t="s">
         <v>99</v>
@@ -4994,7 +4998,7 @@
     </row>
     <row r="34" spans="1:30" ht="150">
       <c r="A34" s="9" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>232</v>
@@ -5023,14 +5027,14 @@
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9" t="s">
@@ -5042,7 +5046,7 @@
         <v>235</v>
       </c>
       <c r="Y34" s="9" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Z34" s="9" t="s">
         <v>99</v>
@@ -5070,7 +5074,7 @@
         <v>238</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D35" s="10">
         <v>1978</v>
@@ -5088,7 +5092,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -5096,17 +5100,17 @@
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q35" s="9" t="s">
         <v>585</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>587</v>
       </c>
       <c r="R35" s="9"/>
       <c r="S35" s="9" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="9" t="s">
@@ -5118,7 +5122,7 @@
         <v>235</v>
       </c>
       <c r="Y35" s="9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Z35" s="9" t="s">
         <v>99</v>
@@ -5140,10 +5144,10 @@
     </row>
     <row r="36" spans="1:30" ht="30">
       <c r="A36" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10">
@@ -5172,7 +5176,7 @@
       <c r="S36" s="9"/>
       <c r="T36" s="9"/>
       <c r="U36" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -5185,7 +5189,7 @@
         <v>38</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AC36" s="7" t="str">
         <f>IF(O36="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O36)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O36)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O36)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O36)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O36)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O36)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O36)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O36)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O36)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O36)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O36)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O36)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O36)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O36)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O36)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O36)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O36)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O36)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O36)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O36)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O36)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O36)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O36)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5198,16 +5202,16 @@
     </row>
     <row r="37" spans="1:30" ht="45">
       <c r="A37" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>247</v>
-      </c>
       <c r="D37" s="10">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>33</v>
@@ -5232,12 +5236,12 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
       <c r="X37" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
@@ -5245,7 +5249,7 @@
         <v>38</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>250</v>
+        <v>604</v>
       </c>
       <c r="AC37" s="7" t="str">
         <f>IF(O37="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O37)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O37)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O37)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O37)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O37)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O37)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O37)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O37)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O37)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O37)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O37)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O37)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O37)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O37)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O37)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O37)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O37)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O37)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O37)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O37)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O37)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O37)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O37)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5258,10 +5262,10 @@
     </row>
     <row r="38" spans="1:30" ht="45">
       <c r="A38" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10">
@@ -5290,12 +5294,12 @@
       <c r="S38" s="9"/>
       <c r="T38" s="9"/>
       <c r="U38" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
       <c r="X38" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
@@ -5303,7 +5307,7 @@
         <v>38</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AC38" s="7" t="str">
         <f>IF(O38="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O38)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O38)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O38)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O38)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O38)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O38)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O38)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O38)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O38)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O38)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O38)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O38)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O38)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O38)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O38)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O38)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O38)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O38)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O38)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O38)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O38)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O38)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O38)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5316,13 +5320,13 @@
     </row>
     <row r="39" spans="1:30" ht="30">
       <c r="A39" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D39" s="10">
         <v>1980</v>
@@ -5350,12 +5354,12 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
@@ -5363,7 +5367,7 @@
         <v>38</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AC39" s="7" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5376,13 +5380,13 @@
     </row>
     <row r="40" spans="1:30" ht="30">
       <c r="A40" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D40" s="10">
         <v>1981</v>
@@ -5410,12 +5414,12 @@
       <c r="S40" s="9"/>
       <c r="T40" s="9"/>
       <c r="U40" s="9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="V40" s="9"/>
       <c r="W40" s="9"/>
       <c r="X40" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
@@ -5423,7 +5427,7 @@
         <v>38</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AC40" s="7" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5436,17 +5440,17 @@
     </row>
     <row r="41" spans="1:30" ht="30">
       <c r="A41" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10">
         <v>1981</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="9" t="s">
@@ -5471,7 +5475,7 @@
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
@@ -5479,7 +5483,7 @@
         <v>38</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AC41" s="7" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5492,10 +5496,10 @@
     </row>
     <row r="42" spans="1:30" ht="30">
       <c r="A42" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10">
@@ -5524,12 +5528,12 @@
       <c r="S42" s="9"/>
       <c r="T42" s="9"/>
       <c r="U42" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
       <c r="X42" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
@@ -5537,7 +5541,7 @@
         <v>38</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AC42" s="7" t="str">
         <f>IF(O42="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O42)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O42)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O42)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O42)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O42)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O42)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O42)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O42)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O42)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O42)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O42)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O42)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O42)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O42)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O42)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O42)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O42)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O42)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O42)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O42)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O42)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O42)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O42)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5550,13 +5554,13 @@
     </row>
     <row r="43" spans="1:30" ht="30">
       <c r="A43" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="D43" s="10">
         <v>1981</v>
@@ -5584,12 +5588,12 @@
       <c r="S43" s="9"/>
       <c r="T43" s="9"/>
       <c r="U43" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
       <c r="X43" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
@@ -5597,7 +5601,7 @@
         <v>38</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AC43" s="7" t="str">
         <f>IF(O43="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O43)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O43)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O43)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O43)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O43)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O43)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O43)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O43)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O43)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O43)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O43)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O43)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O43)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O43)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O43)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O43)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O43)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O43)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O43)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O43)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O43)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O43)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O43)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5610,13 +5614,13 @@
     </row>
     <row r="44" spans="1:30" ht="15">
       <c r="A44" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D44" s="10">
         <v>1982</v>
@@ -5644,12 +5648,12 @@
       <c r="S44" s="9"/>
       <c r="T44" s="9"/>
       <c r="U44" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V44" s="9"/>
       <c r="W44" s="9"/>
       <c r="X44" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
@@ -5657,7 +5661,7 @@
         <v>38</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AC44" s="7" t="str">
         <f>IF(O44="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O44)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O44)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O44)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O44)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O44)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O44)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O44)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O44)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O44)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O44)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O44)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O44)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O44)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O44)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O44)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O44)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O44)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O44)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O44)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O44)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O44)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O44)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O44)),'Référentiel entourage'!$A$24,"")))</f>
@@ -5701,10 +5705,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5717,10 +5721,10 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5728,7 +5732,7 @@
         <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5736,22 +5740,22 @@
         <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -5770,32 +5774,32 @@
   <sheetData>
     <row r="1" spans="1:2" ht="80.25" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="99.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="99.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="99.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="99.75" customHeight="1">
@@ -5803,15 +5807,15 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="99.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="99.75" customHeight="1">
@@ -5819,7 +5823,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="99.75" customHeight="1">
@@ -5827,7 +5831,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="99.75" customHeight="1">
@@ -5835,7 +5839,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="99.75" customHeight="1">
@@ -5843,7 +5847,7 @@
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="99.75" customHeight="1">
@@ -5851,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="99.75" customHeight="1">
@@ -5859,39 +5863,39 @@
         <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16">
       <c r="A13" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16">
       <c r="A14" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="53.25" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="53.25" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="81.75" customHeight="1">
@@ -5899,7 +5903,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="81.75" customHeight="1">
@@ -5907,15 +5911,15 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="57" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -5940,731 +5944,731 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="135">
       <c r="A2" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="180">
       <c r="A3" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="75">
       <c r="A4" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="45">
       <c r="A5" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="90">
       <c r="A6" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="180">
       <c r="A7" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="90">
       <c r="A8" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="195">
       <c r="A9" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="120">
       <c r="A10" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="D10" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="150">
       <c r="A11" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="105">
       <c r="A12" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="105">
       <c r="A13" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="D13" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="105">
       <c r="A14" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="D14" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="90">
       <c r="A15" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="D15" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="75">
       <c r="A16" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="D16" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="240">
       <c r="A17" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="45">
       <c r="A18" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="30">
       <c r="A19" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="D19" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>191</v>
@@ -6674,207 +6678,207 @@
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="180">
       <c r="A20" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="D20" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="60">
       <c r="A21" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="D21" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="45">
       <c r="A22" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="D22" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>548</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="75">
       <c r="A23" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="D23" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>561</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="105">
       <c r="A24" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="D24" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C63B5989-C971-4B45-A608-204D22394DCD}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61718449-BA5A-5748-9C0E-213E96A3AACC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6600" yWindow="600" windowWidth="10000" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="845">
   <si>
     <t>ID</t>
   </si>
@@ -1298,48 +1298,6 @@
     <t>Une personne absente du référentiel reste sans ID : aucun identifiant n’est inventé.</t>
   </si>
   <si>
-    <t>ID canonique</t>
-  </si>
-  <si>
-    <t>Nom canonique</t>
-  </si>
-  <si>
-    <t>Nom source</t>
-  </si>
-  <si>
-    <t>Prénom source</t>
-  </si>
-  <si>
-    <t>Surnom</t>
-  </si>
-  <si>
-    <t>Strate</t>
-  </si>
-  <si>
-    <t>Fonction dominante</t>
-  </si>
-  <si>
-    <t>Type de collaboration</t>
-  </si>
-  <si>
-    <t>Vie privée / lien avec Fassbinder</t>
-  </si>
-  <si>
-    <t>Œuvres de Fassbinder</t>
-  </si>
-  <si>
-    <t>IDs films — Œuvres de Fassbinder</t>
-  </si>
-  <si>
-    <t>Œuvres non rapprochées</t>
-  </si>
-  <si>
-    <t>Rôle dans l’univers Fassbinder</t>
-  </si>
-  <si>
-    <t>Portrait</t>
-  </si>
-  <si>
     <t>pers-harry-baer</t>
   </si>
   <si>
@@ -1365,9 +1323,6 @@
   </si>
   <si>
     <t>Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Pionniers à Ingolstadt; Whity; Le Marchand des quatre saisons; Despair; La Troisième génération; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande</t>
-  </si>
-  <si>
-    <t>film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generation; film-1981-le-secret-de-veronika-voss; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</t>
   </si>
   <si>
     <t>Témoin de l’intérieur du collectif, relais organisationnel</t>
@@ -1650,9 +1605,6 @@
   </si>
   <si>
     <t>Hermann</t>
-  </si>
-  <si>
-    <t>Irm</t>
   </si>
   <si>
     <t>Jeu, répétition de rôle, tension sociale</t>
@@ -1756,9 +1708,6 @@
     <t>film-1976-roulette-chinoise; film-1977-la-femme-du-chef-de-gare; film-1978-despair; film-1979-la-troisieme-generation; film-1980-berlin-alexanderplatz; film-1981-le-secret-de-veronika-voss; film-1981-lola-une-femme-allemande</t>
   </si>
   <si>
-    <t>Fig essentielle de la dernière période, à la fois techniquement indispensable et historiquement décisive pour la conservation de l’héritage Fassbinder</t>
-  </si>
-  <si>
     <t>Lorenz.jpg</t>
   </si>
   <si>
@@ -1849,9 +1798,6 @@
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-le-soldat-americain; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-prenez-garde-a-la-sainte-putain; film-1971-whity; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1974-martha; film-1975-le-droit-du-plus-fort; film-1975-maman-kusters-s-en-va-au-ciel; film-1975-peur-de-la-peur; film-1976-le-roti-de-satan; film-1979-le-mariage-de-maria-braun; film-1981-lili-marleen; film-1982-querelle</t>
   </si>
   <si>
-    <t>Collaborateur total, à la frontière du jeu et de la fabrication matérielle, Chef Décorateur , identité visuelle des films de RWF</t>
-  </si>
-  <si>
     <t>Raab.jpg</t>
   </si>
   <si>
@@ -1930,12 +1876,6 @@
     <t>Proche collaboratrice de longue durée, liée au noyau fondateur du groupe et à l’intimité artistique de Fassbinder</t>
   </si>
   <si>
-    <t>L’Amour est plus froid que la mort; Le Bouc; Les Dieux de la peste; Prenez garde à la sainte putain; Huit heures ne font pas un jour; Le Marchand des quatre saisons; Les Larmes amères de Petra von Kant; Effi Briest; La Troisième génération; Le Mariage de Maria Braun; Berlin Alexanderplatz; Lili Marleen</t>
-  </si>
-  <si>
-    <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-lili-marleen</t>
-  </si>
-  <si>
     <t>Rio das Mortes</t>
   </si>
   <si>
@@ -2047,16 +1987,10 @@
     <t>Spengler</t>
   </si>
   <si>
-    <t>Collaboration ponctuelle et opportuniste</t>
-  </si>
-  <si>
     <t>Maman Küsters s’en va au ciel; Le Rôti de Satan; Roulette chinoise; Despair; L’Année des treize lunes; La Troisième génération; Le Mariage de Maria Braun; Berlin Alexanderplatz</t>
   </si>
   <si>
     <t>film-1975-maman-kusters-s-en-va-au-ciel; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz</t>
-  </si>
-  <si>
-    <t>Incarne souvent des personnages de travestis ou qui se déguisent, il incarne une inquiétante étrangeté.</t>
   </si>
   <si>
     <t>Volker.jpg</t>
@@ -3154,12 +3088,310 @@
   <si>
     <t>Projet initié par le producteur Luggi Waldleitner autour de la désormais star Schygulla. Cette dernière refuse que le scénariste Mandred Purzer, issu du cinéma commercial et notoirement de droite, réalise le film. Elle impose RWF qui a pourtant juré de ne plus travailler avec elle mais accepte.  A l'annonce du projet, la presse déclare que RWF a "vendu son âme". RWF affronte deux écueils : celui du cinéma  de papa qu'incarnent producteur et scénariste, risque de s'inscrire dans la nostalgie et le kitsch qui glamourise la période nazie. RWF s'en libère en faisant apparaîter la manière dont la société de consommation et le capitalisme sont la poursuite du fascisme. Guerre et technologie médiatique relèvent d'une même logique de domination pour un pouvoir devenu invisible, car masqué par les signes qui l'incarnent.</t>
   </si>
+  <si>
+    <t>pers-hark-bohm</t>
+  </si>
+  <si>
+    <t>Hark Bohm</t>
+  </si>
+  <si>
+    <t>Bohm</t>
+  </si>
+  <si>
+    <t>Hark</t>
+  </si>
+  <si>
+    <t>stock company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration durant toute la carrière de RWF. </t>
+  </si>
+  <si>
+    <t>Le Soldat américain;Prenez garde à la sainte putain; Effi Briest; Tous les autres s’appellent Ali;Le Droit du plus fort; Le Rôti de Satan; Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1970-le-soldat-americain; film-1971-prenez-garde-a-la-sainte-putain; film-1974-effi-briest; film-1974-tous-les-autres-s-appellent-ali;film-1975-le-droit-du-plus-fort; film-1976-le-roti-de-satan; film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un des "mauvais garçons" du Nouveau cinéma allemand. Il est associé à  l'« École de Munich », tournant pour des réalisateurs comme Rudolf Thome, Klaus Lemke ou Roland Klick avant de collaborer avec RWF pour lequel il offre une relecture du gangster de film noir. Il est le "doc" du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Soldat américain et tient le rôle principal de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prenez garde à la sainte putain. Fils de Martha dans</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tous les autres s'appellent Ali</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, il devient une figure de l'oppression ordinaire. virilité ironique et désenchantée</t>
+    </r>
+  </si>
+  <si>
+    <t>Bohm.H.jpg</t>
+  </si>
+  <si>
+    <t>Noyau théâtral / Stock company/ période centrale et tardive</t>
+  </si>
+  <si>
+    <t>pers-michael-fengler</t>
+  </si>
+  <si>
+    <t>Fengler</t>
+  </si>
+  <si>
+    <t>Producteur, collaborateur</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">un des plus proches collaborateurs de RWF jusqu'à son éviction après </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maria Braun</t>
+    </r>
+  </si>
+  <si>
+    <t>Il fait partie du groupe qui fonde l'antiteater et la société de production antiteater-X-Film</t>
+  </si>
+  <si>
+    <t>Petit Chaos; Le Clochard; Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Le Voyage à Niklashausen; Rio das Mortes; Whity; Le Marchand des quatre saisons; Le Rôti de Satan; Roulette chinoise; Le Mariage de Maria Braun</t>
+  </si>
+  <si>
+    <t>film-1966-le-clochard; film-1967-le-clochard; film-1969-le-bouc; film-1969-l-amour-est-plus-froid-que-la-mort; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1976-le-roti-de-satan; film-1976-roulette-chinoise; film-1979-le-mariage-de-maria-braun</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Il assure la photographie du court-métrage Le Petit Chaos (1967) et participe au montage du Clochard (1966). Il l co-réalise </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pourquoi monsieur R. est-il atteint de folie meurtrière</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ? (1970). Produit plus de 12 films de RWF.</t>
+    </r>
+  </si>
+  <si>
+    <t>Fengler.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Irm</t>
+  </si>
+  <si>
+    <t>Figure essentielle de la dernière période, à la fois techniquement indispensable et historiquement décisive pour la conservation de l’héritage Fassbinder</t>
+  </si>
+  <si>
+    <t>Collaborateur total, à la frontière du jeu et de la fabrication matérielle, chef décorateur , identité visuelle des films de RWF</t>
+  </si>
+  <si>
+    <t>L’Amour est plus froid que la mort; Le Bouc; Les Dieux de la peste; Rio das Mortes; Prenez garde à la sainte putain; Huit heures ne font pas un jour; Le Marchand des quatre saisons; Les Larmes amères de Petra von Kant; Effi Briest; La Troisième génération; Le Mariage de Maria Braun; Berlin Alexanderplatz; Lili Marleen</t>
+  </si>
+  <si>
+    <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-rio-das-mortes; film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1972-le-marchand-des-quatre-saisons; film-1972-les-larmes-ameres-de-petra-von-kant; film-1974-effi-briest; film-1979-la-troisieme-generation; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>pers-elisabeth-trissenaar</t>
+  </si>
+  <si>
+    <t>Elisabeth Trissenaar</t>
+  </si>
+  <si>
+    <t>Trissenaar</t>
+  </si>
+  <si>
+    <t>Elisabeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeu, prestige d'une actrice renommée. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actrice autrichienne de formatrice classique, elle est formée au prestigieux Max Reinhardt Seminar. Elle rejoint l'univers de RWF en 1974 pour une production au Theater am Turm (TAT) de Francfort. Perçue comme une intruse par le premier cercle, son travail avec le metteur en scène et compagnon Hans Neuenfelsla matintient à une certaine distance critique vis-à-vis du « système » Fassbinder, ne vivant jamais en communauté avec le groupe. </t>
+  </si>
+  <si>
+    <t>La Femme du chef de gare; L’Année des treize lunes; Le Mariage de Maria Braun; Berlin Alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1977-la-femme-du-chef-de-gare; film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aux côtés de Schygulla (la malléable) et de Carstensen (la nerveuse), Trissenaar incarne une féminité plus mûre, terrienne et dotée d'une autorité naturelle. Fassbinder l'utilise pour son jeu stylisé. Son personnage dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>La femme du chef de gare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> présente des points communs avec celui d'Elvira dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>l'année des treize lunes :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> elle aussi être prête à abandonner son identité au nom du désir. </t>
+    </r>
+  </si>
+  <si>
+    <t>Trissenaar.jpeg</t>
+  </si>
+  <si>
+    <t>Incarne souvent des personnages de travestis ou qui se déguisent, dégage une inquiétante étrangeté.</t>
+  </si>
+  <si>
+    <t>pers-waldleitner-luggi</t>
+  </si>
+  <si>
+    <t>Luggi Waldleitner</t>
+  </si>
+  <si>
+    <t>Waldleitner</t>
+  </si>
+  <si>
+    <t>Luggi</t>
+  </si>
+  <si>
+    <t>Producteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production de prestige; Collaboration ponctuelle et opportuniste; </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RWF se rapproche de Waldleitner pour Berlin Alexander Plats. La brouille du cinéaste avec son producteur historique, Fengler à propos des droits du </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Mariage de Maria Braun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> ouvre de nouvelles collaborations. Waldleitner est à l'origine du projet de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Lili Marleen, dont il détroit les droits de la chanson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lili Marleen;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rwf-1981-lili-marleen; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producteur majeur du cinéma ouest allemand, plutôt tourné vers l'industrie et les films divertissants. Il fait quelques incursions dans le cinéma de prestigue, d'auteur. </t>
+  </si>
+  <si>
+    <t>Waldleitner.jpeg</t>
+  </si>
+  <si>
+    <t>Colonne1</t>
+  </si>
+  <si>
+    <t>film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generatio</t>
+  </si>
+  <si>
+    <t>Colonne2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3214,8 +3446,58 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF56343A"/>
+      <name val="IBM Plex Mono"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF56343A"/>
+      <name val="IBM Plex Mono"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="IBM Plex Mono"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="IBM Plex Mono"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3249,11 +3531,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F7FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF5FA"/>
       </patternFill>
     </fill>
@@ -3263,7 +3540,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3271,11 +3548,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D1CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D1CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D1CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D1CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3290,10 +3596,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3305,24 +3608,71 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="46">
     <dxf>
       <fill>
         <patternFill>
@@ -3336,6 +3686,464 @@
           <bgColor rgb="FFF3F6F8"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF56343A"/>
+        <name val="IBM Plex Mono"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF56343A"/>
+        <name val="IBM Plex Mono"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D1CC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D1CC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3574,58 +4382,62 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA44" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA44" dataDxfId="45">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="18"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="34"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="24"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="21"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="20"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="19"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferentielEntourage" displayName="ReferentielEntourage" ref="A1:N24" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferentielEntourage" displayName="ReferentielEntourage" ref="A1:N27" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID canonique"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Nom canonique"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Nom source"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Prénom source"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Surnom"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Strate"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Fonction dominante"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Type de collaboration"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Vie privée / lien avec Fassbinder"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Œuvres de Fassbinder"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="IDs films — Œuvres de Fassbinder"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Œuvres non rapprochées"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Rôle dans l’univers Fassbinder"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Portrait"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="pers-harry-baer" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Harry Baer" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Baer" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Harry" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Colonne1" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Noyau théâtral / Factory" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Acteur, assistant, production" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Jeu, soutien de production, présence interne" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Proche compagnon de travail et membre du cercle masculin du collectif" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Pionniers à Ingolstadt; Whity; Le Marchand des quatre saisons; Despair; La Troisième génération; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generatio" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Colonne2" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Témoin de l’intérieur du collectif, relais organisationnel" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Baer.jpg" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3903,3390 +4715,3389 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="12" customFormat="1" ht="107" customHeight="1">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:30" s="11" customFormat="1" ht="107" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>605</v>
-      </c>
-      <c r="D2" s="11">
+      <c r="C2" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="D2" s="10">
         <v>1966</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>10</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>606</v>
-      </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>610</v>
-      </c>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11" t="s">
-        <v>611</v>
-      </c>
-      <c r="AA2" s="11"/>
+      <c r="J2" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="AA2" s="10"/>
       <c r="AB2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-    </row>
-    <row r="3" spans="1:30" s="12" customFormat="1" ht="107" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+    </row>
+    <row r="3" spans="1:30" s="11" customFormat="1" ht="107" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="C3" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="D3" s="10">
         <v>1967</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>9</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>615</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>616</v>
-      </c>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11" t="s">
+      <c r="J3" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
     </row>
     <row r="4" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>1969</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>88</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9" t="s">
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="AA4" s="9" t="s">
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA4" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AC4" s="7" t="str">
+      <c r="AC4" s="6" t="str">
         <f>IF(O4="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O4)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O4)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O4)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O4)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O4)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O4)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O4)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O4)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O4)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O4)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O4)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O4)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O4)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O4)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O4)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O4)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O4)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O4)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O4)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O4)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O4)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O4)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O4)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-ursula-stratz</v>
       </c>
-      <c r="AD4" s="7" t="str">
+      <c r="AD4" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H4:N4,P4),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-ulli-lommel; pers-peer-raben</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>1969</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>88</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9" t="s">
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9" t="s">
+      <c r="N5" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9" t="s">
+      <c r="T5" s="8"/>
+      <c r="U5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9" t="s">
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="AA5" s="9" t="s">
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="AA5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AC5" s="7" t="str">
+      <c r="AC5" s="6" t="str">
         <f>IF(O5="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O5)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O5)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O5)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O5)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O5)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O5)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O5)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O5)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O5)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O5)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O5)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O5)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O5)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O5)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O5)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O5)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O5)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O5)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O5)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O5)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O5)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O5)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O5)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-irm-hermann; pers-hanna-schygulla; pers-lilith-ungerer</v>
-      </c>
-      <c r="AD5" s="7" t="str">
+        <v>pers-irm-hermann; pers-hanna-schygulla; pers-lilith-ungerer</v>
+      </c>
+      <c r="AD5" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H5:N5,P5),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-peer-raben</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C6" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="D6" s="9">
         <v>1970</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>91</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N6" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9" t="s">
+      <c r="N6" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9" t="s">
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="AA6" s="9" t="s">
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="AA6" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AC6" s="7" t="str">
+      <c r="AC6" s="6" t="str">
         <f>IF(O6="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O6)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O6)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O6)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O6)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O6)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O6)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O6)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O6)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O6)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O6)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O6)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O6)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O6)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O6)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O6)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O6)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O6)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O6)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O6)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O6)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O6)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O6)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O6)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-ingrid-caven; pers-lilo-pempeit; pers-gunther-kaufmann; pers-hanna-schygulla; pers-lilith-ungerer</v>
-      </c>
-      <c r="AD6" s="7" t="str">
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-gunther-kaufmann; pers-hanna-schygulla; pers-lilith-ungerer</v>
+      </c>
+      <c r="AD6" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H6:N6,P6),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-michael-fengler; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C7" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="D7" s="9">
         <v>1970</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>88</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="J7" s="9" t="s">
+      <c r="I7" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="L7" s="9" t="s">
+      <c r="K7" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N7" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9" t="s">
+      <c r="N7" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="AA7" s="9" t="s">
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="AA7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AC7" s="7" t="str">
+      <c r="AC7" s="6" t="str">
         <f>IF(O7="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O7)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O7)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O7)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O7)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O7)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O7)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O7)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O7)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O7)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O7)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O7)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O7)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O7)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O7)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O7)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O7)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O7)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O7)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O7)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O7)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O7)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O7)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O7)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-lilith-ungerer</v>
-      </c>
-      <c r="AD7" s="7" t="str">
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-lilith-ungerer</v>
+      </c>
+      <c r="AD7" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H7:N7,P7),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-michael-fengler; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="D8" s="9">
         <v>1970</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>80</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L8" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="M8" s="9" t="s">
+      <c r="L8" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9" t="s">
+      <c r="N8" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9" t="s">
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="AA8" s="9" t="s">
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="AA8" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AC8" s="7" t="str">
+      <c r="AC8" s="6" t="str">
         <f>IF(O8="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O8)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O8)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O8)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O8)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O8)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O8)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O8)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O8)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O8)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O8)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O8)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O8)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O8)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O8)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O8)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O8)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O8)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O8)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O8)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O8)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O8)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O8)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O8)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab</v>
-      </c>
-      <c r="AD8" s="7" t="str">
+        <v>pers-hark-bohm; pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab</v>
+      </c>
+      <c r="AD8" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H8:N8,P8),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="C9" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="D9" s="9">
         <v>1970</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>90</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="AA9" s="9" t="s">
+      <c r="AA9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AC9" s="7" t="str">
+      <c r="AC9" s="6" t="str">
         <f>IF(O9="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O9)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O9)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O9)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O9)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O9)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O9)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O9)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O9)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O9)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O9)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O9)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O9)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O9)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O9)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O9)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O9)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O9)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O9)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O9)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O9)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O9)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O9)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O9)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ingrid-caven; pers-gunther-kaufmann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD9" s="7" t="str">
+        <v>pers-margit-carstensen; pers-ingrid-caven; pers-michael-fengler; pers-gunther-kaufmann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD9" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H9:N9,P9),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-michael-fengler; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10">
+      <c r="C10" s="8"/>
+      <c r="D10" s="9">
         <v>1970</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>84</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="L10" s="9" t="s">
+      <c r="K10" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N10" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9">
+      <c r="N10" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8">
         <v>1970</v>
       </c>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="AA10" s="9"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="AA10" s="8"/>
       <c r="AB10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
     </row>
     <row r="11" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10">
+      <c r="C11" s="8"/>
+      <c r="D11" s="9">
         <v>1971</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>95</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="L11" s="9" t="s">
+      <c r="K11" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9" t="s">
+      <c r="N11" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="AA11" s="9" t="s">
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="AA11" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AC11" s="7" t="str">
+      <c r="AC11" s="6" t="str">
         <f>IF(O11="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O11)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O11)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O11)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O11)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O11)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O11)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O11)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O11)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O11)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O11)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O11)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O11)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O11)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O11)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O11)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O11)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O11)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O11)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O11)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O11)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O11)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O11)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O11)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-gunther-kaufmann; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD11" s="7" t="str">
+        <v>pers-gunther-kaufmann; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD11" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H11:N11,P11),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-ulli-lommel; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="D12" s="10">
+      <c r="C12" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D12" s="9">
         <v>1971</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>103</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K12" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="L12" s="9" t="s">
+      <c r="K12" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9" t="s">
+      <c r="N12" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9" t="s">
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="AA12" s="9" t="s">
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="AA12" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AC12" s="7" t="str">
+      <c r="AC12" s="6" t="str">
         <f>IF(O12="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O12)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O12)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O12)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O12)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O12)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O12)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O12)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O12)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O12)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O12)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O12)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O12)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O12)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O12)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O12)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O12)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O12)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O12)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O12)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O12)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O12)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O12)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O12)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-ingrid-caven; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD12" s="7" t="str">
+        <v>pers-ingrid-caven; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD12" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H12:N12,P12),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="D13" s="10">
+      <c r="C13" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="D13" s="9">
         <v>1971</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>84</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="I13" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N13" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9" t="s">
+      <c r="N13" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="AA13" s="9" t="s">
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="AA13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AC13" s="7" t="str">
+      <c r="AC13" s="6" t="str">
         <f>IF(O13="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O13)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O13)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O13)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O13)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O13)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O13)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O13)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O13)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O13)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O13)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O13)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O13)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O13)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O13)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O13)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O13)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O13)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O13)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O13)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O13)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O13)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O13)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O13)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-irm-hermann; pers-gunther-kaufmann; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD13" s="7" t="str">
+        <v>pers-irm-hermann; pers-gunther-kaufmann; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD13" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H13:N13,P13),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>1972</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>88</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9" t="s">
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9" t="s">
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="AA14" s="9" t="s">
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="AA14" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AC14" s="7" t="str">
+      <c r="AC14" s="6" t="str">
         <f>IF(O14="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O14)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O14)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O14)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O14)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O14)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O14)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O14)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O14)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O14)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O14)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O14)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O14)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O14)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O14)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O14)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O14)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O14)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O14)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O14)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O14)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O14)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O14)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O14)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-kurt-raab; pers-daniel-schmid; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD14" s="7" t="str">
+        <v>pers-hark-bohm; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-michael-fengler; pers-irm-hermann; pers-kurt-raab; pers-daniel-schmid; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD14" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H14:N14,P14),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>1972</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>124</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="I15" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9" t="s">
+      <c r="M15" s="8"/>
+      <c r="N15" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="O15" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9" t="s">
+      <c r="O15" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9" t="s">
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="AA15" s="9" t="s">
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="AA15" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AC15" s="7" t="str">
+      <c r="AC15" s="6" t="str">
         <f>IF(O15="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O15)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O15)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O15)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O15)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O15)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O15)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O15)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O15)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O15)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O15)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O15)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O15)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O15)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O15)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O15)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O15)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O15)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O15)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O15)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O15)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O15)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O15)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O15)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-margit-carstensen; pers-irm-hermann; pers-hanna-schygulla</v>
       </c>
-      <c r="AD15" s="7" t="str">
+      <c r="AD15" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H15:N15,P15),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="D16" s="10">
+      <c r="C16" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="D16" s="9">
         <v>1972</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>87</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="L16" s="9" t="s">
+      <c r="I16" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9" t="s">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="AA16" s="9" t="s">
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="AA16" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB16" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AC16" s="7" t="str">
+      <c r="AC16" s="6" t="str">
         <f>IF(O16="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O16)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O16)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O16)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O16)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O16)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O16)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O16)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O16)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O16)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O16)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O16)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O16)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O16)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O16)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O16)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O16)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O16)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O16)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O16)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O16)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O16)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O16)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O16)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-margit-carstensen; pers-lilo-pempeit; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
-      <c r="AD16" s="7" t="str">
+      <c r="AD16" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H16:N16,P16),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>1972</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>467</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9" t="s">
+      <c r="M17" s="8"/>
+      <c r="N17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="O17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="P17" s="9" t="s">
+      <c r="P17" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="Q17" s="9" t="s">
+      <c r="Q17" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9" t="s">
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="Y17" s="9" t="s">
+      <c r="Y17" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="Z17" s="9" t="s">
+      <c r="Z17" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA17" s="9" t="s">
+      <c r="AA17" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AC17" s="7" t="str">
+      <c r="AC17" s="6" t="str">
         <f>IF(O17="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O17)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O17)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O17)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O17)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O17)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O17)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O17)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O17)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O17)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O17)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O17)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O17)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O17)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O17)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O17)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O17)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O17)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O17)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O17)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O17)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O17)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O17)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O17)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-gottfried-john; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
-      <c r="AD17" s="7" t="str">
+      <c r="AD17" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H17:N17,P17),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="D18" s="10">
+      <c r="C18" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="D18" s="9">
         <v>1973</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>102</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="I18" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M18" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>703</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9" t="s">
+      <c r="M18" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="AA18" s="9" t="s">
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="AA18" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AC18" s="7" t="str">
+      <c r="AC18" s="6" t="str">
         <f>IF(O18="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O18)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O18)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O18)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O18)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O18)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O18)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O18)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O18)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O18)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O18)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O18)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O18)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O18)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O18)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O18)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O18)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O18)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O18)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O18)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O18)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O18)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O18)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O18)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-el-hedi-ben-salem; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD18" s="7" t="str">
+        <v>pers-el-hedi-ben-salem; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD18" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H18:N18,P18),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-irm-hermann; pers-kurt-raab</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>1973</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>212</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9" t="s">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9" t="s">
+      <c r="O19" s="8"/>
+      <c r="P19" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="Q19" s="9" t="s">
+      <c r="Q19" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9" t="s">
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="U19" s="9" t="s">
+      <c r="U19" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9" t="s">
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="Y19" s="9" t="s">
+      <c r="Y19" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Z19" s="9" t="s">
+      <c r="Z19" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA19" s="9" t="s">
+      <c r="AA19" s="8" t="s">
         <v>129</v>
       </c>
       <c r="AB19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AC19" s="7" t="str">
+      <c r="AC19" s="6" t="str">
         <f>IF(O19="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O19)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O19)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O19)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O19)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O19)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O19)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O19)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O19)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O19)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O19)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O19)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O19)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O19)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O19)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O19)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O19)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O19)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O19)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O19)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O19)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O19)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O19)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O19)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD19" s="7" t="str">
+      <c r="AD19" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H19:N19,P19),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>1974</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>93</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9" t="s">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="P20" s="9" t="s">
+      <c r="P20" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="Q20" s="9" t="s">
+      <c r="Q20" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9" t="s">
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9" t="s">
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="Y20" s="9" t="s">
+      <c r="Y20" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="Z20" s="9" t="s">
+      <c r="Z20" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA20" s="9" t="s">
+      <c r="AA20" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB20" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AC20" s="7" t="str">
+      <c r="AC20" s="6" t="str">
         <f>IF(O20="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O20)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O20)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O20)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O20)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O20)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O20)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O20)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O20)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O20)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O20)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O20)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O20)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O20)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O20)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O20)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O20)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O20)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O20)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O20)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O20)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O20)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O20)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O20)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira; pers-barbara-valentin</v>
-      </c>
-      <c r="AD20" s="7" t="str">
+        <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira</v>
+      </c>
+      <c r="AD20" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H20:N20,P20),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>1974</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>140</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9" t="s">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="O21" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="P21" s="9" t="s">
+      <c r="P21" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="Q21" s="9" t="s">
+      <c r="Q21" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9" t="s">
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="U21" s="9" t="s">
+      <c r="U21" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9" t="s">
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="Y21" s="9" t="s">
+      <c r="Y21" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="Z21" s="9" t="s">
+      <c r="Z21" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA21" s="9" t="s">
+      <c r="AA21" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB21" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AC21" s="7" t="str">
+      <c r="AC21" s="6" t="str">
         <f>IF(O21="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O21)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O21)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O21)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O21)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O21)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O21)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O21)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O21)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O21)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O21)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O21)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O21)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O21)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O21)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O21)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O21)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O21)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O21)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O21)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O21)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O21)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O21)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O21)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-karlheinz-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz; pers-barbara-valentin</v>
-      </c>
-      <c r="AD21" s="7" t="str">
+        <v>pers-karlheinz-bohm; pers-hark-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz</v>
+      </c>
+      <c r="AD21" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H21:N21,P21),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="105">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10">
+      <c r="C22" s="8"/>
+      <c r="D22" s="9">
         <v>1974</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <v>101</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>708</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>709</v>
-      </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>712</v>
-      </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9" t="s">
+      <c r="I22" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="AA22" s="9" t="s">
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="AA22" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB22" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AC22" s="7" t="str">
+      <c r="AC22" s="6" t="str">
         <f>IF(O22="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O22)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O22)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O22)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O22)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O22)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O22)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O22)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O22)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O22)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O22)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O22)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O22)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O22)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O22)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O22)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O22)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O22)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O22)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O22)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O22)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O22)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O22)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O22)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-barbara-valentin</v>
-      </c>
-      <c r="AD22" s="7" t="str">
+        <v>pers-margit-carstensen; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel</v>
+      </c>
+      <c r="AD22" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H22:N22,P22),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:30" ht="150">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>1974</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>116</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9" t="s">
+      <c r="M23" s="8"/>
+      <c r="N23" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="O23" s="9" t="s">
+      <c r="O23" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="P23" s="9" t="s">
+      <c r="P23" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Q23" s="9" t="s">
+      <c r="Q23" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9" t="s">
+      <c r="R23" s="8"/>
+      <c r="S23" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="T23" s="9" t="s">
+      <c r="T23" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9" t="s">
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+      <c r="X23" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="Y23" s="9" t="s">
+      <c r="Y23" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="Z23" s="9" t="s">
+      <c r="Z23" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA23" s="9" t="s">
+      <c r="AA23" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB23" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AC23" s="7" t="str">
+      <c r="AC23" s="6" t="str">
         <f>IF(O23="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O23)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O23)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O23)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O23)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O23)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O23)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O23)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O23)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O23)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O23)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O23)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O23)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O23)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O23)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O23)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O23)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O23)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O23)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O23)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O23)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O23)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O23)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O23)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab; pers-barbara-valentin</v>
-      </c>
-      <c r="AD23" s="7" t="str">
+        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab</v>
+      </c>
+      <c r="AD23" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H23:N23,P23),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="255">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>1975</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="9">
         <v>123</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9" t="s">
+      <c r="L24" s="8"/>
+      <c r="M24" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="N24" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="O24" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="P24" s="9" t="s">
+      <c r="P24" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="Q24" s="9" t="s">
+      <c r="Q24" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9" t="s">
+      <c r="R24" s="8"/>
+      <c r="S24" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9" t="s">
+      <c r="T24" s="8"/>
+      <c r="U24" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9" t="s">
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+      <c r="X24" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="Y24" s="9" t="s">
+      <c r="Y24" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="Z24" s="9" t="s">
+      <c r="Z24" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA24" s="9" t="s">
+      <c r="AA24" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB24" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="AC24" s="7" t="str">
+      <c r="AC24" s="6" t="str">
         <f>IF(O24="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O24)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O24)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O24)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O24)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O24)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O24)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O24)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O24)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O24)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O24)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O24)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O24)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O24)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O24)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O24)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O24)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O24)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O24)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O24)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O24)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O24)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O24)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O24)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab; pers-barbara-valentin</v>
-      </c>
-      <c r="AD24" s="7" t="str">
+        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab</v>
+      </c>
+      <c r="AD24" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H24:N24,P24),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="240">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>1975</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <v>120</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="M25" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="N25" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="O25" s="9" t="s">
+      <c r="O25" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="P25" s="9" t="s">
+      <c r="P25" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="Q25" s="9" t="s">
+      <c r="Q25" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9" t="s">
+      <c r="R25" s="8"/>
+      <c r="S25" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="T25" s="9" t="s">
+      <c r="T25" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="U25" s="9" t="s">
+      <c r="U25" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9" t="s">
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="Y25" s="9" t="s">
+      <c r="Y25" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="Z25" s="9" t="s">
+      <c r="Z25" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA25" s="9" t="s">
+      <c r="AA25" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB25" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AC25" s="7" t="str">
+      <c r="AC25" s="6" t="str">
         <f>IF(O25="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O25)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O25)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O25)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O25)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O25)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O25)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O25)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O25)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O25)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O25)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O25)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O25)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O25)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O25)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O25)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O25)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O25)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O25)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O25)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O25)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O25)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O25)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O25)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
-      </c>
-      <c r="AD25" s="7" t="str">
+        <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
+      </c>
+      <c r="AD25" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H25:N25,P25),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="60">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="D26" s="10">
+      <c r="C26" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="D26" s="9">
         <v>1975</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="9">
         <v>44</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>715</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9" t="s">
+      <c r="I26" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M26" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="N26" s="9" t="s">
+      <c r="M26" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="O26" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9" t="s">
+      <c r="O26" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9" t="s">
-        <v>721</v>
-      </c>
-      <c r="AA26" s="9" t="s">
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="AA26" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB26" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AC26" s="7" t="str">
+      <c r="AC26" s="6" t="str">
         <f>IF(O26="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O26)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O26)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O26)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O26)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O26)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O26)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O26)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O26)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O26)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O26)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O26)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O26)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O26)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O26)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O26)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O26)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O26)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O26)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O26)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O26)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O26)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O26)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O26)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-el-hedi-ben-salem; pers-brigitte-mira</v>
       </c>
-      <c r="AD26" s="7" t="str">
+      <c r="AD26" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H26:N26,P26),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="195">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="D27" s="10">
+      <c r="C27" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="D27" s="9">
         <v>1975</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <v>88</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>725</v>
-      </c>
-      <c r="L27" s="9" t="s">
+      <c r="I27" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M27" s="9" t="s">
+      <c r="M27" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N27" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9" t="s">
+      <c r="N27" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+      <c r="X27" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="AA27" s="9" t="s">
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="AA27" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB27" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AC27" s="7" t="str">
+      <c r="AC27" s="6" t="str">
         <f>IF(O27="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O27)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O27)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O27)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O27)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O27)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O27)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O27)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O27)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O27)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O27)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O27)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O27)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O27)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O27)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O27)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O27)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O27)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O27)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O27)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O27)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O27)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O27)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O27)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
-      </c>
-      <c r="AD27" s="7" t="str">
+        <v>pers-hark-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
+      </c>
+      <c r="AD27" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H27:N27,P27),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="135">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="D28" s="10">
+      <c r="C28" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="D28" s="9">
         <v>1976</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>101</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="K28" s="9" t="s">
+      <c r="H28" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9" t="s">
+      <c r="L28" s="8"/>
+      <c r="M28" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9" t="s">
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="AA28" s="9" t="s">
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="AA28" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB28" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AC28" s="7" t="str">
+      <c r="AC28" s="6" t="str">
         <f>IF(O28="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O28)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O28)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O28)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O28)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O28)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O28)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O28)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O28)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O28)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O28)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O28)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O28)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O28)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O28)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O28)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O28)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O28)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O28)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O28)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O28)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O28)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O28)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O28)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-ingrid-caven; pers-ulli-lommel</v>
       </c>
-      <c r="AD28" s="7" t="str">
+      <c r="AD28" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H28:N28,P28),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-peer-raben; pers-daniel-schmid</v>
+        <v>pers-michael-fengler; pers-peer-raben; pers-daniel-schmid</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="210">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>1976</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>112</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9" t="s">
+      <c r="L29" s="8"/>
+      <c r="M29" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="N29" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="O29" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="P29" s="9" t="s">
+      <c r="P29" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="Q29" s="9" t="s">
+      <c r="Q29" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9" t="s">
+      <c r="R29" s="8"/>
+      <c r="S29" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="T29" s="9" t="s">
+      <c r="T29" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="U29" s="9" t="s">
+      <c r="U29" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9" t="s">
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Y29" s="9" t="s">
+      <c r="Y29" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="Z29" s="9" t="s">
+      <c r="Z29" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA29" s="9" t="s">
+      <c r="AA29" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB29" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AC29" s="7" t="str">
+      <c r="AC29" s="6" t="str">
         <f>IF(O29="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O29)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O29)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O29)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O29)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O29)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O29)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O29)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O29)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O29)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O29)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O29)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O29)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O29)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O29)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O29)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O29)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O29)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O29)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O29)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O29)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O29)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O29)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O29)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab; pers-volker-spengler</v>
-      </c>
-      <c r="AD29" s="7" t="str">
+        <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
+      </c>
+      <c r="AD29" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H29:N29,P29),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
+        <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="150">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>1976</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>96</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K30" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9" t="s">
+      <c r="L30" s="8"/>
+      <c r="M30" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="N30" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="O30" s="9" t="s">
+      <c r="O30" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="P30" s="9" t="s">
+      <c r="P30" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="Q30" s="9" t="s">
+      <c r="Q30" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9" t="s">
+      <c r="R30" s="8"/>
+      <c r="S30" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9" t="s">
+      <c r="T30" s="8"/>
+      <c r="U30" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9" t="s">
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Y30" s="9" t="s">
+      <c r="Y30" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="Z30" s="9" t="s">
+      <c r="Z30" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA30" s="9" t="s">
+      <c r="AA30" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB30" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AC30" s="7" t="str">
+      <c r="AC30" s="6" t="str">
         <f>IF(O30="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O30)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O30)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O30)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O30)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O30)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O30)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O30)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O30)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O30)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O30)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O30)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O30)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O30)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O30)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O30)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O30)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O30)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O30)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O30)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O30)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O30)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O30)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O30)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-volker-spengler</v>
-      </c>
-      <c r="AD30" s="7" t="str">
+        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira</v>
+      </c>
+      <c r="AD30" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H30:N30,P30),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
+        <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="342">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>1976</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>104</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9" t="s">
+      <c r="I31" s="8"/>
+      <c r="J31" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K31" s="9" t="s">
+      <c r="K31" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M31" s="9" t="s">
+      <c r="M31" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="N31" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="O31" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="P31" s="9" t="s">
+      <c r="P31" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="Q31" s="9" t="s">
+      <c r="Q31" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9" t="s">
+      <c r="R31" s="8"/>
+      <c r="S31" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9" t="s">
+      <c r="T31" s="8"/>
+      <c r="U31" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9" t="s">
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Y31" s="9" t="s">
+      <c r="Y31" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="Z31" s="9" t="s">
+      <c r="Z31" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA31" s="9" t="s">
+      <c r="AA31" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB31" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AC31" s="7" t="str">
+      <c r="AC31" s="6" t="str">
         <f>IF(O31="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O31)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O31)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O31)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O31)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O31)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O31)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O31)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O31)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O31)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O31)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O31)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O31)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O31)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O31)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O31)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O31)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O31)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O31)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O31)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O31)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O31)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O31)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O31)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-ingrid-caven; pers-lilo-pempeit; pers-armin-meier</v>
       </c>
-      <c r="AD31" s="7" t="str">
+      <c r="AD31" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H31:N31,P31),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="398">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="D32" s="10">
+      <c r="C32" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="D32" s="9">
         <v>1977</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <v>111</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="I32" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K32" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="R32" s="9"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9" t="s">
+      <c r="K32" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="R32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="8"/>
+      <c r="V32" s="8"/>
+      <c r="W32" s="8"/>
+      <c r="X32" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="AA32" s="9" t="s">
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="AA32" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB32" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AC32" s="7" t="str">
+      <c r="AC32" s="6" t="str">
         <f>IF(O32="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O32)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O32)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O32)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O32)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O32)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O32)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O32)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O32)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O32)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O32)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O32)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O32)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O32)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O32)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O32)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O32)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O32)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O32)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O32)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O32)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O32)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O32)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O32)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-margit-carstensen; pers-irm-hermann</v>
       </c>
-      <c r="AD32" s="7" t="str">
+      <c r="AD32" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H32:N32,P32),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="135">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="D33" s="10">
+      <c r="C33" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="D33" s="9">
         <v>1977</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>201</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="I33" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9" t="s">
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N33" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9" t="s">
+      <c r="N33" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="8"/>
+      <c r="X33" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9" t="s">
-        <v>754</v>
-      </c>
-      <c r="AA33" s="9" t="s">
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="AA33" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB33" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AC33" s="7" t="str">
+      <c r="AC33" s="6" t="str">
         <f>IF(O33="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O33)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O33)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O33)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O33)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O33)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O33)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O33)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O33)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O33)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O33)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O33)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O33)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O33)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O33)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O33)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O33)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O33)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O33)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O33)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O33)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O33)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O33)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O33)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-armin-meier; pers-kurt-raab; pers-volker-spengler</v>
-      </c>
-      <c r="AD33" s="7" t="str">
+        <v>pers-armin-meier; pers-kurt-raab; pers-elisabeth-trissenaar</v>
+      </c>
+      <c r="AD33" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H33:N33,P33),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="150">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10">
+      <c r="C34" s="8"/>
+      <c r="D34" s="9">
         <v>1978</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="9">
         <v>119</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9" t="s">
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="Q34" s="9" t="s">
+      <c r="Q34" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9" t="s">
+      <c r="R34" s="8"/>
+      <c r="S34" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9" t="s">
+      <c r="T34" s="8"/>
+      <c r="U34" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9" t="s">
+      <c r="V34" s="8"/>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="Y34" s="9" t="s">
+      <c r="Y34" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="Z34" s="9" t="s">
+      <c r="Z34" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA34" s="9" t="s">
+      <c r="AA34" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB34" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AC34" s="7" t="str">
+      <c r="AC34" s="6" t="str">
         <f>IF(O34="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O34)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O34)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O34)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O34)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O34)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O34)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O34)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O34)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O34)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O34)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O34)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O34)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O34)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O34)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O34)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O34)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O34)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O34)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O34)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O34)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O34)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O34)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O34)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD34" s="7" t="str">
+      <c r="AD34" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H34:N34,P34),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:30" ht="225">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>1978</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <v>119</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9" t="s">
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="P35" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="Q35" s="9" t="s">
+      <c r="Q35" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9" t="s">
+      <c r="R35" s="8"/>
+      <c r="S35" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9" t="s">
+      <c r="T35" s="8"/>
+      <c r="U35" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9" t="s">
+      <c r="V35" s="8"/>
+      <c r="W35" s="8"/>
+      <c r="X35" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="Y35" s="9" t="s">
+      <c r="Y35" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="Z35" s="9" t="s">
+      <c r="Z35" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA35" s="9" t="s">
+      <c r="AA35" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB35" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="AC35" s="7" t="str">
+      <c r="AC35" s="6" t="str">
         <f>IF(O35="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O35)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O35)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O35)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O35)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O35)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O35)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O35)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O35)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O35)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O35)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O35)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O35)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O35)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O35)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O35)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O35)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O35)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O35)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O35)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O35)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O35)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O35)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O35)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-gottfried-john; pers-volker-spengler</v>
-      </c>
-      <c r="AD35" s="7" t="str">
+        <v>pers-hark-bohm; pers-ingrid-caven; pers-gottfried-john</v>
+      </c>
+      <c r="AD35" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H35:N35,P35),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:30" ht="135">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="D36" s="10">
+      <c r="C36" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="D36" s="9">
         <v>1978</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="9">
         <v>124</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K36" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9" t="s">
+      <c r="K36" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N36" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9" t="s">
-        <v>761</v>
-      </c>
-      <c r="T36" s="9" t="s">
-        <v>762</v>
-      </c>
-      <c r="U36" s="9" t="s">
+      <c r="N36" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="T36" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="U36" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9" t="s">
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="Y36" s="9" t="s">
-        <v>763</v>
-      </c>
-      <c r="Z36" s="9" t="s">
+      <c r="Y36" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="Z36" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA36" s="9" t="s">
+      <c r="AA36" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB36" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AC36" s="7" t="str">
+      <c r="AC36" s="6" t="str">
         <f>IF(O36="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O36)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O36)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O36)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O36)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O36)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O36)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O36)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O36)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O36)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O36)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O36)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O36)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O36)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O36)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O36)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O36)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O36)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O36)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O36)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O36)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O36)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O36)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O36)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-gottfried-john; pers-volker-spengler</v>
-      </c>
-      <c r="AD36" s="7" t="str">
+        <v>pers-ingrid-caven; pers-gottfried-john; pers-elisabeth-trissenaar</v>
+      </c>
+      <c r="AD36" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H36:N36,P36),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="314">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>1978</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="9">
         <v>120</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I37" s="9" t="s">
-        <v>764</v>
-      </c>
-      <c r="J37" s="9" t="s">
+      <c r="I37" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="J37" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9" t="s">
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N37" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>766</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>767</v>
-      </c>
-      <c r="Q37" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9" t="s">
-        <v>769</v>
-      </c>
-      <c r="T37" s="9" t="s">
-        <v>770</v>
-      </c>
-      <c r="U37" s="9" t="s">
+      <c r="N37" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="P37" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="R37" s="8"/>
+      <c r="S37" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="T37" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="U37" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="13">
+      <c r="V37" s="8"/>
+      <c r="W37" s="8"/>
+      <c r="X37" s="12">
         <v>1978</v>
       </c>
-      <c r="Y37" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="Z37" s="9" t="s">
+      <c r="Y37" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="Z37" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA37" s="9" t="s">
+      <c r="AA37" s="8" t="s">
         <v>113</v>
       </c>
       <c r="AB37" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="AC37" s="7" t="str">
+      <c r="AC37" s="6" t="str">
         <f>IF(O37="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O37)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O37)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O37)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O37)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O37)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O37)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O37)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O37)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O37)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O37)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O37)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O37)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O37)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O37)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O37)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O37)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O37)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O37)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O37)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O37)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O37)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O37)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O37)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-lilo-pempeit; pers-gottfried-john; pers-hanna-schygulla; pers-volker-spengler</v>
-      </c>
-      <c r="AD37" s="7" t="str">
+        <v>pers-hark-bohm; pers-lilo-pempeit; pers-gottfried-john; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
+      </c>
+      <c r="AD37" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H37:N37,P37),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="180">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>772</v>
-      </c>
-      <c r="D38" s="10">
+      <c r="C38" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="D38" s="9">
         <v>1979</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="9">
         <v>105</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K38" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9" t="s">
+      <c r="K38" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N38" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="P38" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="Q38" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9" t="s">
+      <c r="N38" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="R38" s="8"/>
+      <c r="S38" s="8"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9" t="s">
+      <c r="V38" s="8"/>
+      <c r="W38" s="8"/>
+      <c r="X38" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="AA38" s="9" t="s">
+      <c r="Y38" s="8"/>
+      <c r="Z38" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="AA38" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB38" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="AC38" s="7" t="str">
+      <c r="AC38" s="6" t="str">
         <f>IF(O38="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O38)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O38)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O38)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O38)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O38)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O38)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O38)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O38)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O38)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O38)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O38)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O38)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O38)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O38)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O38)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O38)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O38)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O38)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O38)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O38)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O38)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O38)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O38)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-margit-carstensen; pers-peer-raben; pers-hanna-schygulla; pers-volker-spengler</v>
-      </c>
-      <c r="AD38" s="7" t="str">
+        <v>pers-hark-bohm; pers-margit-carstensen; pers-peer-raben; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD38" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H38:N38,P38),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-harry-baer; pers-juliane-lorenz; pers-peer-raben</v>
+        <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="270">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>1980</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="9">
         <v>894</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I39" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>779</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9" t="s">
+      <c r="I39" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N39" s="9" t="s">
-        <v>780</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>781</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>782</v>
-      </c>
-      <c r="Q39" s="9" t="s">
-        <v>783</v>
-      </c>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9" t="s">
+      <c r="N39" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9" t="s">
+      <c r="V39" s="8"/>
+      <c r="W39" s="8"/>
+      <c r="X39" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9" t="s">
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AA39" s="9" t="s">
+      <c r="AA39" s="8" t="s">
         <v>318</v>
       </c>
       <c r="AB39" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AC39" s="7" t="str">
+      <c r="AC39" s="6" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-gottfried-john; pers-brigitte-mira; pers-hanna-schygulla; pers-barbara-valentin; pers-volker-spengler</v>
-      </c>
-      <c r="AD39" s="7" t="str">
+        <v>pers-margit-carstensen; pers-gottfried-john; pers-brigitte-mira; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
+      </c>
+      <c r="AD39" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H39:N39,P39),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="370">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="9">
         <v>1981</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="9">
         <v>115</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I40" s="9" t="s">
-        <v>784</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>785</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9" t="s">
+      <c r="I40" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N40" s="9" t="s">
-        <v>787</v>
-      </c>
-      <c r="O40" s="9" t="s">
-        <v>788</v>
-      </c>
-      <c r="P40" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="Q40" s="9" t="s">
-        <v>814</v>
-      </c>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9" t="s">
+      <c r="N40" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40" s="9" t="s">
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="Y40" s="9"/>
-      <c r="Z40" s="9" t="s">
-        <v>790</v>
-      </c>
-      <c r="AA40" s="9" t="s">
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="AA40" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB40" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AC40" s="7" t="str">
+      <c r="AC40" s="6" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-harry-baer; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-brigitte-mira; pers-hanna-schygulla; pers-barbara-valentin</v>
-      </c>
-      <c r="AD40" s="7" t="str">
+        <v>pers-hark-bohm; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-brigitte-mira; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD40" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H40:N40,P40),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-ballhaus; pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="45">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>791</v>
-      </c>
-      <c r="D41" s="10">
+      <c r="C41" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="D41" s="9">
         <v>1981</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="9">
         <v>91</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="I41" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9" t="s">
-        <v>792</v>
-      </c>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9" t="s">
-        <v>793</v>
-      </c>
-      <c r="Q41" s="9" t="s">
-        <v>794</v>
-      </c>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9" t="s">
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="Q41" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="R41" s="8"/>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="8"/>
+      <c r="V41" s="8"/>
+      <c r="W41" s="8"/>
+      <c r="X41" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="9" t="s">
-        <v>795</v>
-      </c>
-      <c r="AA41" s="9" t="s">
+      <c r="Y41" s="8"/>
+      <c r="Z41" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="AA41" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB41" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="AC41" s="7" t="str">
+      <c r="AC41" s="6" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
         <v/>
       </c>
-      <c r="AD41" s="7" t="str">
+      <c r="AD41" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H41:N41,P41),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:30" ht="240">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>796</v>
-      </c>
-      <c r="D42" s="10">
+      <c r="C42" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D42" s="9">
         <v>1981</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="9">
         <v>113</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I42" s="9" t="s">
-        <v>797</v>
-      </c>
-      <c r="J42" s="9" t="s">
+      <c r="I42" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="O42" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="K42" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9" t="s">
-        <v>798</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>799</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>800</v>
-      </c>
-      <c r="P42" s="9" t="s">
-        <v>801</v>
-      </c>
-      <c r="Q42" s="9" t="s">
-        <v>802</v>
-      </c>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9" t="s">
+      <c r="Q42" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="R42" s="8"/>
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9" t="s">
+      <c r="V42" s="8"/>
+      <c r="W42" s="8"/>
+      <c r="X42" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9" t="s">
-        <v>803</v>
-      </c>
-      <c r="AA42" s="9" t="s">
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="AA42" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB42" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="AC42" s="7" t="str">
+      <c r="AC42" s="6" t="str">
         <f>IF(O42="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O42)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O42)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O42)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O42)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O42)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O42)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O42)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O42)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O42)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O42)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O42)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O42)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O42)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O42)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O42)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O42)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O42)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O42)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O42)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O42)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O42)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O42)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O42)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-gunther-kaufmann</v>
-      </c>
-      <c r="AD42" s="7" t="str">
+        <v>pers-hark-bohm; pers-gunther-kaufmann</v>
+      </c>
+      <c r="AD42" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H42:N42,P42),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="255">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="9">
         <v>1981</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="10"/>
-      <c r="G43" s="9" t="s">
+      <c r="F43" s="9"/>
+      <c r="G43" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9" t="s">
-        <v>804</v>
-      </c>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9" t="s">
-        <v>805</v>
-      </c>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9" t="s">
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="R43" s="8"/>
+      <c r="S43" s="8"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9" t="s">
+      <c r="V43" s="8"/>
+      <c r="W43" s="8"/>
+      <c r="X43" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9" t="s">
-        <v>806</v>
-      </c>
-      <c r="AA43" s="9" t="s">
+      <c r="Y43" s="8"/>
+      <c r="Z43" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="AA43" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB43" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AC43" s="7" t="str">
+      <c r="AC43" s="6" t="str">
         <f>IF(O43="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O43)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O43)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O43)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O43)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O43)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O43)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O43)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O43)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O43)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O43)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O43)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O43)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O43)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O43)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O43)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O43)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O43)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O43)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O43)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O43)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O43)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O43)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O43)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-lilo-pempeit; pers-gunther-kaufmann; pers-volker-spengler</v>
-      </c>
-      <c r="AD43" s="7" t="str">
+        <v>pers-lilo-pempeit; pers-gunther-kaufmann</v>
+      </c>
+      <c r="AD43" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H43:N43,P43),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:30" ht="270">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <v>1982</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="9">
         <v>107</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="9" t="s">
-        <v>807</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>779</v>
-      </c>
-      <c r="K44" s="9" t="s">
+      <c r="I44" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="L44" s="9" t="s">
-        <v>808</v>
-      </c>
-      <c r="M44" s="9" t="s">
+      <c r="M44" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N44" s="9" t="s">
-        <v>809</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>810</v>
-      </c>
-      <c r="P44" s="9" t="s">
-        <v>811</v>
-      </c>
-      <c r="Q44" s="9" t="s">
-        <v>812</v>
-      </c>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
-      <c r="U44" s="9" t="s">
+      <c r="N44" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q44" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="R44" s="8"/>
+      <c r="S44" s="8"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9" t="s">
+      <c r="V44" s="8"/>
+      <c r="W44" s="8"/>
+      <c r="X44" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="Y44" s="9"/>
-      <c r="Z44" s="9" t="s">
-        <v>813</v>
-      </c>
-      <c r="AA44" s="9" t="s">
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="AA44" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AB44" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AC44" s="7" t="str">
+      <c r="AC44" s="6" t="str">
         <f>IF(O44="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O44)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O44)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O44)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O44)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O44)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O44)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O44)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O44)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O44)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O44)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O44)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O44)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O44)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O44)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O44)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O44)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O44)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O44)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O44)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O44)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O44)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O44)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O44)),'Référentiel entourage'!$A$24,"")))</f>
         <v>pers-gunther-kaufmann</v>
       </c>
-      <c r="AD44" s="7" t="str">
+      <c r="AD44" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H44:N44,P44),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-juliane-lorenz; pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-michael-fengler; pers-juliane-lorenz; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
   </sheetData>
@@ -7390,10 +8201,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="107" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2" ht="133" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -7500,7 +8311,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="71" customHeight="1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>344</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -7508,7 +8319,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="71" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>346</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -7516,7 +8327,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="109" customHeight="1">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -7524,7 +8335,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="109" customHeight="1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -7532,7 +8343,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="76" customHeight="1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>350</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -7549,7 +8360,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7559,943 +8370,1062 @@
     <col min="7" max="14" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" ht="98">
+      <c r="A1" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="15" t="s">
+        <v>843</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>844</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" ht="156">
+      <c r="A2" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B2" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="D2" s="18" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="135">
-      <c r="A2" s="6" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="G2" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="18"/>
+      <c r="M2" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="N2" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="J2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:14" ht="60">
+      <c r="A3" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="B3" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="C3" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="D3" s="18" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="180">
-      <c r="A3" s="6" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="G3" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="N3" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="K3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="48">
+      <c r="A4" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1" t="s">
+      <c r="B4" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="C4" s="18" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="75">
-      <c r="A4" s="6" t="s">
+      <c r="D4" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="H4" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="I4" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="L4" s="18"/>
+      <c r="M4" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="N4" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="J4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:14" ht="182">
+      <c r="A5" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>795</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>796</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18" t="s">
+        <v>798</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>799</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>800</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>801</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="L5" s="18"/>
+      <c r="M5" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="84">
+      <c r="A6" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="B6" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1" t="s">
+      <c r="C6" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="D6" s="18" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="45">
-      <c r="A5" s="6" t="s">
+      <c r="E6" s="18"/>
+      <c r="F6" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="G6" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="H6" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="I6" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="J6" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="K6" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="L6" s="18"/>
+      <c r="M6" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="N6" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="K5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:14" ht="156">
+      <c r="A7" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
+      <c r="B7" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="C7" s="18" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="90">
-      <c r="A6" s="6" t="s">
+      <c r="D7" s="18" t="s">
         <v>412</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E7" s="18"/>
+      <c r="F7" s="18" t="s">
+        <v>805</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="H7" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="I7" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
+      <c r="J7" s="18" t="s">
         <v>416</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="K7" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="L7" s="18"/>
+      <c r="M7" s="16" t="s">
         <v>418</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="N7" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="J6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:14" ht="72">
+      <c r="A8" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="B8" s="18" t="s">
         <v>421</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1" t="s">
+      <c r="C8" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="D8" s="18" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="180">
-      <c r="A7" s="6" t="s">
+      <c r="E8" s="18"/>
+      <c r="F8" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="G8" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="I8" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="J8" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="K8" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="L8" s="18"/>
+      <c r="M8" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="N8" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="J7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:14" ht="156">
+      <c r="A9" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="B9" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1" t="s">
+      <c r="C9" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="D9" s="18" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="90">
-      <c r="A8" s="6" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="s">
         <v>435</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="H9" s="18"/>
+      <c r="I9" s="18" t="s">
         <v>436</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="J9" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="K9" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="L9" s="18" t="s">
         <v>439</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="M9" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="N9" s="18" t="s">
         <v>441</v>
       </c>
-      <c r="J8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:14" ht="144">
+      <c r="A10" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>591</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>807</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>808</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>809</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>810</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>811</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>812</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="108">
+      <c r="A11" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="B11" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1" t="s">
+      <c r="C11" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="D11" s="18" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="195">
-      <c r="A9" s="6" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H11" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="I11" s="18"/>
+      <c r="J11" s="18" t="s">
         <v>447</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="K11" s="19" t="s">
         <v>448</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="L11" s="18"/>
+      <c r="M11" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="N11" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
+    </row>
+    <row r="12" spans="1:14" ht="120">
+      <c r="A12" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="B12" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="C12" s="18" t="s">
         <v>453</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="D12" s="18" t="s">
+        <v>815</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="H12" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="I12" s="18" t="s">
         <v>455</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="J12" s="18" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="120">
-      <c r="A10" s="6" t="s">
+      <c r="K12" s="19" t="s">
         <v>457</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="L12" s="18"/>
+      <c r="M12" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="N12" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="D10" s="1" t="s">
+    </row>
+    <row r="13" spans="1:14" ht="84">
+      <c r="A13" s="17" t="s">
         <v>460</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="B13" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1" t="s">
+      <c r="C13" s="18" t="s">
         <v>462</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="D13" s="18" t="s">
         <v>463</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1" t="s">
+      <c r="E13" s="18"/>
+      <c r="F13" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="I13" s="18" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="150">
-      <c r="A11" s="6" t="s">
+      <c r="J13" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="K13" s="19" t="s">
         <v>467</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="L13" s="18"/>
+      <c r="M13" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="N13" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="H11" s="1" t="s">
+    </row>
+    <row r="14" spans="1:14" ht="96">
+      <c r="A14" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="B14" s="18" t="s">
         <v>471</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="C14" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="D14" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1" t="s">
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="105">
-      <c r="A12" s="6" t="s">
+      <c r="K14" s="19" t="s">
         <v>476</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="L14" s="18"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="15" spans="1:14" ht="84">
+      <c r="A15" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="B15" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="C15" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="D15" s="18" t="s">
         <v>481</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18" t="s">
         <v>482</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="H15" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1" t="s">
+      <c r="I15" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="J15" s="18" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="105">
-      <c r="A13" s="6" t="s">
+      <c r="K15" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="L15" s="18"/>
+      <c r="M15" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="N15" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="C13" s="1" t="s">
+    </row>
+    <row r="16" spans="1:14" ht="72">
+      <c r="A16" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="B16" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
+      <c r="C16" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
+      <c r="D16" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1" t="s">
+      <c r="I16" s="18" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="105">
-      <c r="A14" s="6" t="s">
+      <c r="J16" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="K16" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="L16" s="18"/>
+      <c r="M16" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="N16" s="18" t="s">
         <v>497</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
+    </row>
+    <row r="17" spans="1:14" ht="72">
+      <c r="A17" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="B17" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="C17" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="D17" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="E17" s="18"/>
+      <c r="F17" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1" t="s">
+      <c r="G17" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="H17" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="I17" s="18" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="90">
-      <c r="A15" s="6" t="s">
+      <c r="J17" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="K17" s="19" t="s">
         <v>506</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="L17" s="18"/>
+      <c r="M17" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="N17" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H15" s="1" t="s">
+    </row>
+    <row r="18" spans="1:14" ht="204">
+      <c r="A18" s="17" t="s">
         <v>509</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="B18" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>510</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="D18" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="E18" s="18"/>
+      <c r="F18" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1" t="s">
+      <c r="H18" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="I18" s="18" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="75">
-      <c r="A16" s="6" t="s">
+      <c r="J18" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="K18" s="19" t="s">
         <v>516</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="L18" s="18"/>
+      <c r="M18" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="N18" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="D16" s="1" t="s">
+    </row>
+    <row r="19" spans="1:14" ht="42">
+      <c r="A19" s="17" t="s">
         <v>518</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
+      <c r="B19" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>519</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="D19" s="18" t="s">
         <v>520</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="E19" s="18"/>
+      <c r="F19" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="G19" s="18" t="s">
         <v>521</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="H19" s="18" t="s">
         <v>522</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="I19" s="18" t="s">
         <v>523</v>
       </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
+      <c r="J19" s="18"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N19" s="18" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="240">
-      <c r="A17" s="6" t="s">
+    <row r="20" spans="1:14" ht="28">
+      <c r="A20" s="17" t="s">
         <v>526</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B20" s="18" t="s">
         <v>527</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="C20" s="18" t="s">
         <v>528</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="D20" s="18" t="s">
         <v>529</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="E20" s="18"/>
+      <c r="F20" s="18" t="s">
         <v>530</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="G20" s="18" t="s">
         <v>531</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="H20" s="18" t="s">
         <v>532</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="I20" s="18" t="s">
         <v>533</v>
       </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1" t="s">
+      <c r="J20" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="L20" s="18"/>
+      <c r="M20" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N20" s="18" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="45">
-      <c r="A18" s="6" t="s">
+    <row r="21" spans="1:14" ht="156">
+      <c r="A21" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B21" s="18" t="s">
         <v>537</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="C21" s="18" t="s">
         <v>538</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="D21" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="E21" s="18"/>
+      <c r="F21" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="G21" s="18" t="s">
         <v>540</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="H21" s="18" t="s">
         <v>541</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1" t="s">
+      <c r="I21" s="18" t="s">
         <v>542</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="J21" s="18" t="s">
+        <v>818</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>819</v>
+      </c>
+      <c r="L21" s="18" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="30">
-      <c r="A19" s="6" t="s">
+      <c r="M21" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="N21" s="18" t="s">
         <v>545</v>
       </c>
-      <c r="C19" s="1" t="s">
+    </row>
+    <row r="22" spans="1:14" ht="48">
+      <c r="A22" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="B22" s="18" t="s">
         <v>547</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
+      <c r="C22" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="D22" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="E22" s="18"/>
+      <c r="F22" s="18" t="s">
         <v>550</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="G22" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="H22" s="18" t="s">
         <v>551</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1" t="s">
+      <c r="I22" s="18" t="s">
         <v>552</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="J22" s="18" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="180">
-      <c r="A20" s="6" t="s">
+      <c r="K22" s="19" t="s">
         <v>554</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="L22" s="18"/>
+      <c r="M22" s="16" t="s">
         <v>555</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="N22" s="18" t="s">
         <v>556</v>
       </c>
-      <c r="D20" s="1" t="s">
+    </row>
+    <row r="23" spans="1:14" ht="168">
+      <c r="A23" s="23" t="s">
+        <v>820</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>821</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>822</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>823</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>824</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>825</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>826</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>827</v>
+      </c>
+      <c r="L23" s="18"/>
+      <c r="M23" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="N23" s="18" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="42">
+      <c r="A24" s="17" t="s">
         <v>557</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="B24" s="18" t="s">
         <v>558</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="C24" s="18" t="s">
         <v>559</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="D24" s="18" t="s">
         <v>560</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="E24" s="18"/>
+      <c r="F24" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="H24" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="I24" s="18" t="s">
         <v>562</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="J24" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="K24" s="19" t="s">
         <v>564</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="L24" s="18"/>
+      <c r="M24" s="16" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="60">
-      <c r="A21" s="6" t="s">
+      <c r="N24" s="18" t="s">
         <v>566</v>
       </c>
-      <c r="B21" s="6" t="s">
+    </row>
+    <row r="25" spans="1:14" ht="60">
+      <c r="A25" s="17" t="s">
         <v>567</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="B25" s="18" t="s">
         <v>568</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="C25" s="18" t="s">
         <v>569</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1" t="s">
+      <c r="D25" s="18" t="s">
         <v>570</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="I25" s="18" t="s">
         <v>571</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J25" s="18" t="s">
         <v>572</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K25" s="19" t="s">
         <v>573</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L25" s="18"/>
+      <c r="M25" s="22" t="s">
         <v>574</v>
       </c>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1" t="s">
+      <c r="N25" s="18" t="s">
         <v>575</v>
       </c>
-      <c r="N21" s="1" t="s">
+    </row>
+    <row r="26" spans="1:14" ht="96">
+      <c r="A26" s="25" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="45">
-      <c r="A22" s="6" t="s">
+      <c r="B26" s="26" t="s">
         <v>577</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C26" s="26" t="s">
         <v>578</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D26" s="26" t="s">
         <v>579</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26" t="s">
         <v>580</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="K26" s="27" t="s">
         <v>581</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="L26" s="26"/>
+      <c r="M26" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="N26" s="26" t="s">
         <v>582</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="75">
-      <c r="A23" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="105">
-      <c r="A24" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>604</v>
+    </row>
+    <row r="27" spans="1:14" ht="124">
+      <c r="A27" s="28" t="s">
+        <v>831</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>833</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>834</v>
+      </c>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28" t="s">
+        <v>530</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>835</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>836</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>838</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="L27" s="28"/>
+      <c r="M27" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>841</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61718449-BA5A-5748-9C0E-213E96A3AACC}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0B80929-9C38-4A44-A37A-4DC2EB3BD8F5}"/>
   <bookViews>
-    <workbookView xWindow="6600" yWindow="600" windowWidth="10000" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6600" yWindow="600" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -2771,12 +2771,6 @@
   </si>
   <si>
     <t>Elvira, femme transgenre rejetée de presque tous sauf de Zora la Rouge, déambule désespérément dans Francfort sur les traces de son passé et d’une vie douloureuse. Elle revient sur son enfance au couvent, son travail aux abattoirs, son mariage avec la fille d’un boucher et son amour pour Anton Saitz.</t>
-  </si>
-  <si>
-    <t>La séquence où Anton Saitz et son entourage imitent la comédie hollywoodienne You’re Never Too Young fait de la régression un principe collectif. Anton, travesti en tennisman, devient le miroir de la transformation qu’Erwin devenu Elvira a imposée à son corps pour répondre au désir d’un autre. Fassbinder associe ainsi trois formes d’aliénation : soumission au regard d’autrui, discipline capitaliste des corps et assujettissement du spectateur aux images hollywoodiennes.</t>
-  </si>
-  <si>
-    <t>Norman Taurog, You’re Never Too Young (1955)</t>
   </si>
   <si>
     <t>identité|transidentité|aliénation|regard|corps|capitalisme|Hollywood|régression|Francfort</t>
@@ -3386,12 +3380,40 @@
   <si>
     <t>Colonne2</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Réalisé dans l’urgence après le suicide d’Armin Meier, L’Année des treize lunes ne se réduit pas à la transposition d’un deuil privé. Fassbinder reprend certains éléments de la vie de son ancien compagnon, mais les inscrit dans une réflexion plus vaste sur l’abandon, l’exploitation et l’impossibilité de réparer le passé. Le récit des cinq derniers jours d’Elvira est construit comme un parcours à rebours : abattoirs, couvent, bureaux d’Anton, appartement familial. À chaque étape, elle cherche dans les lieux et les récits d’autrui une continuité biographique qui lui échappe. Le film fait ainsi du corps et de la mémoire les deux faces d’une même histoire brisée. L’approche de Claire Kaiser part de la présence physique de Volker Spengler et de la manière dont Fassbinder la filme. Le corps d’Elvira, lourd, meurtri, changeant d’apparence et constamment exposé aux regards, s’écarte de toute représentation idéalisée de la transition. Cette « défiguration » n’a pas pour fonction de réduire le personnage au grotesque : elle rend visibles les violences qui l’ont façonné. Dès l’ouverture, Elvira est battue et contrainte de ramper ; dans l’appartement, Christof détruit son image en la plaçant devant le miroir ; à l’abattoir, son récit se superpose aux opérations d’équarrissage. La mise en scène rapproche alors corps humain et carcasse animale. Pour Kaiser, cette assimilation possède une portée politique : l’organisation capitaliste transforme le vivant en matière exploitable, tandis que le trafic de viande conduit au trafic des êtres et à la prostitution. Kaiser prolonge cette lecture à travers Anton Saitz. Rescapé de Bergen-Belsen, celui-ci reproduit dans ses entreprises la discipline apprise dans le camp : « la même structure d’ordre, d’obéissance, de devoir et de peur » (scénario de Fassbinder, cité par Claire Kaiser). La victime historique devient donc elle-même l’agent d’un ordre économique totalitaire, sans que le film efface pour autant l’asymétrie des positions. La scène où Anton et ses hommes imitent </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">You’re Never Too Young (Chérie je me sens rajeunir, 1955) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>de Norman Taurog condense ce mécanisme : chacun reproduit les gestes du chef, qui copie lui-même une image hollywoodienne. L’imitation burlesque révèle un système où les corps obéissent à une loi qu’ils ne comprennent pas. Chez Kaiser, le corps d’Elvira est ainsi politique parce qu’il enregistre matériellement le refoulement historique, la domination sociale et la circulation de la violence. Thomas Elsaesser adopte un autre point de départ. Il lit le film comme la « solution imaginaire » d’un problème historique spécifiquement allemand : comment vivre, aimer et se définir après Auschwitz ? L’amour sans retour d’Elvira pour Anton devient le noyau d’une rencontre à la fois indispensable et impossible entre un Allemand né sous le nazisme et un Juif survivant des camps. Elsaesser ne fait pourtant pas des personnages de simples symboles. Il insiste au contraire sur l’impossibilité de convertir la faute en dette acquittable : aucune compensation ne peut abolir l’incommensurabilité entre victimes et héritiers de la culpabilité. Elvira sacrifie son corps, son nom, sa famille et sa place sociale pour obtenir d’Anton une reconnaissance qui lui demeure refusée ; ce sacrifice sans fondement rend sensible l’impasse d’un désir de réparation. Cette lecture est aussi temporelle. Elvira et Anton sont tous deux pris dans des boucles : elle revient sur les lieux de sa vie, tandis qu’Anton répète une comédie américaine et une discipline héritée du passé concentrationnaire. Leur rencontre est indéfiniment différée. Elsaesser décrit alors le corps d’Elvira comme une sorte de machine à remonter le temps, où les identités masculine, féminine, homosexuelle, asexuée et transsexuelle se succèdent sans former une évolution stable. Ce corps, à la fois intérieur et extérieur, présence et absence, devient une « plaie ouverte », un « corps sans peau » (Thomas Elsaesser, p. 346) sur lequel s’inscrivent le désir des autres et une histoire nationale non résolue. Les deux analyses se complètent donc sans se confondre. Kaiser montre comment la critique s’élabore concrètement par le jeu de l’acteur, les humiliations, les miroirs, l’abattoir et les gestes d’imitation ; Elsaesser interprète cette fragilité corporelle comme une forme historique, travaillée par le déphasage temporel, la culpabilité et l’impossible relation entre Allemands et Juifs après la Shoah. Leur articulation permet enfin de définir le film comme un mélodrame post-classique : la souffrance n’y est ni réprimée ni véritablement mise en mots, mais exprimée par un corps qui déborde toutes les identités assignables. Né d’une décision de survivre au deuil, le film transforme ainsi la douleur intime en interrogation politique sur ce que signifie « devenir allemand » après Auschwitz.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Elsaesser, Rainer Werner Fassbinder : un cinéaste d’Allemagne, Paris, Centre Pompidou, 2005, chap. 8, p. 327-350.
+Claire Kaiser, « Rainer Werner Fassbinder », conférence à la Cinémathèque de Toulouse, 2016 : https://www.youtube.com/watch?v=TMhzoG7NsLsb
+Rainer Werner Fassbinder, scénario de L’Année des treize lunes, cité par Claire Kaiser dans cette conférence.
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3496,6 +3518,17 @@
       <color rgb="FF000000"/>
       <name val="IBM Plex Mono"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -3581,7 +3614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3667,6 +3700,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7390,7 +7426,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="135">
+    <row r="36" spans="1:30" ht="409.6">
       <c r="A36" s="8" t="s">
         <v>273</v>
       </c>
@@ -7441,11 +7477,11 @@
         <v>738</v>
       </c>
       <c r="R36" s="8"/>
-      <c r="S36" s="8" t="s">
-        <v>739</v>
+      <c r="S36" s="30" t="s">
+        <v>843</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>740</v>
+        <v>844</v>
       </c>
       <c r="U36" s="8" t="s">
         <v>275</v>
@@ -7456,7 +7492,7 @@
         <v>259</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Z36" s="8" t="s">
         <v>112</v>
@@ -7502,7 +7538,7 @@
         <v>34</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>160</v>
@@ -7513,23 +7549,23 @@
         <v>174</v>
       </c>
       <c r="N37" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="O37" s="8" t="s">
+      <c r="Q37" s="8" t="s">
         <v>744</v>
-      </c>
-      <c r="P37" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>746</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="8" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="U37" s="8" t="s">
         <v>280</v>
@@ -7540,7 +7576,7 @@
         <v>1978</v>
       </c>
       <c r="Y37" s="8" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="Z37" s="8" t="s">
         <v>112</v>
@@ -7568,7 +7604,7 @@
         <v>283</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D38" s="9">
         <v>1979</v>
@@ -7599,16 +7635,16 @@
         <v>174</v>
       </c>
       <c r="N38" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="O38" s="8" t="s">
+      <c r="Q38" s="8" t="s">
         <v>752</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>754</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="8"/>
@@ -7623,7 +7659,7 @@
       </c>
       <c r="Y38" s="8"/>
       <c r="Z38" s="8" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AA38" s="8" t="s">
         <v>45</v>
@@ -7666,10 +7702,10 @@
         <v>34</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>479</v>
@@ -7679,16 +7715,16 @@
         <v>174</v>
       </c>
       <c r="N39" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="O39" s="8" t="s">
+      <c r="Q39" s="8" t="s">
         <v>759</v>
-      </c>
-      <c r="P39" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>761</v>
       </c>
       <c r="R39" s="8"/>
       <c r="S39" s="8"/>
@@ -7746,33 +7782,33 @@
         <v>34</v>
       </c>
       <c r="I40" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="K40" s="8" t="s">
         <v>762</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>764</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="8" t="s">
         <v>174</v>
       </c>
       <c r="N40" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="P40" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="O40" s="8" t="s">
-        <v>766</v>
-      </c>
-      <c r="P40" s="8" t="s">
-        <v>767</v>
-      </c>
       <c r="Q40" s="8" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="R40" s="8"/>
       <c r="S40" s="8" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="T40" s="8"/>
       <c r="U40" s="8" t="s">
@@ -7785,7 +7821,7 @@
       </c>
       <c r="Y40" s="8"/>
       <c r="Z40" s="8" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AA40" s="8" t="s">
         <v>45</v>
@@ -7810,7 +7846,7 @@
         <v>298</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D41" s="9">
         <v>1981</v>
@@ -7835,14 +7871,14 @@
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
       <c r="N41" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="8" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="Q41" s="8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="R41" s="8"/>
       <c r="S41" s="8"/>
@@ -7855,7 +7891,7 @@
       </c>
       <c r="Y41" s="8"/>
       <c r="Z41" s="8" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="AA41" s="8" t="s">
         <v>45</v>
@@ -7880,7 +7916,7 @@
         <v>302</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D42" s="9">
         <v>1981</v>
@@ -7898,29 +7934,29 @@
         <v>34</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="O42" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="N42" s="8" t="s">
+      <c r="P42" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="O42" s="8" t="s">
+      <c r="Q42" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="Q42" s="8" t="s">
-        <v>780</v>
       </c>
       <c r="R42" s="8"/>
       <c r="S42" s="8"/>
@@ -7935,7 +7971,7 @@
       </c>
       <c r="Y42" s="8"/>
       <c r="Z42" s="8" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AA42" s="8" t="s">
         <v>45</v>
@@ -7982,11 +8018,11 @@
       <c r="M43" s="8"/>
       <c r="N43" s="8"/>
       <c r="O43" s="8" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="P43" s="8"/>
       <c r="Q43" s="8" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="R43" s="8"/>
       <c r="S43" s="8"/>
@@ -8001,7 +8037,7 @@
       </c>
       <c r="Y43" s="8"/>
       <c r="Z43" s="8" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AA43" s="8" t="s">
         <v>45</v>
@@ -8044,31 +8080,31 @@
         <v>34</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M44" s="8" t="s">
         <v>174</v>
       </c>
       <c r="N44" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="P44" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="O44" s="8" t="s">
+      <c r="Q44" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="P44" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
@@ -8083,7 +8119,7 @@
       </c>
       <c r="Y44" s="8"/>
       <c r="Z44" s="8" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AA44" s="8" t="s">
         <v>45</v>
@@ -8384,7 +8420,7 @@
         <v>355</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>356</v>
@@ -8402,10 +8438,10 @@
         <v>360</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="M1" s="16" t="s">
         <v>361</v>
@@ -8536,42 +8572,42 @@
     </row>
     <row r="5" spans="1:14" ht="182">
       <c r="A5" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>793</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>794</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>795</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>796</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>797</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="18" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>390</v>
       </c>
       <c r="H5" s="18" t="s">
+        <v>797</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>798</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="K5" s="19" t="s">
         <v>800</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>801</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>802</v>
       </c>
       <c r="L5" s="18"/>
       <c r="M5" s="16" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="84">
@@ -8629,7 +8665,7 @@
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="18" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>413</v>
@@ -8734,13 +8770,13 @@
     </row>
     <row r="10" spans="1:14" ht="144">
       <c r="A10" s="17" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>591</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>365</v>
@@ -8750,26 +8786,26 @@
         <v>356</v>
       </c>
       <c r="G10" s="18" t="s">
+        <v>806</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>807</v>
+      </c>
+      <c r="I10" s="18" t="s">
         <v>808</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="J10" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="K10" s="21" t="s">
         <v>810</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>811</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>812</v>
       </c>
       <c r="L10" s="18"/>
       <c r="M10" s="16" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="108">
@@ -8819,7 +8855,7 @@
         <v>453</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -8950,7 +8986,7 @@
       </c>
       <c r="L15" s="18"/>
       <c r="M15" s="16" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="N15" s="18" t="s">
         <v>487</v>
@@ -9070,7 +9106,7 @@
       </c>
       <c r="L18" s="18"/>
       <c r="M18" s="16" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="N18" s="18" t="s">
         <v>517</v>
@@ -9179,10 +9215,10 @@
         <v>542</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="L21" s="18" t="s">
         <v>543</v>
@@ -9236,16 +9272,16 @@
     </row>
     <row r="23" spans="1:14" ht="168">
       <c r="A23" s="23" t="s">
+        <v>818</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>819</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>820</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="D23" s="18" t="s">
         <v>821</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>822</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>823</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18" t="s">
@@ -9255,23 +9291,23 @@
         <v>402</v>
       </c>
       <c r="H23" s="18" t="s">
+        <v>822</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>823</v>
+      </c>
+      <c r="J23" s="24" t="s">
         <v>824</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="K23" s="19" t="s">
         <v>825</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>826</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>827</v>
       </c>
       <c r="L23" s="18"/>
       <c r="M23" s="16" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="42">
@@ -9382,7 +9418,7 @@
       </c>
       <c r="L26" s="26"/>
       <c r="M26" s="16" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="N26" s="26" t="s">
         <v>582</v>
@@ -9390,42 +9426,42 @@
     </row>
     <row r="27" spans="1:14" ht="124">
       <c r="A27" s="28" t="s">
+        <v>829</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>830</v>
+      </c>
+      <c r="C27" s="28" t="s">
         <v>831</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="D27" s="28" t="s">
         <v>832</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>833</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>834</v>
       </c>
       <c r="E27" s="28"/>
       <c r="F27" s="28" t="s">
         <v>530</v>
       </c>
       <c r="G27" s="28" t="s">
+        <v>833</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>834</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="J27" s="28" t="s">
         <v>836</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>837</v>
-      </c>
-      <c r="J27" s="28" t="s">
-        <v>838</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>839</v>
       </c>
       <c r="L27" s="28"/>
       <c r="M27" s="8" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="N27" s="28" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0B80929-9C38-4A44-A37A-4DC2EB3BD8F5}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E272DCBC-6554-1C48-BA2E-D2634DDCB039}"/>
   <bookViews>
-    <workbookView xWindow="6600" yWindow="600" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19100" yWindow="800" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="850">
   <si>
     <t>ID</t>
   </si>
@@ -186,33 +186,6 @@
   </si>
   <si>
     <t>Katzelmacher</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">Le film dénonce la violence exercée par une société étriquée contre les étrnagers, violence que le personnage principal, d'origine grecque, reconduit avec des individus encore plus dominés que lui. Film à l'esthétique avant-gardiste, brechtienne par son caractère anti-illustionniste. Il est constitué d'une suite de brefs tableaux, d'images figées, de plans fontaux. Les mouvements de caméra sont rares : des travellings latéraux, sans profondeur d'images, conservent une forme de théâtralité à l'image. Comme d'autres films  de RWF de la période, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">Le bouc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">vise un public qui n'est ni restreint et cinéphile, ni populaire.  </t>
-    </r>
   </si>
   <si>
     <t>Films_images/Le_Bouc.jpg</t>
@@ -3058,26 +3031,6 @@
   </si>
   <si>
     <t>Wikipédia : https://fr.wikipedia.org/wiki/Querelle_(film)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">À Zurich en 1938, Willie, chanteuse allemande, aime Robert Mendelsson, musicien juif suisse engagé dans une organisation qui aide des Juifs à fuir l’Allemagne nazie. Séparés par les événements, Robert poursuit la lutte clandestine tandis que Willie devient une vedette du Reich grâce à la chanson « Lili Marleen », sans renoncer à aider Robert et sa famille.le film s'inspire de la créatrice de la chanson </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>Lili Marleen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> : Lale Andersen. Une de ses chansons d'amour connut pendant la seconde guerre mondiale un succès inédit, devant une sorte d'hymne affectif pour les soldats ; une chanson d'amour devenait emblématique de la guerre. </t>
-    </r>
   </si>
   <si>
     <t>Projet initié par le producteur Luggi Waldleitner autour de la désormais star Schygulla. Cette dernière refuse que le scénariste Mandred Purzer, issu du cinéma commercial et notoirement de droite, réalise le film. Elle impose RWF qui a pourtant juré de ne plus travailler avec elle mais accepte.  A l'annonce du projet, la presse déclare que RWF a "vendu son âme". RWF affronte deux écueils : celui du cinéma  de papa qu'incarnent producteur et scénariste, risque de s'inscrire dans la nostalgie et le kitsch qui glamourise la période nazie. RWF s'en libère en faisant apparaîter la manière dont la société de consommation et le capitalisme sont la poursuite du fascisme. Guerre et technologie médiatique relèvent d'une même logique de domination pour un pouvoir devenu invisible, car masqué par les signes qui l'incarnent.</t>
@@ -3381,13 +3334,46 @@
     <t>Colonne2</t>
   </si>
   <si>
+    <t xml:space="preserve">Thomas Elsaesser, Rainer Werner Fassbinder : un cinéaste d’Allemagne, Paris, Centre Pompidou, 2005, chap. 8, p. 327-350.
+Claire Kaiser, « Rainer Werner Fassbinder », conférence à la Cinémathèque de Toulouse, 2016 : https://www.youtube.com/watch?v=TMhzoG7NsLsb
+Rainer Werner Fassbinder, scénario de L’Année des treize lunes, cité par Claire Kaiser dans cette conférence.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Le film dénonce la violence exercée par une société étriquée contre les étrnagers, violence que le personnage principal, d'origine grecque, reconduit avec des individus encore plus dominés que lui. Film à l'esthétique avant-gardiste, brechtienne par son caractère anti-illustionniste. Il est constitué d'une suite de brefs tableaux, d'images figées, de plans fontaux. Les mouvements de caméra sont rares : des travellings latéraux, sans profondeur d'images, conservent une forme de théâtralité à l'image. Comme d'autres films  de RWF de la période, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Le bouc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">vise un public qui n'est ni restreint et cinéphile, ni populaire.  </t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Réalisé dans l’urgence après le suicide d’Armin Meier, L’Année des treize lunes ne se réduit pas à la transposition d’un deuil privé. Fassbinder reprend certains éléments de la vie de son ancien compagnon, mais les inscrit dans une réflexion plus vaste sur l’abandon, l’exploitation et l’impossibilité de réparer le passé. Le récit des cinq derniers jours d’Elvira est construit comme un parcours à rebours : abattoirs, couvent, bureaux d’Anton, appartement familial. À chaque étape, elle cherche dans les lieux et les récits d’autrui une continuité biographique qui lui échappe. Le film fait ainsi du corps et de la mémoire les deux faces d’une même histoire brisée. L’approche de Claire Kaiser part de la présence physique de Volker Spengler et de la manière dont Fassbinder la filme. Le corps d’Elvira, lourd, meurtri, changeant d’apparence et constamment exposé aux regards, s’écarte de toute représentation idéalisée de la transition. Cette « défiguration » n’a pas pour fonction de réduire le personnage au grotesque : elle rend visibles les violences qui l’ont façonné. Dès l’ouverture, Elvira est battue et contrainte de ramper ; dans l’appartement, Christof détruit son image en la plaçant devant le miroir ; à l’abattoir, son récit se superpose aux opérations d’équarrissage. La mise en scène rapproche alors corps humain et carcasse animale. Pour Kaiser, cette assimilation possède une portée politique : l’organisation capitaliste transforme le vivant en matière exploitable, tandis que le trafic de viande conduit au trafic des êtres et à la prostitution. Kaiser prolonge cette lecture à travers Anton Saitz. Rescapé de Bergen-Belsen, celui-ci reproduit dans ses entreprises la discipline apprise dans le camp : « la même structure d’ordre, d’obéissance, de devoir et de peur » (scénario de Fassbinder, cité par Claire Kaiser). La victime historique devient donc elle-même l’agent d’un ordre économique totalitaire, sans que le film efface pour autant l’asymétrie des positions. La scène où Anton et ses hommes imitent </t>
     </r>
     <r>
       <rPr>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Carlito"/>
       </rPr>
@@ -3395,7 +3381,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="Carlito"/>
       </rPr>
@@ -3403,17 +3389,46 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Thomas Elsaesser, Rainer Werner Fassbinder : un cinéaste d’Allemagne, Paris, Centre Pompidou, 2005, chap. 8, p. 327-350.
-Claire Kaiser, « Rainer Werner Fassbinder », conférence à la Cinémathèque de Toulouse, 2016 : https://www.youtube.com/watch?v=TMhzoG7NsLsb
-Rainer Werner Fassbinder, scénario de L’Année des treize lunes, cité par Claire Kaiser dans cette conférence.
-</t>
+    <r>
+      <t xml:space="preserve">À Zurich en 1938, Willie, chanteuse allemande, aime Robert Mendelsson, musicien juif suisse engagé dans une organisation qui aide des Juifs à fuir l’Allemagne nazie. Séparés par les événements, Robert poursuit la lutte clandestine tandis que Willie devient une vedette du Reich grâce à la chanson « Lili Marleen », sans renoncer à aider Robert et sa famille.le film s'inspire de la créatrice de la chanson </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Lili Marleen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> : Lale Andersen. Une de ses chansons d'amour connut pendant la seconde guerre mondiale un succès inédit, devant une sorte d'hymne affectif pour les soldats ; une chanson d'amour devenait emblématique de la guerre. </t>
+    </r>
+  </si>
+  <si>
+    <t>This night</t>
+  </si>
+  <si>
+    <t>rwf-1966-this-night</t>
+  </si>
+  <si>
+    <t>rwf-1970-le-cafe</t>
+  </si>
+  <si>
+    <t>Le Café</t>
+  </si>
+  <si>
+    <t>Das Kaffehause</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3453,12 +3468,6 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
@@ -3519,18 +3528,38 @@
       <name val="IBM Plex Mono"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3570,6 +3599,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3614,7 +3649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3638,17 +3673,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3656,11 +3688,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3668,22 +3700,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3692,17 +3724,51 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3722,6 +3788,343 @@
           <bgColor rgb="FFF3F6F8"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4181,230 +4584,6 @@
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4423,57 +4602,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA44" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA46" dataDxfId="5">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="34"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="24"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="23"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="21"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="20"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="19"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="22"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferentielEntourage" displayName="ReferentielEntourage" ref="A1:N27" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferentielEntourage" displayName="ReferentielEntourage" ref="A1:N27" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="pers-harry-baer" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Harry Baer" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Baer" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Harry" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Colonne1" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Noyau théâtral / Factory" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Acteur, assistant, production" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Jeu, soutien de production, présence interne" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Proche compagnon de travail et membre du cercle masculin du collectif" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Pionniers à Ingolstadt; Whity; Le Marchand des quatre saisons; Despair; La Troisième génération; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generatio" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Colonne2" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Témoin de l’intérieur du collectif, relais organisationnel" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Baer.jpg" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="pers-harry-baer" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Harry Baer" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Baer" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Harry" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Colonne1" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Noyau théâtral / Factory" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Acteur, assistant, production" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Jeu, soutien de production, présence interne" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Proche compagnon de travail et membre du cercle masculin du collectif" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Pionniers à Ingolstadt; Whity; Le Marchand des quatre saisons; Despair; La Troisième génération; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generatio" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Colonne2" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Témoin de l’intérieur du collectif, relais organisationnel" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Baer.jpg" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4628,13 +4807,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" style="41" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -4669,7 +4848,7 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -4751,452 +4930,418 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="11" customFormat="1" ht="107" customHeight="1">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:30" s="38" customFormat="1" ht="107" customHeight="1">
+      <c r="A2" s="35" t="s">
+        <v>846</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>845</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>845</v>
+      </c>
+      <c r="D2" s="36">
+        <v>1966</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+    </row>
+    <row r="3" spans="1:30" s="10" customFormat="1" ht="107" customHeight="1">
+      <c r="A3" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B3" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C3" s="28" t="s">
+        <v>582</v>
+      </c>
+      <c r="D3" s="28">
+        <v>1966</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="28">
+        <v>10</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="28" t="s">
         <v>583</v>
       </c>
-      <c r="D2" s="10">
-        <v>1966</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28" t="s">
+        <v>584</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>585</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>587</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28" t="s">
+        <v>588</v>
+      </c>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+    </row>
+    <row r="4" spans="1:30" s="10" customFormat="1" ht="107" customHeight="1">
+      <c r="A4" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>589</v>
+      </c>
+      <c r="D4" s="28">
+        <v>1967</v>
+      </c>
+      <c r="E4" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="10">
-        <v>10</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="F4" s="28">
+        <v>9</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J4" s="28" t="s">
+        <v>590</v>
+      </c>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28" t="s">
         <v>584</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-    </row>
-    <row r="3" spans="1:30" s="11" customFormat="1" ht="107" customHeight="1">
-      <c r="A3" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="D3" s="10">
-        <v>1967</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="10">
-        <v>9</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="O4" s="28" t="s">
+        <v>591</v>
+      </c>
+      <c r="P4" s="28" t="s">
+        <v>592</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+    </row>
+    <row r="5" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A5" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="39">
+        <v>1969</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="30">
+        <v>88</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10" t="s">
+      <c r="J5" s="29"/>
+      <c r="K5" s="29" t="s">
         <v>595</v>
       </c>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-    </row>
-    <row r="4" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="9">
-        <v>1969</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="9">
-        <v>88</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8" t="s">
+      <c r="L5" s="29" t="s">
         <v>596</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M5" s="29" t="s">
         <v>597</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N5" s="29" t="s">
         <v>598</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O5" s="29" t="s">
         <v>599</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P5" s="29" t="s">
         <v>600</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q5" s="29" t="s">
         <v>601</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29" t="s">
         <v>602</v>
       </c>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="AA4" s="8" t="s">
+      <c r="AA5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AB5" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="AC4" s="6" t="str">
-        <f>IF(O4="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O4)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O4)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O4)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O4)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O4)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O4)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O4)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O4)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O4)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O4)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O4)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O4)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O4)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O4)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O4)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O4)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O4)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O4)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O4)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O4)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O4)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O4)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O4)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-ursula-stratz</v>
-      </c>
-      <c r="AD4" s="6" t="str">
-        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H4:N4,P4),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-ulli-lommel; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1969</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="9">
-        <v>88</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>605</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="AC5" s="6" t="str">
         <f>IF(O5="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O5)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O5)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O5)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O5)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O5)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O5)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O5)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O5)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O5)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O5)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O5)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O5)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O5)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O5)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O5)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O5)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O5)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O5)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O5)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O5)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O5)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O5)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O5)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-irm-hermann; pers-hanna-schygulla; pers-lilith-ungerer</v>
+        <v>pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-ursula-stratz</v>
       </c>
       <c r="AD5" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H5:N5,P5),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-peer-raben</v>
+        <v>pers-ulli-lommel; pers-peer-raben</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="D6" s="9">
-        <v>1970</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="A6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="39">
+        <v>1969</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="9">
-        <v>91</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="30">
+        <v>88</v>
+      </c>
+      <c r="G6" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K6" s="8" t="s">
+      <c r="J6" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="AA6" s="8" t="s">
+      <c r="L6" s="29"/>
+      <c r="M6" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="O6" s="29" t="s">
+        <v>604</v>
+      </c>
+      <c r="P6" s="29" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q6" s="29" t="s">
+        <v>606</v>
+      </c>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29" t="s">
+        <v>842</v>
+      </c>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29" t="s">
+        <v>607</v>
+      </c>
+      <c r="AA6" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="AC6" s="6" t="str">
         <f>IF(O6="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O6)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O6)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O6)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O6)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O6)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O6)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O6)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O6)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O6)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O6)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O6)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O6)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O6)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O6)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O6)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O6)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O6)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O6)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O6)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O6)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O6)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O6)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O6)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-gunther-kaufmann; pers-hanna-schygulla; pers-lilith-ungerer</v>
+        <v>pers-irm-hermann; pers-hanna-schygulla; pers-lilith-ungerer</v>
       </c>
       <c r="AD6" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H6:N6,P6),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-fengler; pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-peer-raben</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="A7" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>608</v>
+      </c>
+      <c r="D7" s="39">
         <v>1970</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="9">
-        <v>88</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="30">
+        <v>91</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="O7" s="29" t="s">
         <v>610</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8" t="s">
+      <c r="P7" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>612</v>
+      </c>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA7" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB7" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="AA7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="AC7" s="6" t="str">
         <f>IF(O7="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O7)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O7)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O7)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O7)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O7)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O7)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O7)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O7)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O7)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O7)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O7)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O7)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O7)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O7)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O7)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O7)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O7)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O7)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O7)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O7)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O7)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O7)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O7)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-lilith-ungerer</v>
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-gunther-kaufmann; pers-hanna-schygulla; pers-lilith-ungerer</v>
       </c>
       <c r="AD7" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H7:N7,P7),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
@@ -5204,707 +5349,675 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="D8" s="9">
+      <c r="A8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>614</v>
+      </c>
+      <c r="D8" s="39">
         <v>1970</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="9">
-        <v>80</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="30">
+        <v>88</v>
+      </c>
+      <c r="G8" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>622</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="AA8" s="8" t="s">
+      <c r="H8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>615</v>
+      </c>
+      <c r="O8" s="29" t="s">
+        <v>616</v>
+      </c>
+      <c r="P8" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="Q8" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="AA8" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AC8" s="6" t="str">
         <f>IF(O8="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O8)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O8)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O8)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O8)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O8)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O8)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O8)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O8)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O8)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O8)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O8)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O8)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O8)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O8)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O8)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O8)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O8)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O8)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O8)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O8)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O8)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O8)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O8)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab</v>
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla; pers-lilith-ungerer</v>
       </c>
       <c r="AD8" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H8:N8,P8),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-michael-fengler; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="A9" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>620</v>
+      </c>
+      <c r="D9" s="39">
         <v>1970</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="9">
-        <v>90</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="E9" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="30">
+        <v>80</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="AA9" s="8" t="s">
+      <c r="I9" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>621</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>598</v>
+      </c>
+      <c r="O9" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="P9" s="29" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q9" s="29" t="s">
+        <v>624</v>
+      </c>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29" t="s">
+        <v>625</v>
+      </c>
+      <c r="AA9" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="AC9" s="6" t="str">
         <f>IF(O9="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O9)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O9)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O9)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O9)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O9)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O9)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O9)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O9)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O9)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O9)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O9)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O9)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O9)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O9)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O9)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O9)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O9)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O9)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O9)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O9)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O9)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O9)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O9)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ingrid-caven; pers-michael-fengler; pers-gunther-kaufmann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla</v>
+        <v>pers-hark-bohm; pers-ingrid-caven; pers-irm-hermann; pers-ulli-lommel; pers-kurt-raab</v>
       </c>
       <c r="AD9" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H9:N9,P9),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
+        <v>pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>626</v>
+      </c>
+      <c r="D10" s="39">
+        <v>1970</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="30">
+        <v>90</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>627</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>628</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>629</v>
+      </c>
+      <c r="P10" s="29" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29" t="s">
+        <v>631</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC10" s="6" t="str">
+        <f>IF(O10="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O10)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O10)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O10)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O10)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O10)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O10)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O10)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O10)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O10)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O10)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O10)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O10)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O10)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O10)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O10)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O10)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O10)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O10)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O10)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O10)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O10)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O10)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O10)),'Référentiel entourage'!$A$24,"")))</f>
+        <v>pers-margit-carstensen; pers-ingrid-caven; pers-michael-fengler; pers-gunther-kaufmann; pers-kurt-raab; pers-peer-raben; pers-hanna-schygulla</v>
+      </c>
+      <c r="AD10" s="6" t="str">
+        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H10:N10,P10),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-fengler; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>847</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>848</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>849</v>
+      </c>
+      <c r="D11" s="39">
+        <v>1970</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+    </row>
+    <row r="12" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A12" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C12" s="29"/>
+      <c r="D12" s="39">
+        <v>1970</v>
+      </c>
+      <c r="E12" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9">
+      <c r="F12" s="30">
+        <v>84</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>627</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M12" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N12" s="29" t="s">
+        <v>632</v>
+      </c>
+      <c r="O12" s="29" t="s">
+        <v>633</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="Q12" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="29">
         <v>1970</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="Y12" s="29"/>
+      <c r="Z12" s="29" t="s">
+        <v>636</v>
+      </c>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="9">
-        <v>84</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+    </row>
+    <row r="13" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="39">
+        <v>1971</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="30">
+        <v>95</v>
+      </c>
+      <c r="G13" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H13" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I13" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8">
-        <v>1970</v>
-      </c>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8" t="s">
+      <c r="J13" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>627</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N13" s="29" t="s">
         <v>637</v>
       </c>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-    </row>
-    <row r="11" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="O13" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="P13" s="29" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q13" s="29" t="s">
+        <v>640</v>
+      </c>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9">
-        <v>1971</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="9">
-        <v>95</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29" t="s">
         <v>641</v>
       </c>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8" t="s">
+      <c r="AA13" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB13" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="AA11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC11" s="6" t="str">
-        <f>IF(O11="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O11)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O11)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O11)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O11)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O11)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O11)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O11)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O11)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O11)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O11)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O11)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O11)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O11)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O11)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O11)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O11)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O11)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O11)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O11)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O11)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O11)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O11)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O11)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-gunther-kaufmann; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD11" s="6" t="str">
-        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H11:N11,P11),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-ulli-lommel; pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="D12" s="9">
-        <v>1971</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="9">
-        <v>103</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="AA12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC12" s="6" t="str">
-        <f>IF(O12="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O12)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O12)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O12)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O12)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O12)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O12)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O12)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O12)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O12)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O12)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O12)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O12)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O12)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O12)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O12)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O12)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O12)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O12)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O12)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O12)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O12)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O12)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O12)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
-      </c>
-      <c r="AD12" s="6" t="str">
-        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H12:N12,P12),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="D13" s="9">
-        <v>1971</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="9">
-        <v>84</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="AA13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="AC13" s="6" t="str">
         <f>IF(O13="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O13)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O13)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O13)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O13)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O13)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O13)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O13)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O13)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O13)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O13)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O13)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O13)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O13)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O13)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O13)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O13)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O13)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O13)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O13)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O13)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O13)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O13)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O13)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-irm-hermann; pers-gunther-kaufmann; pers-hanna-schygulla</v>
+        <v>pers-gunther-kaufmann; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
       <c r="AD13" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H13:N13,P13),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab; pers-peer-raben</v>
+        <v>pers-michael-ballhaus; pers-ulli-lommel; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="9">
-        <v>1972</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="A14" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>642</v>
+      </c>
+      <c r="D14" s="39">
+        <v>1971</v>
+      </c>
+      <c r="E14" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="9">
-        <v>88</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="30">
+        <v>103</v>
+      </c>
+      <c r="G14" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="AA14" s="8" t="s">
+      <c r="J14" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>643</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>644</v>
+      </c>
+      <c r="O14" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>646</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>647</v>
+      </c>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29" t="s">
+        <v>648</v>
+      </c>
+      <c r="AA14" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC14" s="6" t="str">
         <f>IF(O14="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O14)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O14)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O14)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O14)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O14)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O14)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O14)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O14)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O14)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O14)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O14)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O14)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O14)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O14)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O14)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O14)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O14)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O14)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O14)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O14)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O14)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O14)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O14)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-michael-fengler; pers-irm-hermann; pers-kurt-raab; pers-daniel-schmid; pers-hanna-schygulla</v>
+        <v>pers-ingrid-caven; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
       <c r="AD14" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H14:N14,P14),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab</v>
+        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1972</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="9">
-        <v>124</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="A15" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>649</v>
+      </c>
+      <c r="D15" s="39">
+        <v>1971</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="30">
+        <v>84</v>
+      </c>
+      <c r="G15" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="AA15" s="8" t="s">
+      <c r="I15" s="29" t="s">
+        <v>650</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L15" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="O15" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>654</v>
+      </c>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29" t="s">
+        <v>655</v>
+      </c>
+      <c r="AA15" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AC15" s="6" t="str">
         <f>IF(O15="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O15)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O15)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O15)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O15)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O15)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O15)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O15)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O15)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O15)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O15)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O15)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O15)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O15)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O15)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O15)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O15)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O15)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O15)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O15)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O15)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O15)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O15)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O15)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-irm-hermann; pers-hanna-schygulla</v>
+        <v>pers-irm-hermann; pers-gunther-kaufmann; pers-hanna-schygulla</v>
       </c>
       <c r="AD15" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H15:N15,P15),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab</v>
+        <v>pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A16" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="A16" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="39">
         <v>1972</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="E16" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="30">
+        <v>88</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L16" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29" t="s">
+        <v>656</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="P16" s="29" t="s">
+        <v>658</v>
+      </c>
+      <c r="Q16" s="29" t="s">
+        <v>659</v>
+      </c>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>668</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8" t="s">
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29" t="s">
+        <v>660</v>
+      </c>
+      <c r="AA16" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB16" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="AA16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="AC16" s="6" t="str">
         <f>IF(O16="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O16)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O16)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O16)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O16)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O16)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O16)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O16)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O16)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O16)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O16)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O16)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O16)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O16)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O16)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O16)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O16)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O16)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O16)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O16)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O16)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O16)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O16)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O16)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-lilo-pempeit; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
+        <v>pers-hark-bohm; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-michael-fengler; pers-irm-hermann; pers-kurt-raab; pers-daniel-schmid; pers-hanna-schygulla</v>
       </c>
       <c r="AD16" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H16:N16,P16),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
@@ -5912,2243 +6025,2402 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="A17" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="39">
         <v>1972</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="9">
-        <v>467</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="E17" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="30">
+        <v>124</v>
+      </c>
+      <c r="G17" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K17" s="8" t="s">
+      <c r="I17" s="29" t="s">
+        <v>661</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L17" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA17" s="8" t="s">
-        <v>113</v>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="O17" s="29" t="s">
+        <v>662</v>
+      </c>
+      <c r="P17" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q17" s="29" t="s">
+        <v>664</v>
+      </c>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29" t="s">
+        <v>665</v>
+      </c>
+      <c r="AA17" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="AC17" s="6" t="str">
         <f>IF(O17="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O17)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O17)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O17)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O17)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O17)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O17)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O17)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O17)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O17)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O17)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O17)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O17)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O17)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O17)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O17)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O17)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O17)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O17)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O17)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O17)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O17)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O17)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O17)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-gottfried-john; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
+        <v>pers-margit-carstensen; pers-irm-hermann; pers-hanna-schygulla</v>
       </c>
       <c r="AD17" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H17:N17,P17),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab</v>
+        <v>pers-michael-ballhaus; pers-kurt-raab</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="D18" s="9">
-        <v>1973</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="9">
-        <v>102</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="A18" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>666</v>
+      </c>
+      <c r="D18" s="39">
+        <v>1972</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="30">
+        <v>87</v>
+      </c>
+      <c r="G18" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>678</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>679</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>681</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8" t="s">
-        <v>683</v>
-      </c>
-      <c r="AA18" s="8" t="s">
+      <c r="I18" s="29" t="s">
+        <v>667</v>
+      </c>
+      <c r="J18" s="29" t="s">
+        <v>668</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>669</v>
+      </c>
+      <c r="L18" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29" t="s">
+        <v>670</v>
+      </c>
+      <c r="O18" s="29" t="s">
+        <v>671</v>
+      </c>
+      <c r="P18" s="29" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q18" s="29" t="s">
+        <v>673</v>
+      </c>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29" t="s">
+        <v>674</v>
+      </c>
+      <c r="AA18" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="AC18" s="6" t="str">
         <f>IF(O18="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O18)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O18)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O18)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O18)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O18)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O18)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O18)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O18)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O18)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O18)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O18)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O18)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O18)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O18)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O18)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O18)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O18)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O18)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O18)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O18)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O18)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O18)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O18)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
+        <v>pers-margit-carstensen; pers-lilo-pempeit; pers-ulli-lommel; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
       <c r="AD18" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H18:N18,P18),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-irm-hermann; pers-kurt-raab</v>
+        <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="9">
-        <v>1973</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="9">
-        <v>212</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="A19" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="39">
+        <v>1972</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="30">
+        <v>467</v>
+      </c>
+      <c r="G19" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8" t="s">
+      <c r="I19" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="L19" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="O19" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="U19" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y19" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z19" s="8" t="s">
+      <c r="P19" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q19" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y19" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z19" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA19" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA19" s="8" t="s">
-        <v>129</v>
-      </c>
       <c r="AB19" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AC19" s="6" t="str">
         <f>IF(O19="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O19)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O19)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O19)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O19)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O19)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O19)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O19)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O19)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O19)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O19)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O19)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O19)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O19)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O19)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O19)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O19)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O19)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O19)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O19)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O19)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O19)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O19)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O19)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-gottfried-john; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
       <c r="AD19" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H19:N19,P19),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
+        <v>pers-kurt-raab</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A20" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="9">
-        <v>1974</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="9">
-        <v>93</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="A20" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>675</v>
+      </c>
+      <c r="D20" s="39">
+        <v>1973</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="30">
+        <v>102</v>
+      </c>
+      <c r="G20" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y20" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z20" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA20" s="8" t="s">
-        <v>113</v>
+      <c r="I20" s="29" t="s">
+        <v>676</v>
+      </c>
+      <c r="J20" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L20" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="29" t="s">
+        <v>677</v>
+      </c>
+      <c r="N20" s="29" t="s">
+        <v>678</v>
+      </c>
+      <c r="O20" s="29" t="s">
+        <v>679</v>
+      </c>
+      <c r="P20" s="29" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q20" s="29" t="s">
+        <v>681</v>
+      </c>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29" t="s">
+        <v>682</v>
+      </c>
+      <c r="AA20" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="AC20" s="6" t="str">
         <f>IF(O20="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O20)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O20)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O20)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O20)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O20)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O20)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O20)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O20)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O20)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O20)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O20)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O20)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O20)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O20)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O20)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O20)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O20)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O20)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O20)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O20)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O20)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O20)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O20)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira</v>
+        <v>pers-el-hedi-ben-salem; pers-irm-hermann; pers-kurt-raab; pers-hanna-schygulla</v>
       </c>
       <c r="AD20" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H20:N20,P20),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
+        <v>pers-irm-hermann; pers-kurt-raab</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A21" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D21" s="9">
-        <v>1974</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="9">
-        <v>140</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="A21" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="39">
+        <v>1973</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="30">
+        <v>212</v>
+      </c>
+      <c r="G21" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L21" s="8" t="s">
+      <c r="I21" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="U21" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y21" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z21" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA21" s="8" t="s">
-        <v>113</v>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q21" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="U21" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y21" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z21" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA21" s="29" t="s">
+        <v>128</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="AC21" s="6" t="str">
         <f>IF(O21="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O21)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O21)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O21)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O21)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O21)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O21)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O21)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O21)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O21)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O21)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O21)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O21)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O21)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O21)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O21)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O21)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O21)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O21)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O21)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O21)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O21)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O21)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O21)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-karlheinz-bohm; pers-hark-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz</v>
+        <v/>
       </c>
       <c r="AD21" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H21:N21,P21),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" ht="105">
-      <c r="A22" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9">
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A22" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="39">
         <v>1974</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="9">
-        <v>101</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="E22" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="30">
+        <v>93</v>
+      </c>
+      <c r="G22" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>687</v>
-      </c>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>690</v>
-      </c>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8" t="s">
+      <c r="I22" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="P22" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q22" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y22" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="8" t="s">
-        <v>691</v>
-      </c>
-      <c r="AA22" s="8" t="s">
-        <v>45</v>
+      <c r="Z22" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA22" s="29" t="s">
+        <v>112</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="AC22" s="6" t="str">
         <f>IF(O22="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O22)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O22)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O22)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O22)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O22)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O22)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O22)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O22)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O22)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O22)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O22)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O22)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O22)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O22)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O22)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O22)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O22)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O22)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O22)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O22)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O22)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O22)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O22)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel</v>
+        <v>pers-el-hedi-ben-salem; pers-peter-chatel; pers-lilo-pempeit; pers-irm-hermann; pers-brigitte-mira</v>
       </c>
       <c r="AD22" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H22:N22,P22),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="150">
-      <c r="A23" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="9">
+    <row r="23" spans="1:30" ht="227.75" customHeight="1">
+      <c r="A23" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="39">
         <v>1974</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="9">
-        <v>116</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="E23" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="30">
+        <v>140</v>
+      </c>
+      <c r="G23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="T23" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y23" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z23" s="8" t="s">
+      <c r="I23" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L23" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="O23" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q23" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="U23" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y23" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z23" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA23" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA23" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="AB23" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="AC23" s="6" t="str">
         <f>IF(O23="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O23)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O23)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O23)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O23)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O23)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O23)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O23)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O23)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O23)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O23)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O23)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O23)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O23)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O23)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O23)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O23)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O23)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O23)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O23)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O23)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O23)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O23)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O23)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab</v>
+        <v>pers-karlheinz-bohm; pers-hark-bohm; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel; pers-hanna-schygulla; pers-ursula-stratz</v>
       </c>
       <c r="AD23" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H23:N23,P23),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="255">
-      <c r="A24" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24" s="9">
-        <v>1975</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="9">
-        <v>123</v>
-      </c>
-      <c r="G24" s="8" t="s">
+        <v>pers-kurt-raab</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="133">
+      <c r="A24" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="39">
+        <v>1974</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="30">
+        <v>101</v>
+      </c>
+      <c r="G24" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y24" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA24" s="8" t="s">
-        <v>113</v>
+      <c r="I24" s="29" t="s">
+        <v>683</v>
+      </c>
+      <c r="J24" s="29" t="s">
+        <v>684</v>
+      </c>
+      <c r="K24" s="29" t="s">
+        <v>685</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>686</v>
+      </c>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29" t="s">
+        <v>670</v>
+      </c>
+      <c r="O24" s="29" t="s">
+        <v>687</v>
+      </c>
+      <c r="P24" s="29" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q24" s="29" t="s">
+        <v>689</v>
+      </c>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29" t="s">
+        <v>690</v>
+      </c>
+      <c r="AA24" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="AC24" s="6" t="str">
         <f>IF(O24="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O24)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O24)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O24)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O24)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O24)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O24)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O24)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O24)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O24)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O24)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O24)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O24)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O24)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O24)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O24)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O24)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O24)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O24)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O24)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O24)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O24)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O24)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O24)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab</v>
+        <v>pers-margit-carstensen; pers-lilo-pempeit; pers-irm-hermann; pers-ulli-lommel</v>
       </c>
       <c r="AD24" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H24:N24,P24),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" ht="240">
-      <c r="A25" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="9">
-        <v>1975</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="9">
-        <v>120</v>
-      </c>
-      <c r="G25" s="8" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="228">
+      <c r="A25" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="39">
+        <v>1974</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="30">
+        <v>116</v>
+      </c>
+      <c r="G25" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J25" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="T25" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="U25" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y25" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z25" s="8" t="s">
+      <c r="L25" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="O25" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="P25" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q25" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T25" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y25" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z25" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA25" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA25" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="AB25" s="1" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="AC25" s="6" t="str">
         <f>IF(O25="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O25)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O25)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O25)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O25)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O25)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O25)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O25)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O25)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O25)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O25)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O25)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O25)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O25)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O25)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O25)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O25)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O25)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O25)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O25)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O25)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O25)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O25)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O25)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
+        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-kurt-raab</v>
       </c>
       <c r="AD25" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H25:N25,P25),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" ht="60">
-      <c r="A26" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>692</v>
-      </c>
-      <c r="D26" s="9">
+        <v>pers-michael-ballhaus; pers-kurt-raab</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="342">
+      <c r="A26" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="39">
         <v>1975</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="9">
-        <v>44</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="E26" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="30">
+        <v>123</v>
+      </c>
+      <c r="G26" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8" t="s">
+      <c r="I26" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N26" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="O26" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="P26" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q26" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y26" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="AA26" s="8" t="s">
-        <v>45</v>
+      <c r="Z26" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA26" s="29" t="s">
+        <v>112</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="AC26" s="6" t="str">
         <f>IF(O26="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O26)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O26)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O26)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O26)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O26)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O26)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O26)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O26)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O26)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O26)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O26)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O26)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O26)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O26)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O26)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O26)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O26)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O26)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O26)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O26)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O26)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O26)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O26)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-el-hedi-ben-salem; pers-brigitte-mira</v>
+        <v>pers-el-hedi-ben-salem; pers-karlheinz-bohm; pers-ingrid-caven; pers-peter-chatel; pers-irm-hermann; pers-brigitte-mira; pers-kurt-raab</v>
       </c>
       <c r="AD26" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H26:N26,P26),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" ht="195">
-      <c r="A27" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>700</v>
-      </c>
-      <c r="D27" s="9">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="304">
+      <c r="A27" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="39">
         <v>1975</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="9">
-        <v>88</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="E27" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="30">
+        <v>120</v>
+      </c>
+      <c r="G27" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="Q27" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="AA27" s="8" t="s">
-        <v>45</v>
+      <c r="I27" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="J27" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K27" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L27" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N27" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="O27" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="P27" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q27" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="T27" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="U27" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y27" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z27" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA27" s="29" t="s">
+        <v>112</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AC27" s="6" t="str">
         <f>IF(O27="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O27)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O27)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O27)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O27)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O27)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O27)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O27)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O27)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O27)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O27)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O27)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O27)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O27)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O27)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O27)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O27)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O27)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O27)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O27)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O27)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O27)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O27)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O27)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
+        <v>pers-karlheinz-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
       </c>
       <c r="AD27" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H27:N27,P27),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" ht="135">
-      <c r="A28" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="D28" s="9">
-        <v>1976</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="9">
-        <v>101</v>
-      </c>
-      <c r="G28" s="8" t="s">
+        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="95">
+      <c r="A28" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>691</v>
+      </c>
+      <c r="D28" s="39">
+        <v>1975</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="30">
+        <v>44</v>
+      </c>
+      <c r="G28" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>715</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y28" s="8"/>
-      <c r="Z28" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="AA28" s="8" t="s">
+      <c r="H28" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>692</v>
+      </c>
+      <c r="J28" s="29" t="s">
+        <v>693</v>
+      </c>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M28" s="29" t="s">
+        <v>694</v>
+      </c>
+      <c r="N28" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="O28" s="29" t="s">
+        <v>695</v>
+      </c>
+      <c r="P28" s="29" t="s">
+        <v>696</v>
+      </c>
+      <c r="Q28" s="29" t="s">
+        <v>697</v>
+      </c>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29" t="s">
+        <v>698</v>
+      </c>
+      <c r="AA28" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AC28" s="6" t="str">
         <f>IF(O28="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O28)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O28)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O28)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O28)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O28)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O28)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O28)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O28)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O28)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O28)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O28)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O28)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O28)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O28)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O28)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O28)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O28)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O28)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O28)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O28)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O28)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O28)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O28)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-ulli-lommel</v>
+        <v>pers-el-hedi-ben-salem; pers-brigitte-mira</v>
       </c>
       <c r="AD28" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H28:N28,P28),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-fengler; pers-peer-raben; pers-daniel-schmid</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="210">
-      <c r="A29" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D29" s="9">
-        <v>1976</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="9">
-        <v>112</v>
-      </c>
-      <c r="G29" s="8" t="s">
+        <v>pers-kurt-raab</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="266">
+      <c r="A29" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>699</v>
+      </c>
+      <c r="D29" s="39">
+        <v>1975</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="30">
+        <v>88</v>
+      </c>
+      <c r="G29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="T29" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="U29" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y29" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z29" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA29" s="8" t="s">
-        <v>113</v>
+      <c r="I29" s="29" t="s">
+        <v>700</v>
+      </c>
+      <c r="J29" s="29" t="s">
+        <v>701</v>
+      </c>
+      <c r="K29" s="29" t="s">
+        <v>702</v>
+      </c>
+      <c r="L29" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N29" s="29" t="s">
+        <v>703</v>
+      </c>
+      <c r="O29" s="29" t="s">
+        <v>704</v>
+      </c>
+      <c r="P29" s="29" t="s">
+        <v>705</v>
+      </c>
+      <c r="Q29" s="29" t="s">
+        <v>706</v>
+      </c>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29" t="s">
+        <v>707</v>
+      </c>
+      <c r="AA29" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="AC29" s="6" t="str">
         <f>IF(O29="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O29)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O29)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O29)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O29)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O29)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O29)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O29)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O29)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O29)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O29)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O29)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O29)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O29)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O29)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O29)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O29)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O29)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O29)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O29)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O29)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O29)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O29)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O29)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
+        <v>pers-hark-bohm; pers-margit-carstensen; pers-ingrid-caven; pers-lilo-pempeit; pers-irm-hermann; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
       </c>
       <c r="AD29" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H29:N29,P29),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" ht="150">
-      <c r="A30" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="9">
+        <v>pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="190">
+      <c r="A30" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>708</v>
+      </c>
+      <c r="D30" s="39">
         <v>1976</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="9">
-        <v>96</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="F30" s="30">
+        <v>101</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>709</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>710</v>
+      </c>
+      <c r="K30" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q30" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="V30" s="8"/>
-      <c r="W30" s="8"/>
-      <c r="X30" s="8" t="s">
+      <c r="L30" s="29"/>
+      <c r="M30" s="29" t="s">
+        <v>711</v>
+      </c>
+      <c r="N30" s="29" t="s">
+        <v>712</v>
+      </c>
+      <c r="O30" s="29" t="s">
+        <v>713</v>
+      </c>
+      <c r="P30" s="29" t="s">
+        <v>714</v>
+      </c>
+      <c r="Q30" s="29" t="s">
+        <v>715</v>
+      </c>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29" t="s">
+        <v>716</v>
+      </c>
+      <c r="AA30" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB30" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="Y30" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z30" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA30" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="AB30" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="AC30" s="6" t="str">
         <f>IF(O30="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O30)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O30)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O30)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O30)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O30)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O30)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O30)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O30)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O30)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O30)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O30)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O30)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O30)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O30)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O30)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O30)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O30)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O30)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O30)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O30)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O30)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O30)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O30)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira</v>
+        <v>pers-ingrid-caven; pers-ulli-lommel</v>
       </c>
       <c r="AD30" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H30:N30,P30),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" ht="342">
-      <c r="A31" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="D31" s="9">
+        <v>pers-michael-fengler; pers-peer-raben; pers-daniel-schmid</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" ht="266">
+      <c r="A31" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="39">
         <v>1976</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="9">
-        <v>104</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="E31" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="30">
+        <v>112</v>
+      </c>
+      <c r="G31" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="V31" s="8"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y31" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z31" s="8" t="s">
+      <c r="I31" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N31" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="O31" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="P31" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q31" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="T31" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="U31" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y31" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z31" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA31" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA31" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="AB31" s="1" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="AC31" s="6" t="str">
         <f>IF(O31="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O31)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O31)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O31)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O31)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O31)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O31)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O31)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O31)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O31)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O31)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O31)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O31)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O31)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O31)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O31)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O31)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O31)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O31)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O31)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O31)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O31)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O31)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O31)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-armin-meier</v>
+        <v>pers-margit-carstensen; pers-ingrid-caven; pers-peter-chatel; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira; pers-kurt-raab</v>
       </c>
       <c r="AD31" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H31:N31,P31),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" ht="398">
-      <c r="A32" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="D32" s="9">
-        <v>1977</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="9">
+        <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="209">
+      <c r="A32" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="D32" s="39">
+        <v>1976</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="30">
+        <v>96</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N32" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="O32" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="P32" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q32" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y32" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z32" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>721</v>
-      </c>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="R32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="8"/>
-      <c r="W32" s="8"/>
-      <c r="X32" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y32" s="8"/>
-      <c r="Z32" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="AA32" s="8" t="s">
-        <v>45</v>
+      <c r="AA32" s="29" t="s">
+        <v>112</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="AC32" s="6" t="str">
         <f>IF(O32="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O32)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O32)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O32)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O32)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O32)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O32)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O32)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O32)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O32)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O32)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O32)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O32)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O32)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O32)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O32)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O32)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O32)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O32)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O32)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O32)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O32)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O32)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O32)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-irm-hermann</v>
+        <v>pers-margit-carstensen; pers-ulli-lommel; pers-armin-meier; pers-brigitte-mira</v>
       </c>
       <c r="AD32" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H32:N32,P32),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" ht="135">
-      <c r="A33" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>726</v>
-      </c>
-      <c r="D33" s="9">
-        <v>1977</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="9">
-        <v>201</v>
-      </c>
-      <c r="G33" s="8" t="s">
+        <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" ht="409.6">
+      <c r="A33" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="D33" s="39">
+        <v>1976</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="30">
+        <v>104</v>
+      </c>
+      <c r="G33" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="I33" s="29"/>
+      <c r="J33" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K33" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="8"/>
-      <c r="W33" s="8"/>
-      <c r="X33" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y33" s="8"/>
-      <c r="Z33" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="AA33" s="8" t="s">
-        <v>45</v>
+      <c r="L33" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N33" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="O33" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="P33" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q33" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="T33" s="29"/>
+      <c r="U33" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="V33" s="29"/>
+      <c r="W33" s="29"/>
+      <c r="X33" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y33" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z33" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA33" s="29" t="s">
+        <v>112</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AC33" s="6" t="str">
         <f>IF(O33="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O33)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O33)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O33)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O33)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O33)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O33)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O33)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O33)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O33)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O33)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O33)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O33)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O33)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O33)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O33)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O33)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O33)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O33)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O33)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O33)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O33)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O33)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O33)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-armin-meier; pers-kurt-raab; pers-elisabeth-trissenaar</v>
+        <v>pers-ingrid-caven; pers-lilo-pempeit; pers-armin-meier</v>
       </c>
       <c r="AD33" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H33:N33,P33),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" ht="150">
-      <c r="A34" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9">
-        <v>1978</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F34" s="9">
-        <v>119</v>
-      </c>
-      <c r="G34" s="8" t="s">
+        <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" ht="409.6">
+      <c r="A34" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="C34" s="29" t="s">
+        <v>717</v>
+      </c>
+      <c r="D34" s="39">
+        <v>1977</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="30">
+        <v>111</v>
+      </c>
+      <c r="G34" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="V34" s="8"/>
-      <c r="W34" s="8"/>
-      <c r="X34" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y34" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="Z34" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA34" s="8" t="s">
-        <v>113</v>
+      <c r="I34" s="29" t="s">
+        <v>718</v>
+      </c>
+      <c r="J34" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>719</v>
+      </c>
+      <c r="L34" s="29" t="s">
+        <v>720</v>
+      </c>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29" t="s">
+        <v>721</v>
+      </c>
+      <c r="P34" s="29" t="s">
+        <v>722</v>
+      </c>
+      <c r="Q34" s="29" t="s">
+        <v>723</v>
+      </c>
+      <c r="R34" s="29"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="29"/>
+      <c r="X34" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y34" s="29"/>
+      <c r="Z34" s="29" t="s">
+        <v>724</v>
+      </c>
+      <c r="AA34" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="AC34" s="6" t="str">
         <f>IF(O34="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O34)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O34)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O34)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O34)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O34)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O34)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O34)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O34)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O34)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O34)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O34)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O34)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O34)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O34)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O34)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O34)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O34)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O34)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O34)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O34)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O34)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O34)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O34)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-margit-carstensen; pers-irm-hermann</v>
       </c>
       <c r="AD34" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H34:N34,P34),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:30" ht="225">
-      <c r="A35" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="D35" s="9">
-        <v>1978</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="9">
-        <v>119</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="H35" s="8" t="s">
+        <v>pers-michael-ballhaus</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" ht="190">
+      <c r="A35" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>725</v>
+      </c>
+      <c r="D35" s="39">
+        <v>1977</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" s="30">
+        <v>201</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="P35" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="R35" s="8"/>
-      <c r="S35" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="V35" s="8"/>
-      <c r="W35" s="8"/>
-      <c r="X35" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z35" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA35" s="8" t="s">
-        <v>113</v>
+      <c r="I35" s="29" t="s">
+        <v>726</v>
+      </c>
+      <c r="J35" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N35" s="29" t="s">
+        <v>727</v>
+      </c>
+      <c r="O35" s="29" t="s">
+        <v>728</v>
+      </c>
+      <c r="P35" s="29" t="s">
+        <v>729</v>
+      </c>
+      <c r="Q35" s="29" t="s">
+        <v>730</v>
+      </c>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+      <c r="W35" s="29"/>
+      <c r="X35" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y35" s="29"/>
+      <c r="Z35" s="29" t="s">
+        <v>731</v>
+      </c>
+      <c r="AA35" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="AC35" s="6" t="str">
         <f>IF(O35="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O35)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O35)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O35)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O35)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O35)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O35)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O35)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O35)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O35)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O35)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O35)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O35)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O35)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O35)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O35)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O35)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O35)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O35)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O35)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O35)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O35)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O35)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O35)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-ingrid-caven; pers-gottfried-john</v>
+        <v>pers-armin-meier; pers-kurt-raab; pers-elisabeth-trissenaar</v>
       </c>
       <c r="AD35" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H35:N35,P35),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:30" ht="409.6">
-      <c r="A36" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="D36" s="9">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" ht="228">
+      <c r="A36" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="C36" s="29"/>
+      <c r="D36" s="39">
         <v>1978</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="9">
-        <v>124</v>
-      </c>
-      <c r="G36" s="8" t="s">
+      <c r="E36" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="F36" s="30">
+        <v>119</v>
+      </c>
+      <c r="G36" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>734</v>
-      </c>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="O36" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="R36" s="8"/>
-      <c r="S36" s="30" t="s">
-        <v>843</v>
-      </c>
-      <c r="T36" s="8" t="s">
-        <v>844</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="V36" s="8"/>
-      <c r="W36" s="8"/>
-      <c r="X36" s="8" t="s">
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q36" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="V36" s="29"/>
+      <c r="W36" s="29"/>
+      <c r="X36" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y36" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="Y36" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="Z36" s="8" t="s">
+      <c r="Z36" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA36" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA36" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="AB36" s="1" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="AC36" s="6" t="str">
         <f>IF(O36="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O36)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O36)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O36)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O36)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O36)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O36)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O36)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O36)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O36)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O36)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O36)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O36)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O36)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O36)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O36)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O36)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O36)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O36)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O36)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O36)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O36)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O36)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O36)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-ingrid-caven; pers-gottfried-john; pers-elisabeth-trissenaar</v>
+        <v/>
       </c>
       <c r="AD36" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H36:N36,P36),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-juliane-lorenz; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" ht="314">
-      <c r="A37" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="D37" s="9">
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:30" ht="285">
+      <c r="A37" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="D37" s="39">
         <v>1978</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="9">
-        <v>120</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" s="8" t="s">
+      <c r="F37" s="30">
+        <v>119</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="H37" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="O37" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="P37" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>744</v>
-      </c>
-      <c r="R37" s="8"/>
-      <c r="S37" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="T37" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="V37" s="8"/>
-      <c r="W37" s="8"/>
-      <c r="X37" s="12">
-        <v>1978</v>
-      </c>
-      <c r="Y37" s="8" t="s">
-        <v>747</v>
-      </c>
-      <c r="Z37" s="8" t="s">
+      <c r="I37" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="P37" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q37" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y37" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z37" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA37" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA37" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="AB37" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="AC37" s="6" t="str">
         <f>IF(O37="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O37)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O37)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O37)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O37)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O37)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O37)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O37)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O37)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O37)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O37)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O37)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O37)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O37)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O37)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O37)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O37)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O37)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O37)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O37)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O37)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O37)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O37)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O37)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-lilo-pempeit; pers-gottfried-john; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
+        <v>pers-hark-bohm; pers-ingrid-caven; pers-gottfried-john</v>
       </c>
       <c r="AD37" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H37:N37,P37),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" ht="180">
-      <c r="A38" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="D38" s="9">
-        <v>1979</v>
-      </c>
-      <c r="E38" s="8" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:30" ht="409.6">
+      <c r="A38" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>732</v>
+      </c>
+      <c r="D38" s="39">
+        <v>1978</v>
+      </c>
+      <c r="E38" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="9">
-        <v>105</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="F38" s="30">
+        <v>124</v>
+      </c>
+      <c r="G38" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="K38" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>749</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>752</v>
-      </c>
-      <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="V38" s="8"/>
-      <c r="W38" s="8"/>
-      <c r="X38" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="Y38" s="8"/>
-      <c r="Z38" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="AA38" s="8" t="s">
-        <v>45</v>
+      <c r="K38" s="29" t="s">
+        <v>733</v>
+      </c>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N38" s="29" t="s">
+        <v>734</v>
+      </c>
+      <c r="O38" s="29" t="s">
+        <v>735</v>
+      </c>
+      <c r="P38" s="29" t="s">
+        <v>736</v>
+      </c>
+      <c r="Q38" s="29" t="s">
+        <v>737</v>
+      </c>
+      <c r="R38" s="29"/>
+      <c r="S38" s="32" t="s">
+        <v>843</v>
+      </c>
+      <c r="T38" s="29" t="s">
+        <v>841</v>
+      </c>
+      <c r="U38" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="V38" s="29"/>
+      <c r="W38" s="29"/>
+      <c r="X38" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y38" s="29" t="s">
+        <v>738</v>
+      </c>
+      <c r="Z38" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA38" s="29" t="s">
+        <v>112</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AC38" s="6" t="str">
         <f>IF(O38="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O38)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O38)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O38)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O38)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O38)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O38)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O38)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O38)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O38)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O38)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O38)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O38)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O38)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O38)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O38)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O38)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O38)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O38)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O38)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O38)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O38)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O38)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O38)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-margit-carstensen; pers-peer-raben; pers-hanna-schygulla</v>
+        <v>pers-ingrid-caven; pers-gottfried-john; pers-elisabeth-trissenaar</v>
       </c>
       <c r="AD38" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H38:N38,P38),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="270">
-      <c r="A39" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D39" s="9">
-        <v>1980</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F39" s="9">
-        <v>894</v>
-      </c>
-      <c r="G39" s="8" t="s">
+    <row r="39" spans="1:30" ht="409.6">
+      <c r="A39" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" s="39">
+        <v>1978</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="30">
+        <v>120</v>
+      </c>
+      <c r="G39" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I39" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>756</v>
-      </c>
-      <c r="O39" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="P39" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>759</v>
-      </c>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="V39" s="8"/>
-      <c r="W39" s="8"/>
-      <c r="X39" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="Y39" s="8"/>
-      <c r="Z39" s="8" t="s">
+      <c r="I39" s="29" t="s">
+        <v>739</v>
+      </c>
+      <c r="J39" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N39" s="29" t="s">
+        <v>740</v>
+      </c>
+      <c r="O39" s="29" t="s">
+        <v>741</v>
+      </c>
+      <c r="P39" s="29" t="s">
+        <v>742</v>
+      </c>
+      <c r="Q39" s="29" t="s">
+        <v>743</v>
+      </c>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29" t="s">
+        <v>744</v>
+      </c>
+      <c r="T39" s="29" t="s">
+        <v>745</v>
+      </c>
+      <c r="U39" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="V39" s="29"/>
+      <c r="W39" s="29"/>
+      <c r="X39" s="33">
+        <v>1978</v>
+      </c>
+      <c r="Y39" s="29" t="s">
+        <v>746</v>
+      </c>
+      <c r="Z39" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA39" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA39" s="8" t="s">
-        <v>318</v>
-      </c>
       <c r="AB39" s="1" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="AC39" s="6" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-margit-carstensen; pers-gottfried-john; pers-brigitte-mira; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
+        <v>pers-hark-bohm; pers-lilo-pempeit; pers-gottfried-john; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
       </c>
       <c r="AD39" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H39:N39,P39),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-juliane-lorenz; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" ht="370">
-      <c r="A40" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D40" s="9">
-        <v>1981</v>
-      </c>
-      <c r="E40" s="8" t="s">
+        <v>pers-michael-ballhaus; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" ht="228">
+      <c r="A40" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>747</v>
+      </c>
+      <c r="D40" s="39">
+        <v>1979</v>
+      </c>
+      <c r="E40" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="9">
-        <v>115</v>
-      </c>
-      <c r="G40" s="8" t="s">
+      <c r="F40" s="30">
+        <v>105</v>
+      </c>
+      <c r="G40" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I40" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="P40" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="Q40" s="8" t="s">
-        <v>790</v>
-      </c>
-      <c r="R40" s="8"/>
-      <c r="S40" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="V40" s="8"/>
-      <c r="W40" s="8"/>
-      <c r="X40" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y40" s="8"/>
-      <c r="Z40" s="8" t="s">
-        <v>766</v>
-      </c>
-      <c r="AA40" s="8" t="s">
+      <c r="I40" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N40" s="29" t="s">
+        <v>748</v>
+      </c>
+      <c r="O40" s="29" t="s">
+        <v>749</v>
+      </c>
+      <c r="P40" s="29" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q40" s="29" t="s">
+        <v>751</v>
+      </c>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y40" s="29"/>
+      <c r="Z40" s="29" t="s">
+        <v>752</v>
+      </c>
+      <c r="AA40" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="AC40" s="6" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-brigitte-mira; pers-hanna-schygulla</v>
+        <v>pers-hark-bohm; pers-margit-carstensen; pers-peer-raben; pers-hanna-schygulla</v>
       </c>
       <c r="AD40" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H40:N40,P40),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-michael-ballhaus; pers-juliane-lorenz; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" ht="45">
-      <c r="A41" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>767</v>
-      </c>
-      <c r="D41" s="9">
-        <v>1981</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="F41" s="9">
-        <v>91</v>
-      </c>
-      <c r="G41" s="8" t="s">
+        <v>pers-juliane-lorenz; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="342">
+      <c r="A41" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="D41" s="39">
+        <v>1980</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="30">
+        <v>894</v>
+      </c>
+      <c r="G41" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I41" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8" t="s">
-        <v>769</v>
-      </c>
-      <c r="Q41" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="R41" s="8"/>
-      <c r="S41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="8"/>
-      <c r="X41" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y41" s="8"/>
-      <c r="Z41" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="AA41" s="8" t="s">
-        <v>45</v>
+      <c r="I41" s="29" t="s">
+        <v>753</v>
+      </c>
+      <c r="J41" s="29" t="s">
+        <v>754</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N41" s="29" t="s">
+        <v>755</v>
+      </c>
+      <c r="O41" s="29" t="s">
+        <v>756</v>
+      </c>
+      <c r="P41" s="29" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q41" s="29" t="s">
+        <v>758</v>
+      </c>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="V41" s="29"/>
+      <c r="W41" s="29"/>
+      <c r="X41" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y41" s="29"/>
+      <c r="Z41" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA41" s="29" t="s">
+        <v>317</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AC41" s="6" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
-        <v/>
+        <v>pers-margit-carstensen; pers-gottfried-john; pers-brigitte-mira; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
       </c>
       <c r="AD41" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H41:N41,P41),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:30" ht="240">
-      <c r="A42" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="D42" s="9">
+        <v>pers-juliane-lorenz; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" ht="409.6">
+      <c r="A42" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="39">
         <v>1981</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="9">
-        <v>113</v>
-      </c>
-      <c r="G42" s="8" t="s">
+      <c r="F42" s="30">
+        <v>115</v>
+      </c>
+      <c r="G42" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I42" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="K42" s="8" t="s">
+      <c r="I42" s="29" t="s">
+        <v>759</v>
+      </c>
+      <c r="J42" s="29" t="s">
+        <v>760</v>
+      </c>
+      <c r="K42" s="29" t="s">
+        <v>761</v>
+      </c>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N42" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8" t="s">
-        <v>774</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="O42" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="Q42" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="8" t="s">
+      <c r="O42" s="29" t="s">
+        <v>763</v>
+      </c>
+      <c r="P42" s="29" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q42" s="29" t="s">
+        <v>844</v>
+      </c>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29" t="s">
+        <v>789</v>
+      </c>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="V42" s="29"/>
+      <c r="W42" s="29"/>
+      <c r="X42" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y42" s="29"/>
+      <c r="Z42" s="29" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA42" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB42" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="AA42" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB42" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="AC42" s="6" t="str">
         <f>IF(O42="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O42)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O42)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O42)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O42)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O42)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O42)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O42)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O42)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O42)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O42)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O42)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O42)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O42)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O42)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O42)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O42)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O42)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O42)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O42)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O42)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O42)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O42)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O42)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-gunther-kaufmann</v>
+        <v>pers-hark-bohm; pers-peter-chatel; pers-lilo-pempeit; pers-gottfried-john; pers-irm-hermann; pers-brigitte-mira; pers-hanna-schygulla</v>
       </c>
       <c r="AD42" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H42:N42,P42),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
-        <v>pers-juliane-lorenz; pers-peer-raben</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" ht="255">
-      <c r="A43" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="D43" s="9">
+        <v>pers-michael-ballhaus; pers-juliane-lorenz; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="76">
+      <c r="A43" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>766</v>
+      </c>
+      <c r="D43" s="39">
         <v>1981</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="8" t="s">
+      <c r="E43" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="F43" s="30">
+        <v>91</v>
+      </c>
+      <c r="G43" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8" t="s">
-        <v>780</v>
-      </c>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8" t="s">
-        <v>781</v>
-      </c>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="V43" s="8"/>
-      <c r="W43" s="8"/>
-      <c r="X43" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y43" s="8"/>
-      <c r="Z43" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="AA43" s="8" t="s">
+      <c r="I43" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="Q43" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="29"/>
+      <c r="X43" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y43" s="29"/>
+      <c r="Z43" s="29" t="s">
+        <v>770</v>
+      </c>
+      <c r="AA43" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="AC43" s="6" t="str">
         <f>IF(O43="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O43)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O43)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O43)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O43)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O43)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O43)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O43)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O43)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O43)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O43)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O43)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O43)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O43)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O43)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O43)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O43)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O43)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O43)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O43)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O43)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O43)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O43)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O43)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-lilo-pempeit; pers-gunther-kaufmann</v>
+        <v/>
       </c>
       <c r="AD43" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H43:N43,P43),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="270">
-      <c r="A44" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D44" s="9">
-        <v>1982</v>
-      </c>
-      <c r="E44" s="8" t="s">
+    <row r="44" spans="1:30" ht="304">
+      <c r="A44" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>771</v>
+      </c>
+      <c r="D44" s="39">
+        <v>1981</v>
+      </c>
+      <c r="E44" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="9">
-        <v>107</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="H44" s="8" t="s">
+      <c r="F44" s="30">
+        <v>113</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="8" t="s">
-        <v>783</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>784</v>
-      </c>
-      <c r="M44" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>785</v>
-      </c>
-      <c r="O44" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="P44" s="8" t="s">
-        <v>787</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="V44" s="8"/>
-      <c r="W44" s="8"/>
-      <c r="X44" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y44" s="8"/>
-      <c r="Z44" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="AA44" s="8" t="s">
+      <c r="I44" s="29" t="s">
+        <v>772</v>
+      </c>
+      <c r="J44" s="29" t="s">
+        <v>754</v>
+      </c>
+      <c r="K44" s="29" t="s">
+        <v>761</v>
+      </c>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29" t="s">
+        <v>773</v>
+      </c>
+      <c r="N44" s="29" t="s">
+        <v>774</v>
+      </c>
+      <c r="O44" s="29" t="s">
+        <v>775</v>
+      </c>
+      <c r="P44" s="29" t="s">
+        <v>776</v>
+      </c>
+      <c r="Q44" s="29" t="s">
+        <v>777</v>
+      </c>
+      <c r="R44" s="29"/>
+      <c r="S44" s="29"/>
+      <c r="T44" s="29"/>
+      <c r="U44" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="V44" s="29"/>
+      <c r="W44" s="29"/>
+      <c r="X44" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y44" s="29"/>
+      <c r="Z44" s="29" t="s">
+        <v>778</v>
+      </c>
+      <c r="AA44" s="29" t="s">
         <v>45</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="AC44" s="6" t="str">
         <f>IF(O44="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O44)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O44)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O44)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O44)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O44)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O44)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O44)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O44)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O44)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O44)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O44)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O44)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O44)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O44)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O44)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O44)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O44)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O44)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O44)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O44)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O44)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O44)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O44)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-gunther-kaufmann</v>
+        <v>pers-hark-bohm; pers-gunther-kaufmann</v>
       </c>
       <c r="AD44" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H44:N44,P44),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
+        <v>pers-juliane-lorenz; pers-peer-raben</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="380">
+      <c r="A45" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B45" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="D45" s="39">
+        <v>1981</v>
+      </c>
+      <c r="E45" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="30"/>
+      <c r="G45" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29" t="s">
+        <v>779</v>
+      </c>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29" t="s">
+        <v>780</v>
+      </c>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+      <c r="T45" s="29"/>
+      <c r="U45" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="V45" s="29"/>
+      <c r="W45" s="29"/>
+      <c r="X45" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y45" s="29"/>
+      <c r="Z45" s="29" t="s">
+        <v>781</v>
+      </c>
+      <c r="AA45" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB45" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC45" s="6" t="str">
+        <f>IF(O45="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O45)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O45)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O45)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O45)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O45)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O45)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O45)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O45)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O45)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O45)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O45)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O45)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O45)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O45)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O45)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O45)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O45)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O45)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O45)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O45)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O45)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O45)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O45)),'Référentiel entourage'!$A$24,"")))</f>
+        <v>pers-lilo-pempeit; pers-gunther-kaufmann</v>
+      </c>
+      <c r="AD45" s="6" t="str">
+        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H45:N45,P45),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:30" ht="342">
+      <c r="A46" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="C46" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="D46" s="39">
+        <v>1982</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="30">
+        <v>107</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>782</v>
+      </c>
+      <c r="J46" s="29" t="s">
+        <v>754</v>
+      </c>
+      <c r="K46" s="29" t="s">
+        <v>761</v>
+      </c>
+      <c r="L46" s="29" t="s">
+        <v>783</v>
+      </c>
+      <c r="M46" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="N46" s="29" t="s">
+        <v>784</v>
+      </c>
+      <c r="O46" s="29" t="s">
+        <v>785</v>
+      </c>
+      <c r="P46" s="29" t="s">
+        <v>786</v>
+      </c>
+      <c r="Q46" s="29" t="s">
+        <v>787</v>
+      </c>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29" t="s">
+        <v>788</v>
+      </c>
+      <c r="AA46" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB46" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AC46" s="6" t="str">
+        <f>IF(O46="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O46)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O46)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O46)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O46)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O46)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O46)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O46)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O46)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O46)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O46)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O46)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O46)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O46)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O46)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O46)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O46)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O46)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O46)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O46)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O46)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O46)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O46)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O46)),'Référentiel entourage'!$A$24,"")))</f>
+        <v>pers-gunther-kaufmann</v>
+      </c>
+      <c r="AD46" s="6" t="str">
+        <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H46:N46,P46),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
         <v>pers-michael-fengler; pers-juliane-lorenz; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:T21 V4:AA21">
+  <conditionalFormatting sqref="V5:AA23 A5:T23">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="AA4:AA21" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="AA5:AA23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"À compléter,Partiellement documenté,Documenté,Validé"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8169,10 +8441,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8185,41 +8457,41 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" t="s">
         <v>317</v>
-      </c>
-      <c r="B3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -8237,33 +8509,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="107" customHeight="1">
-      <c r="A1" s="29" t="s">
-        <v>324</v>
-      </c>
-      <c r="B1" s="29"/>
+      <c r="A1" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:2" ht="133" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="133" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="133" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="133" customHeight="1">
@@ -8271,15 +8543,15 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="133" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="133" customHeight="1">
@@ -8287,7 +8559,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="133" customHeight="1">
@@ -8295,7 +8567,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="133" customHeight="1">
@@ -8303,7 +8575,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="133" customHeight="1">
@@ -8311,7 +8583,7 @@
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="133" customHeight="1">
@@ -8319,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="133" customHeight="1">
@@ -8327,39 +8599,39 @@
         <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16">
       <c r="A13" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16">
       <c r="A14" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="71" customHeight="1">
       <c r="A15" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="71" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="109" customHeight="1">
@@ -8367,7 +8639,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="109" customHeight="1">
@@ -8375,15 +8647,15 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76" customHeight="1">
       <c r="A19" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -8407,1061 +8679,1061 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="98">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="G1" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>839</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>840</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="J1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="K1" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>842</v>
-      </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="N1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:14" ht="156">
+      <c r="A2" s="15" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="156">
-      <c r="A2" s="17" t="s">
+      <c r="B2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18" t="s">
+      <c r="G2" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="H2" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="I2" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="J2" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="L2" s="16"/>
+      <c r="M2" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="N2" s="18" t="s">
+    </row>
+    <row r="3" spans="1:14" ht="60">
+      <c r="A3" s="15" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="60">
-      <c r="A3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18" t="s">
+      <c r="G3" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="H3" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="I3" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="J3" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="K3" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="L3" s="16"/>
+      <c r="M3" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="16" t="s">
+      <c r="N3" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="N3" s="18" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="48">
+      <c r="A4" s="15" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="48">
-      <c r="A4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="G4" s="18" t="s">
+      <c r="H4" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="I4" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="J4" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="L4" s="16"/>
+      <c r="M4" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="16" t="s">
+      <c r="N4" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="N4" s="18" t="s">
+    </row>
+    <row r="5" spans="1:14" ht="182">
+      <c r="A5" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>793</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="L5" s="16"/>
+      <c r="M5" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="84">
+      <c r="A6" s="15" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="182">
-      <c r="A5" s="17" t="s">
-        <v>792</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>793</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>794</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>795</v>
-      </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18" t="s">
-        <v>796</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>797</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>798</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>799</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>800</v>
-      </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="16" t="s">
+      <c r="B6" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="L6" s="16"/>
+      <c r="M6" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="156">
+      <c r="A7" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16" t="s">
         <v>801</v>
       </c>
-      <c r="N5" s="18" t="s">
+      <c r="G7" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="72">
+      <c r="A8" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="L8" s="16"/>
+      <c r="M8" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="156">
+      <c r="A9" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="144">
+      <c r="A10" s="15" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="84">
-      <c r="A6" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>398</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>399</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="B10" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>806</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="L10" s="16"/>
+      <c r="M10" s="14" t="s">
+        <v>809</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="108">
+      <c r="A11" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="L11" s="16"/>
+      <c r="M11" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="120">
+      <c r="A12" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="L12" s="16"/>
+      <c r="M12" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="84">
+      <c r="A13" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18" t="s">
+      <c r="G13" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="L13" s="16"/>
+      <c r="M13" s="14" t="s">
+        <v>467</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="96">
+      <c r="A14" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="L14" s="16"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="16" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="84">
+      <c r="A15" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="L15" s="16"/>
+      <c r="M15" s="14" t="s">
+        <v>812</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="72">
+      <c r="A16" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="L16" s="16"/>
+      <c r="M16" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="72">
+      <c r="A17" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="G6" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="N6" s="18" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="156">
-      <c r="A7" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18" t="s">
-        <v>803</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>414</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="L7" s="18"/>
-      <c r="M7" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="72">
-      <c r="A8" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="N8" s="18" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="156">
-      <c r="A9" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>433</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>434</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="144">
-      <c r="A10" s="17" t="s">
-        <v>804</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>591</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>805</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>806</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>807</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>808</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>809</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>810</v>
-      </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="16" t="s">
-        <v>811</v>
-      </c>
-      <c r="N10" s="18" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="108">
-      <c r="A11" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>443</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>444</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="120">
-      <c r="A12" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>452</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="H17" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="L17" s="16"/>
+      <c r="M17" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="204">
+      <c r="A18" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="L18" s="16"/>
+      <c r="M18" s="14" t="s">
         <v>813</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="16" t="s">
-        <v>458</v>
-      </c>
-      <c r="N12" s="18" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="84">
-      <c r="A13" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>463</v>
-      </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18" t="s">
+      <c r="N18" s="16" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="42">
+      <c r="A19" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28">
+      <c r="A20" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="L20" s="16"/>
+      <c r="M20" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="156">
+      <c r="A21" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>815</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="48">
+      <c r="A22" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="G13" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="16" t="s">
-        <v>468</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="96">
-      <c r="A14" s="17" t="s">
-        <v>470</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18" t="s">
-        <v>474</v>
-      </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="K14" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="18" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="84">
-      <c r="A15" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="L15" s="18"/>
-      <c r="M15" s="16" t="s">
-        <v>814</v>
-      </c>
-      <c r="N15" s="18" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="72">
-      <c r="A16" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>490</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>493</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>495</v>
-      </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="16" t="s">
-        <v>496</v>
-      </c>
-      <c r="N16" s="18" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="72">
-      <c r="A17" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>500</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>501</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="K17" s="19" t="s">
-        <v>506</v>
-      </c>
-      <c r="L17" s="18"/>
-      <c r="M17" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="204">
-      <c r="A18" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="K18" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="L18" s="18"/>
-      <c r="M18" s="16" t="s">
-        <v>815</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="42">
-      <c r="A19" s="17" t="s">
-        <v>518</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>519</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>521</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>523</v>
-      </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="16" t="s">
-        <v>524</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="28">
-      <c r="A20" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>528</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="H22" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="L22" s="16"/>
+      <c r="M22" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="168">
+      <c r="A23" s="21" t="s">
+        <v>816</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>531</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="156">
-      <c r="A21" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>537</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>538</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>540</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>541</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>542</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>816</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>817</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>543</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>544</v>
-      </c>
-      <c r="N21" s="18" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="48">
-      <c r="A22" s="17" t="s">
-        <v>546</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>547</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>549</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18" t="s">
-        <v>550</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>551</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>552</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>554</v>
-      </c>
-      <c r="L22" s="18"/>
-      <c r="M22" s="16" t="s">
-        <v>555</v>
-      </c>
-      <c r="N22" s="18" t="s">
+      <c r="G23" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>822</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="L23" s="16"/>
+      <c r="M23" s="14" t="s">
+        <v>824</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="42">
+      <c r="A24" s="15" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="168">
-      <c r="A23" s="23" t="s">
-        <v>818</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>819</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>820</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>821</v>
-      </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>822</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>823</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>824</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="L23" s="18"/>
-      <c r="M23" s="16" t="s">
+      <c r="B24" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="L24" s="16"/>
+      <c r="M24" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="60">
+      <c r="A25" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="L25" s="16"/>
+      <c r="M25" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="96">
+      <c r="A26" s="23" t="s">
+        <v>575</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="K26" s="25" t="s">
+        <v>580</v>
+      </c>
+      <c r="L26" s="24"/>
+      <c r="M26" s="14" t="s">
         <v>826</v>
       </c>
-      <c r="N23" s="18" t="s">
+      <c r="N26" s="24" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="124">
+      <c r="A27" s="26" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="42">
-      <c r="A24" s="17" t="s">
-        <v>557</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>558</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>559</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>561</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>563</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="L24" s="18"/>
-      <c r="M24" s="16" t="s">
-        <v>565</v>
-      </c>
-      <c r="N24" s="18" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="60">
-      <c r="A25" s="17" t="s">
-        <v>567</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>568</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>569</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>570</v>
-      </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>561</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>572</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="L25" s="18"/>
-      <c r="M25" s="22" t="s">
-        <v>574</v>
-      </c>
-      <c r="N25" s="18" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="96">
-      <c r="A26" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>577</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>578</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>579</v>
-      </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>561</v>
-      </c>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26" t="s">
-        <v>580</v>
-      </c>
-      <c r="K26" s="27" t="s">
-        <v>581</v>
-      </c>
-      <c r="L26" s="26"/>
-      <c r="M26" s="16" t="s">
+      <c r="B27" s="26" t="s">
         <v>828</v>
       </c>
-      <c r="N26" s="26" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="124">
-      <c r="A27" s="28" t="s">
+      <c r="C27" s="26" t="s">
         <v>829</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="D27" s="26" t="s">
         <v>830</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="E27" s="26"/>
+      <c r="F27" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="G27" s="26" t="s">
         <v>831</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="H27" s="26" t="s">
         <v>832</v>
       </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28" t="s">
-        <v>530</v>
-      </c>
-      <c r="G27" s="28" t="s">
+      <c r="I27" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="J27" s="26" t="s">
         <v>834</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="J27" s="28" t="s">
+      <c r="L27" s="26"/>
+      <c r="M27" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="N27" s="26" t="s">
         <v>837</v>
-      </c>
-      <c r="L27" s="28"/>
-      <c r="M27" s="8" t="s">
-        <v>838</v>
-      </c>
-      <c r="N27" s="28" t="s">
-        <v>839</v>
       </c>
     </row>
   </sheetData>
